--- a/resources/Data/University Fees.xlsx
+++ b/resources/Data/University Fees.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gloria/Desktop/Uni/2022 Honours/Materials/Calculator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Financial Calculator\resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398E3A0E-59FB-0C47-919E-B8EA08C8A579}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2456CE-AADB-4A33-BA9F-7513D93D8D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28200" windowHeight="15660" activeTab="1" xr2:uid="{01CFE5D6-AA87-C245-BD6A-9B9FEBC32DEB}"/>
+    <workbookView xWindow="46335" yWindow="1995" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{9076E21E-61F9-4A5A-ABD0-5DFDD0B945A9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tuition Fees" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,11 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1794,8 +1798,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1842,7 +1846,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1858,6 +1862,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2102,9 +2112,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2112,17 +2122,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2134,80 +2144,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2219,41 +2229,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2262,29 +2272,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2293,25 +2303,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2324,7 +2340,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2760,88 +2776,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416D676E-B013-8A48-ABB7-A5EE076452DB}">
   <dimension ref="E2:AI142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="38.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="18.375" style="5" customWidth="1"/>
     <col min="7" max="7" width="17" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="32.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.33203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="32.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="3" customWidth="1"/>
     <col min="11" max="11" width="17.5" style="3" customWidth="1"/>
-    <col min="13" max="13" width="60.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.33203125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="59.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="23.33203125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="60.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="20.875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="59.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="23.375" style="3" customWidth="1"/>
     <col min="19" max="19" width="23.5" style="3" customWidth="1"/>
-    <col min="21" max="21" width="43.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.6640625" style="3" customWidth="1"/>
-    <col min="23" max="23" width="24.1640625" style="3" customWidth="1"/>
+    <col min="21" max="21" width="43.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.625" style="3" customWidth="1"/>
+    <col min="23" max="23" width="24.125" style="3" customWidth="1"/>
     <col min="25" max="25" width="51" style="1" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="20.5" style="3" customWidth="1"/>
     <col min="27" max="27" width="22" style="3" customWidth="1"/>
-    <col min="29" max="29" width="54.1640625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="54.125" style="1" customWidth="1"/>
     <col min="30" max="30" width="22" style="3" customWidth="1"/>
     <col min="31" max="31" width="26.5" style="3" customWidth="1"/>
     <col min="33" max="33" width="66.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="20.6640625" style="3" customWidth="1"/>
-    <col min="35" max="35" width="23.33203125" style="3" customWidth="1"/>
+    <col min="34" max="34" width="20.625" style="3" customWidth="1"/>
+    <col min="35" max="35" width="23.375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="F2" s="86" t="s">
+    <row r="2" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="F2" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="86"/>
-      <c r="H2" s="86"/>
-      <c r="I2" s="86"/>
-      <c r="J2" s="86"/>
-      <c r="K2" s="86"/>
-      <c r="L2" s="86"/>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86"/>
-    </row>
-    <row r="4" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E4" s="89"/>
-      <c r="F4" s="87" t="s">
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="88"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+    </row>
+    <row r="4" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E4" s="91"/>
+      <c r="F4" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="88"/>
+      <c r="G4" s="90"/>
       <c r="H4" s="1"/>
-      <c r="J4" s="87" t="s">
+      <c r="J4" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="88"/>
+      <c r="K4" s="90"/>
       <c r="L4" s="1"/>
       <c r="M4"/>
-      <c r="N4" s="85" t="s">
+      <c r="N4" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="O4" s="85"/>
+      <c r="O4" s="87"/>
       <c r="Q4" s="19"/>
-      <c r="R4" s="85" t="s">
+      <c r="R4" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="S4" s="85"/>
-      <c r="V4" s="85" t="s">
+      <c r="S4" s="87"/>
+      <c r="V4" s="87" t="s">
         <v>209</v>
       </c>
-      <c r="W4" s="85"/>
-      <c r="Z4" s="85" t="s">
+      <c r="W4" s="87"/>
+      <c r="Z4" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="AA4" s="85"/>
-      <c r="AD4" s="85" t="s">
+      <c r="AA4" s="87"/>
+      <c r="AD4" s="87" t="s">
         <v>475</v>
       </c>
-      <c r="AE4" s="85"/>
-      <c r="AH4" s="85" t="s">
+      <c r="AE4" s="87"/>
+      <c r="AH4" s="87" t="s">
         <v>505</v>
       </c>
-      <c r="AI4" s="85"/>
-    </row>
-    <row r="5" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E5" s="89"/>
+      <c r="AI4" s="87"/>
+    </row>
+    <row r="5" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E5" s="91"/>
       <c r="F5" s="11" t="s">
         <v>2</v>
       </c>
@@ -2895,52 +2911,52 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E6" s="87" t="s">
+    <row r="6" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E6" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="90"/>
-      <c r="G6" s="88"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="90"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="84" t="s">
+      <c r="I6" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="84"/>
-      <c r="K6" s="84"/>
+      <c r="J6" s="86"/>
+      <c r="K6" s="86"/>
       <c r="L6" s="1"/>
-      <c r="M6" s="84" t="s">
+      <c r="M6" s="86" t="s">
         <v>121</v>
       </c>
-      <c r="N6" s="84"/>
-      <c r="O6" s="84"/>
-      <c r="Q6" s="84" t="s">
+      <c r="N6" s="86"/>
+      <c r="O6" s="86"/>
+      <c r="Q6" s="86" t="s">
         <v>186</v>
       </c>
-      <c r="R6" s="84"/>
-      <c r="S6" s="84"/>
-      <c r="U6" s="84" t="s">
+      <c r="R6" s="86"/>
+      <c r="S6" s="86"/>
+      <c r="U6" s="86" t="s">
         <v>210</v>
       </c>
-      <c r="V6" s="84"/>
-      <c r="W6" s="84"/>
-      <c r="Y6" s="81" t="s">
+      <c r="V6" s="86"/>
+      <c r="W6" s="86"/>
+      <c r="Y6" s="83" t="s">
         <v>235</v>
       </c>
-      <c r="Z6" s="82"/>
-      <c r="AA6" s="83"/>
-      <c r="AC6" s="84" t="s">
+      <c r="Z6" s="84"/>
+      <c r="AA6" s="85"/>
+      <c r="AC6" s="86" t="s">
         <v>476</v>
       </c>
-      <c r="AD6" s="84"/>
-      <c r="AE6" s="84"/>
-      <c r="AG6" s="84" t="s">
+      <c r="AD6" s="86"/>
+      <c r="AE6" s="86"/>
+      <c r="AG6" s="86" t="s">
         <v>506</v>
       </c>
-      <c r="AH6" s="84"/>
-      <c r="AI6" s="84"/>
-    </row>
-    <row r="7" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E7" s="2" t="s">
+      <c r="AH6" s="86"/>
+      <c r="AI6" s="86"/>
+    </row>
+    <row r="7" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E7" s="81" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="7">
@@ -3015,8 +3031,8 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="8" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E8" s="2" t="s">
+    <row r="8" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E8" s="81" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="7">
@@ -3063,11 +3079,11 @@
       <c r="W8" s="18">
         <v>12080</v>
       </c>
-      <c r="Y8" s="84" t="s">
+      <c r="Y8" s="86" t="s">
         <v>236</v>
       </c>
-      <c r="Z8" s="84"/>
-      <c r="AA8" s="84"/>
+      <c r="Z8" s="86"/>
+      <c r="AA8" s="86"/>
       <c r="AC8" s="10" t="s">
         <v>478</v>
       </c>
@@ -3087,8 +3103,8 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="9" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E9" s="2" t="s">
+    <row r="9" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E9" s="81" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="7">
@@ -3163,8 +3179,8 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="10" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E10" s="2" t="s">
+    <row r="10" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E10" s="81" t="s">
         <v>12</v>
       </c>
       <c r="F10" s="7">
@@ -3239,8 +3255,8 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="11" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E11" s="2" t="s">
+    <row r="11" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E11" s="81" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="7">
@@ -3250,11 +3266,11 @@
         <v>8021</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="81" t="s">
+      <c r="I11" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="82"/>
-      <c r="K11" s="83"/>
+      <c r="J11" s="84"/>
+      <c r="K11" s="85"/>
       <c r="L11" s="1"/>
       <c r="M11" s="2" t="s">
         <v>73</v>
@@ -3283,11 +3299,11 @@
       <c r="W11" s="18">
         <v>14095</v>
       </c>
-      <c r="Y11" s="81" t="s">
+      <c r="Y11" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="Z11" s="82"/>
-      <c r="AA11" s="83"/>
+      <c r="Z11" s="84"/>
+      <c r="AA11" s="85"/>
       <c r="AC11" s="10" t="s">
         <v>477</v>
       </c>
@@ -3307,8 +3323,8 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="12" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E12" s="2" t="s">
+    <row r="12" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E12" s="81" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="7">
@@ -3373,14 +3389,14 @@
       <c r="AE12" s="18">
         <v>14630</v>
       </c>
-      <c r="AG12" s="81" t="s">
+      <c r="AG12" s="83" t="s">
         <v>509</v>
       </c>
-      <c r="AH12" s="82"/>
-      <c r="AI12" s="83"/>
-    </row>
-    <row r="13" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E13" s="2" t="s">
+      <c r="AH12" s="84"/>
+      <c r="AI12" s="85"/>
+    </row>
+    <row r="13" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E13" s="81" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="7">
@@ -3427,11 +3443,11 @@
       <c r="W13" s="18">
         <v>14493</v>
       </c>
-      <c r="Y13" s="81" t="s">
+      <c r="Y13" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="Z13" s="82"/>
-      <c r="AA13" s="83"/>
+      <c r="Z13" s="84"/>
+      <c r="AA13" s="85"/>
       <c r="AC13" s="10" t="s">
         <v>18</v>
       </c>
@@ -3451,8 +3467,8 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="14" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E14" s="9" t="s">
+    <row r="14" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E14" s="82" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="7">
@@ -3490,11 +3506,11 @@
       <c r="S14" s="18">
         <v>8021</v>
       </c>
-      <c r="U14" s="84" t="s">
+      <c r="U14" s="86" t="s">
         <v>217</v>
       </c>
-      <c r="V14" s="84"/>
-      <c r="W14" s="84"/>
+      <c r="V14" s="86"/>
+      <c r="W14" s="86"/>
       <c r="Y14" s="2" t="s">
         <v>218</v>
       </c>
@@ -3523,12 +3539,12 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="15" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E15" s="84" t="s">
+    <row r="15" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E15" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
       <c r="H15" s="1"/>
       <c r="I15" s="2" t="s">
         <v>31</v>
@@ -3595,8 +3611,8 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="16" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E16" s="2" t="s">
+    <row r="16" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E16" s="81" t="s">
         <v>270</v>
       </c>
       <c r="F16" s="6" t="s">
@@ -3606,11 +3622,11 @@
         <v>14630</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="84" t="s">
+      <c r="I16" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="84"/>
-      <c r="K16" s="84"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
       <c r="L16" s="1"/>
       <c r="M16" s="2" t="s">
         <v>80</v>
@@ -3667,8 +3683,8 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="17" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E17" s="2" t="s">
+    <row r="17" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E17" s="81" t="s">
         <v>271</v>
       </c>
       <c r="F17" s="6" t="s">
@@ -3697,11 +3713,11 @@
       <c r="O17" s="18">
         <v>9662</v>
       </c>
-      <c r="Q17" s="81" t="s">
+      <c r="Q17" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="R17" s="82"/>
-      <c r="S17" s="83"/>
+      <c r="R17" s="84"/>
+      <c r="S17" s="85"/>
       <c r="U17" s="2" t="s">
         <v>70</v>
       </c>
@@ -3720,19 +3736,19 @@
       <c r="AA17" s="18">
         <v>14630</v>
       </c>
-      <c r="AC17" s="84" t="s">
+      <c r="AC17" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="AD17" s="84"/>
-      <c r="AE17" s="84"/>
-      <c r="AG17" s="81" t="s">
+      <c r="AD17" s="86"/>
+      <c r="AE17" s="86"/>
+      <c r="AG17" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="AH17" s="82"/>
-      <c r="AI17" s="83"/>
-    </row>
-    <row r="18" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E18" s="2" t="s">
+      <c r="AH17" s="84"/>
+      <c r="AI17" s="85"/>
+    </row>
+    <row r="18" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E18" s="81" t="s">
         <v>272</v>
       </c>
       <c r="F18" s="6" t="s">
@@ -3807,7 +3823,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="19" spans="5:35" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E19" s="8" t="s">
         <v>273</v>
       </c>
@@ -3846,21 +3862,21 @@
       <c r="S19" s="18">
         <v>8021</v>
       </c>
-      <c r="U19" s="84" t="s">
+      <c r="U19" s="86" t="s">
         <v>219</v>
       </c>
-      <c r="V19" s="84"/>
-      <c r="W19" s="84"/>
-      <c r="Y19" s="84" t="s">
+      <c r="V19" s="86"/>
+      <c r="W19" s="86"/>
+      <c r="Y19" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="Z19" s="84"/>
-      <c r="AA19" s="84"/>
-      <c r="AC19" s="81" t="s">
+      <c r="Z19" s="86"/>
+      <c r="AA19" s="86"/>
+      <c r="AC19" s="83" t="s">
         <v>482</v>
       </c>
-      <c r="AD19" s="82"/>
-      <c r="AE19" s="83"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="85"/>
       <c r="AG19" s="10" t="s">
         <v>68</v>
       </c>
@@ -3871,7 +3887,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="20" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E20" s="2" t="s">
         <v>274</v>
       </c>
@@ -3947,7 +3963,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="21" spans="5:35" ht="17" x14ac:dyDescent="0.2">
+    <row r="21" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E21" s="2" t="s">
         <v>275</v>
       </c>
@@ -4023,7 +4039,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="22" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E22" s="2" t="s">
         <v>276</v>
       </c>
@@ -4080,18 +4096,18 @@
       <c r="AA22" s="18">
         <v>8021</v>
       </c>
-      <c r="AC22" s="84" t="s">
+      <c r="AC22" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="AD22" s="84"/>
-      <c r="AE22" s="84"/>
-      <c r="AG22" s="81" t="s">
+      <c r="AD22" s="86"/>
+      <c r="AE22" s="86"/>
+      <c r="AG22" s="83" t="s">
         <v>516</v>
       </c>
-      <c r="AH22" s="82"/>
-      <c r="AI22" s="83"/>
-    </row>
-    <row r="23" spans="5:35" x14ac:dyDescent="0.2">
+      <c r="AH22" s="84"/>
+      <c r="AI22" s="85"/>
+    </row>
+    <row r="23" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E23" s="2" t="s">
         <v>277</v>
       </c>
@@ -4167,7 +4183,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="24" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E24" s="2" t="s">
         <v>28</v>
       </c>
@@ -4188,11 +4204,11 @@
         <v>13500</v>
       </c>
       <c r="L24" s="1"/>
-      <c r="M24" s="81" t="s">
+      <c r="M24" s="83" t="s">
         <v>122</v>
       </c>
-      <c r="N24" s="82"/>
-      <c r="O24" s="83"/>
+      <c r="N24" s="84"/>
+      <c r="O24" s="85"/>
       <c r="Q24" s="2" t="s">
         <v>201</v>
       </c>
@@ -4202,16 +4218,16 @@
       <c r="S24" s="18">
         <v>8021</v>
       </c>
-      <c r="U24" s="84" t="s">
+      <c r="U24" s="86" t="s">
         <v>120</v>
       </c>
-      <c r="V24" s="84"/>
-      <c r="W24" s="84"/>
-      <c r="Y24" s="84" t="s">
+      <c r="V24" s="86"/>
+      <c r="W24" s="86"/>
+      <c r="Y24" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="Z24" s="84"/>
-      <c r="AA24" s="84"/>
+      <c r="Z24" s="86"/>
+      <c r="AA24" s="86"/>
       <c r="AC24" s="10" t="s">
         <v>88</v>
       </c>
@@ -4231,7 +4247,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="25" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E25" s="10" t="s">
         <v>39</v>
       </c>
@@ -4307,7 +4323,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="26" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E26" s="10" t="s">
         <v>278</v>
       </c>
@@ -4383,7 +4399,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="27" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E27" s="10" t="s">
         <v>279</v>
       </c>
@@ -4394,11 +4410,11 @@
         <v>3985</v>
       </c>
       <c r="H27" s="1"/>
-      <c r="I27" s="84" t="s">
+      <c r="I27" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="J27" s="84"/>
-      <c r="K27" s="84"/>
+      <c r="J27" s="86"/>
+      <c r="K27" s="86"/>
       <c r="L27" s="1"/>
       <c r="M27" s="2" t="s">
         <v>90</v>
@@ -4427,11 +4443,11 @@
       <c r="W27" s="18">
         <v>6599</v>
       </c>
-      <c r="Y27" s="84" t="s">
+      <c r="Y27" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="Z27" s="84"/>
-      <c r="AA27" s="84"/>
+      <c r="Z27" s="86"/>
+      <c r="AA27" s="86"/>
       <c r="AC27" s="10" t="s">
         <v>486</v>
       </c>
@@ -4451,7 +4467,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="28" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E28" s="10" t="s">
         <v>280</v>
       </c>
@@ -4479,11 +4495,11 @@
       <c r="O28" s="18">
         <v>5395</v>
       </c>
-      <c r="Q28" s="84" t="s">
+      <c r="Q28" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="R28" s="84"/>
-      <c r="S28" s="84"/>
+      <c r="R28" s="86"/>
+      <c r="S28" s="86"/>
       <c r="U28" s="2" t="s">
         <v>223</v>
       </c>
@@ -4502,11 +4518,11 @@
       <c r="AA28" s="18">
         <v>8021</v>
       </c>
-      <c r="AC28" s="84" t="s">
+      <c r="AC28" s="86" t="s">
         <v>487</v>
       </c>
-      <c r="AD28" s="84"/>
-      <c r="AE28" s="84"/>
+      <c r="AD28" s="86"/>
+      <c r="AE28" s="86"/>
       <c r="AG28" s="10" t="s">
         <v>518</v>
       </c>
@@ -4517,7 +4533,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="29" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E29" s="10" t="s">
         <v>281</v>
       </c>
@@ -4527,16 +4543,16 @@
       <c r="G29" s="14">
         <v>14630</v>
       </c>
-      <c r="I29" s="84" t="s">
+      <c r="I29" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="J29" s="84"/>
-      <c r="K29" s="84"/>
-      <c r="M29" s="84" t="s">
+      <c r="J29" s="86"/>
+      <c r="K29" s="86"/>
+      <c r="M29" s="86" t="s">
         <v>123</v>
       </c>
-      <c r="N29" s="84"/>
-      <c r="O29" s="84"/>
+      <c r="N29" s="86"/>
+      <c r="O29" s="86"/>
       <c r="Q29" s="2" t="s">
         <v>133</v>
       </c>
@@ -4583,7 +4599,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="30" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E30" s="10" t="s">
         <v>282</v>
       </c>
@@ -4647,13 +4663,13 @@
       <c r="AE30" s="18">
         <v>8021</v>
       </c>
-      <c r="AG30" s="84" t="s">
+      <c r="AG30" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="AH30" s="84"/>
-      <c r="AI30" s="84"/>
-    </row>
-    <row r="31" spans="5:35" x14ac:dyDescent="0.2">
+      <c r="AH30" s="86"/>
+      <c r="AI30" s="86"/>
+    </row>
+    <row r="31" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E31" s="10" t="s">
         <v>283</v>
       </c>
@@ -4663,11 +4679,11 @@
       <c r="G31" s="14">
         <v>14630</v>
       </c>
-      <c r="I31" s="84" t="s">
+      <c r="I31" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="J31" s="84"/>
-      <c r="K31" s="84"/>
+      <c r="J31" s="86"/>
+      <c r="K31" s="86"/>
       <c r="M31" s="2" t="s">
         <v>69</v>
       </c>
@@ -4723,7 +4739,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="32" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E32" s="10" t="s">
         <v>284</v>
       </c>
@@ -4760,11 +4776,11 @@
       <c r="S32" s="18">
         <v>8021</v>
       </c>
-      <c r="U32" s="81" t="s">
+      <c r="U32" s="83" t="s">
         <v>226</v>
       </c>
-      <c r="V32" s="82"/>
-      <c r="W32" s="83"/>
+      <c r="V32" s="84"/>
+      <c r="W32" s="85"/>
       <c r="Y32" s="2" t="s">
         <v>252</v>
       </c>
@@ -4793,7 +4809,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="33" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E33" s="10" t="s">
         <v>285</v>
       </c>
@@ -4867,7 +4883,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="34" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E34" s="10" t="s">
         <v>286</v>
       </c>
@@ -4877,11 +4893,11 @@
       <c r="G34" s="14">
         <v>3985</v>
       </c>
-      <c r="I34" s="84" t="s">
+      <c r="I34" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="J34" s="84"/>
-      <c r="K34" s="84"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
       <c r="M34" s="2" t="s">
         <v>105</v>
       </c>
@@ -4937,7 +4953,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="35" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E35" s="10" t="s">
         <v>287</v>
       </c>
@@ -5001,13 +5017,13 @@
       <c r="AE35" s="18">
         <v>8021</v>
       </c>
-      <c r="AG35" s="81" t="s">
+      <c r="AG35" s="83" t="s">
         <v>524</v>
       </c>
-      <c r="AH35" s="82"/>
-      <c r="AI35" s="83"/>
-    </row>
-    <row r="36" spans="5:35" x14ac:dyDescent="0.2">
+      <c r="AH35" s="84"/>
+      <c r="AI35" s="85"/>
+    </row>
+    <row r="36" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E36" s="10" t="s">
         <v>288</v>
       </c>
@@ -5017,11 +5033,11 @@
       <c r="G36" s="14">
         <v>3985</v>
       </c>
-      <c r="I36" s="84" t="s">
+      <c r="I36" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="J36" s="84"/>
-      <c r="K36" s="84"/>
+      <c r="J36" s="86"/>
+      <c r="K36" s="86"/>
       <c r="M36" s="2" t="s">
         <v>113</v>
       </c>
@@ -5058,11 +5074,11 @@
       <c r="AA36" s="18">
         <v>8021</v>
       </c>
-      <c r="AC36" s="84" t="s">
+      <c r="AC36" s="86" t="s">
         <v>493</v>
       </c>
-      <c r="AD36" s="84"/>
-      <c r="AE36" s="84"/>
+      <c r="AD36" s="86"/>
+      <c r="AE36" s="86"/>
       <c r="AG36" s="10" t="s">
         <v>103</v>
       </c>
@@ -5073,7 +5089,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="37" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E37" s="10" t="s">
         <v>289</v>
       </c>
@@ -5119,11 +5135,11 @@
       <c r="W37" s="18">
         <v>7655</v>
       </c>
-      <c r="Y37" s="84" t="s">
+      <c r="Y37" s="86" t="s">
         <v>261</v>
       </c>
-      <c r="Z37" s="84"/>
-      <c r="AA37" s="84"/>
+      <c r="Z37" s="86"/>
+      <c r="AA37" s="86"/>
       <c r="AC37" s="10" t="s">
         <v>494</v>
       </c>
@@ -5143,7 +5159,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="38" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E38" s="10" t="s">
         <v>290</v>
       </c>
@@ -5162,11 +5178,11 @@
       <c r="K38" s="18">
         <v>8500</v>
       </c>
-      <c r="M38" s="84" t="s">
+      <c r="M38" s="86" t="s">
         <v>124</v>
       </c>
-      <c r="N38" s="84"/>
-      <c r="O38" s="84"/>
+      <c r="N38" s="86"/>
+      <c r="O38" s="86"/>
       <c r="Q38" s="2" t="s">
         <v>206</v>
       </c>
@@ -5176,11 +5192,11 @@
       <c r="S38" s="18">
         <v>8021</v>
       </c>
-      <c r="U38" s="81" t="s">
+      <c r="U38" s="83" t="s">
         <v>229</v>
       </c>
-      <c r="V38" s="82"/>
-      <c r="W38" s="83"/>
+      <c r="V38" s="84"/>
+      <c r="W38" s="85"/>
       <c r="Y38" s="2" t="s">
         <v>257</v>
       </c>
@@ -5209,7 +5225,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="39" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E39" s="10" t="s">
         <v>291</v>
       </c>
@@ -5237,11 +5253,11 @@
       <c r="O39" s="18">
         <v>10986</v>
       </c>
-      <c r="Q39" s="84" t="s">
+      <c r="Q39" s="86" t="s">
         <v>137</v>
       </c>
-      <c r="R39" s="84"/>
-      <c r="S39" s="84"/>
+      <c r="R39" s="86"/>
+      <c r="S39" s="86"/>
       <c r="U39" s="2" t="s">
         <v>82</v>
       </c>
@@ -5279,7 +5295,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="40" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E40" s="10" t="s">
         <v>292</v>
       </c>
@@ -5353,7 +5369,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="41" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E41" s="10" t="s">
         <v>293</v>
       </c>
@@ -5390,11 +5406,11 @@
       <c r="S41" s="18">
         <v>11401</v>
       </c>
-      <c r="U41" s="84" t="s">
+      <c r="U41" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="V41" s="84"/>
-      <c r="W41" s="84"/>
+      <c r="V41" s="86"/>
+      <c r="W41" s="86"/>
       <c r="Y41" s="2" t="s">
         <v>259</v>
       </c>
@@ -5423,7 +5439,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="42" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E42" s="10" t="s">
         <v>294</v>
       </c>
@@ -5487,13 +5503,13 @@
       <c r="AE42" s="18">
         <v>8021</v>
       </c>
-      <c r="AG42" s="84" t="s">
+      <c r="AG42" s="86" t="s">
         <v>530</v>
       </c>
-      <c r="AH42" s="84"/>
-      <c r="AI42" s="84"/>
-    </row>
-    <row r="43" spans="5:35" x14ac:dyDescent="0.2">
+      <c r="AH42" s="86"/>
+      <c r="AI42" s="86"/>
+    </row>
+    <row r="43" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E43" s="10" t="s">
         <v>55</v>
       </c>
@@ -5567,7 +5583,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="44" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E44" s="10" t="s">
         <v>295</v>
       </c>
@@ -5613,11 +5629,11 @@
       <c r="W44" s="18">
         <v>7596</v>
       </c>
-      <c r="Y44" s="81" t="s">
+      <c r="Y44" s="83" t="s">
         <v>263</v>
       </c>
-      <c r="Z44" s="82"/>
-      <c r="AA44" s="83"/>
+      <c r="Z44" s="84"/>
+      <c r="AA44" s="85"/>
       <c r="AC44" s="10" t="s">
         <v>497</v>
       </c>
@@ -5637,7 +5653,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="45" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E45" s="10" t="s">
         <v>296</v>
       </c>
@@ -5665,11 +5681,11 @@
       <c r="O45" s="18">
         <v>8272</v>
       </c>
-      <c r="Q45" s="81" t="s">
+      <c r="Q45" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="R45" s="82"/>
-      <c r="S45" s="83"/>
+      <c r="R45" s="84"/>
+      <c r="S45" s="85"/>
       <c r="U45" s="2" t="s">
         <v>7</v>
       </c>
@@ -5700,13 +5716,13 @@
         <f>AE14</f>
         <v>8021</v>
       </c>
-      <c r="AG45" s="81" t="s">
+      <c r="AG45" s="83" t="s">
         <v>532</v>
       </c>
-      <c r="AH45" s="82"/>
-      <c r="AI45" s="83"/>
-    </row>
-    <row r="46" spans="5:35" x14ac:dyDescent="0.2">
+      <c r="AH45" s="84"/>
+      <c r="AI45" s="85"/>
+    </row>
+    <row r="46" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E46" s="10" t="s">
         <v>297</v>
       </c>
@@ -5761,11 +5777,11 @@
       <c r="AA46" s="18">
         <v>14630</v>
       </c>
-      <c r="AC46" s="84" t="s">
+      <c r="AC46" s="86" t="s">
         <v>498</v>
       </c>
-      <c r="AD46" s="84"/>
-      <c r="AE46" s="84"/>
+      <c r="AD46" s="86"/>
+      <c r="AE46" s="86"/>
       <c r="AG46" s="10" t="s">
         <v>533</v>
       </c>
@@ -5776,7 +5792,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="47" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E47" s="10" t="s">
         <v>298</v>
       </c>
@@ -5853,22 +5869,22 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="48" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E48" s="84" t="s">
+    <row r="48" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E48" s="86" t="s">
         <v>7</v>
       </c>
-      <c r="F48" s="84"/>
-      <c r="G48" s="84"/>
-      <c r="I48" s="84" t="s">
+      <c r="F48" s="86"/>
+      <c r="G48" s="86"/>
+      <c r="I48" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="J48" s="84"/>
-      <c r="K48" s="84"/>
-      <c r="M48" s="84" t="s">
+      <c r="J48" s="86"/>
+      <c r="K48" s="86"/>
+      <c r="M48" s="86" t="s">
         <v>125</v>
       </c>
-      <c r="N48" s="84"/>
-      <c r="O48" s="84"/>
+      <c r="N48" s="86"/>
+      <c r="O48" s="86"/>
       <c r="Q48" s="2" t="s">
         <v>140</v>
       </c>
@@ -5878,11 +5894,11 @@
       <c r="S48" s="18">
         <v>14630</v>
       </c>
-      <c r="Y48" s="84" t="s">
+      <c r="Y48" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="Z48" s="84"/>
-      <c r="AA48" s="84"/>
+      <c r="Z48" s="86"/>
+      <c r="AA48" s="86"/>
       <c r="AC48" s="10" t="str">
         <f t="shared" ref="AC48:AE49" si="0">AC9</f>
         <v>Bachelor of Criminal Justice</v>
@@ -5895,13 +5911,13 @@
         <f t="shared" si="0"/>
         <v>14630</v>
       </c>
-      <c r="AG48" s="81" t="s">
+      <c r="AG48" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="AH48" s="82"/>
-      <c r="AI48" s="83"/>
-    </row>
-    <row r="49" spans="5:35" x14ac:dyDescent="0.2">
+      <c r="AH48" s="84"/>
+      <c r="AI48" s="85"/>
+    </row>
+    <row r="49" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E49" s="10" t="s">
         <v>331</v>
       </c>
@@ -5969,7 +5985,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="50" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E50" s="10" t="s">
         <v>332</v>
       </c>
@@ -6024,13 +6040,13 @@
       <c r="AE50" s="18">
         <v>14630</v>
       </c>
-      <c r="AG50" s="81" t="s">
+      <c r="AG50" s="83" t="s">
         <v>535</v>
       </c>
-      <c r="AH50" s="82"/>
-      <c r="AI50" s="83"/>
-    </row>
-    <row r="51" spans="5:35" ht="17" x14ac:dyDescent="0.2">
+      <c r="AH50" s="84"/>
+      <c r="AI50" s="85"/>
+    </row>
+    <row r="51" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E51" s="10" t="s">
         <v>333</v>
       </c>
@@ -6040,11 +6056,11 @@
       <c r="G51" s="14">
         <v>8021</v>
       </c>
-      <c r="I51" s="84" t="s">
+      <c r="I51" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="J51" s="84"/>
-      <c r="K51" s="84"/>
+      <c r="J51" s="86"/>
+      <c r="K51" s="86"/>
       <c r="M51" s="2" t="s">
         <v>76</v>
       </c>
@@ -6063,16 +6079,16 @@
       <c r="S51" s="18">
         <v>14630</v>
       </c>
-      <c r="Y51" s="84" t="s">
+      <c r="Y51" s="86" t="s">
         <v>266</v>
       </c>
-      <c r="Z51" s="84"/>
-      <c r="AA51" s="84"/>
-      <c r="AC51" s="84" t="s">
+      <c r="Z51" s="86"/>
+      <c r="AA51" s="86"/>
+      <c r="AC51" s="86" t="s">
         <v>499</v>
       </c>
-      <c r="AD51" s="84"/>
-      <c r="AE51" s="84"/>
+      <c r="AD51" s="86"/>
+      <c r="AE51" s="86"/>
       <c r="AG51" s="24" t="s">
         <v>67</v>
       </c>
@@ -6083,7 +6099,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="52" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E52" s="10" t="s">
         <v>334</v>
       </c>
@@ -6151,7 +6167,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="53" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E53" s="10" t="s">
         <v>335</v>
       </c>
@@ -6188,11 +6204,11 @@
       <c r="S53" s="18">
         <v>14630</v>
       </c>
-      <c r="Y53" s="84" t="s">
+      <c r="Y53" s="86" t="s">
         <v>267</v>
       </c>
-      <c r="Z53" s="84"/>
-      <c r="AA53" s="84"/>
+      <c r="Z53" s="86"/>
+      <c r="AA53" s="86"/>
       <c r="AC53" s="10" t="s">
         <v>500</v>
       </c>
@@ -6212,7 +6228,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="54" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E54" s="10" t="s">
         <v>336</v>
       </c>
@@ -6277,7 +6293,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="55" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E55" s="10" t="s">
         <v>337</v>
       </c>
@@ -6333,7 +6349,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="56" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E56" s="10" t="s">
         <v>338</v>
       </c>
@@ -6389,7 +6405,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="57" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E57" s="10" t="s">
         <v>339</v>
       </c>
@@ -6436,7 +6452,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="58" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E58" s="10" t="s">
         <v>340</v>
       </c>
@@ -6473,13 +6489,13 @@
       <c r="AE58" s="18">
         <v>8021</v>
       </c>
-      <c r="AG58" s="84" t="s">
+      <c r="AG58" s="86" t="s">
         <v>540</v>
       </c>
-      <c r="AH58" s="84"/>
-      <c r="AI58" s="84"/>
-    </row>
-    <row r="59" spans="5:35" x14ac:dyDescent="0.2">
+      <c r="AH58" s="86"/>
+      <c r="AI58" s="86"/>
+    </row>
+    <row r="59" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E59" s="10" t="s">
         <v>341</v>
       </c>
@@ -6517,7 +6533,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="60" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E60" s="10" t="s">
         <v>342</v>
       </c>
@@ -6536,11 +6552,11 @@
       <c r="O60" s="18">
         <v>10538</v>
       </c>
-      <c r="Q60" s="84" t="s">
+      <c r="Q60" s="86" t="s">
         <v>157</v>
       </c>
-      <c r="R60" s="84"/>
-      <c r="S60" s="84"/>
+      <c r="R60" s="86"/>
+      <c r="S60" s="86"/>
       <c r="AG60" s="10" t="s">
         <v>519</v>
       </c>
@@ -6551,7 +6567,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="61" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E61" s="10" t="s">
         <v>343</v>
       </c>
@@ -6589,7 +6605,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="62" spans="5:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E62" s="10" t="s">
         <v>344</v>
       </c>
@@ -6617,13 +6633,13 @@
       <c r="S62" s="18">
         <v>14630</v>
       </c>
-      <c r="AG62" s="84" t="s">
+      <c r="AG62" s="86" t="s">
         <v>543</v>
       </c>
-      <c r="AH62" s="84"/>
-      <c r="AI62" s="84"/>
-    </row>
-    <row r="63" spans="5:35" x14ac:dyDescent="0.2">
+      <c r="AH62" s="86"/>
+      <c r="AI62" s="86"/>
+    </row>
+    <row r="63" spans="5:35" x14ac:dyDescent="0.25">
       <c r="E63" s="10" t="s">
         <v>55</v>
       </c>
@@ -6661,12 +6677,12 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="64" spans="5:35" x14ac:dyDescent="0.2">
-      <c r="E64" s="84" t="s">
+    <row r="64" spans="5:35" x14ac:dyDescent="0.25">
+      <c r="E64" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="F64" s="84"/>
-      <c r="G64" s="84"/>
+      <c r="F64" s="86"/>
+      <c r="G64" s="86"/>
       <c r="M64" s="2" t="s">
         <v>107</v>
       </c>
@@ -6686,7 +6702,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="65" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="65" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E65" s="10" t="s">
         <v>21</v>
       </c>
@@ -6715,7 +6731,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="66" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="66" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E66" s="10" t="s">
         <v>361</v>
       </c>
@@ -6744,7 +6760,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="67" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E67" s="10" t="s">
         <v>39</v>
       </c>
@@ -6773,7 +6789,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="68" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="68" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E68" s="10" t="s">
         <v>40</v>
       </c>
@@ -6802,7 +6818,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="69" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="69" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E69" s="10" t="s">
         <v>362</v>
       </c>
@@ -6812,13 +6828,13 @@
       <c r="G69" s="14">
         <v>14630</v>
       </c>
-      <c r="Q69" s="84" t="s">
+      <c r="Q69" s="86" t="s">
         <v>153</v>
       </c>
-      <c r="R69" s="84"/>
-      <c r="S69" s="84"/>
-    </row>
-    <row r="70" spans="5:19" x14ac:dyDescent="0.2">
+      <c r="R69" s="86"/>
+      <c r="S69" s="86"/>
+    </row>
+    <row r="70" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E70" s="10" t="s">
         <v>42</v>
       </c>
@@ -6838,12 +6854,12 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="71" spans="5:19" x14ac:dyDescent="0.2">
-      <c r="E71" s="81" t="s">
+    <row r="71" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E71" s="83" t="s">
         <v>244</v>
       </c>
-      <c r="F71" s="82"/>
-      <c r="G71" s="83"/>
+      <c r="F71" s="84"/>
+      <c r="G71" s="85"/>
       <c r="Q71" s="21" t="s">
         <v>103</v>
       </c>
@@ -6854,7 +6870,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="72" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="72" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E72" s="10" t="s">
         <v>369</v>
       </c>
@@ -6864,13 +6880,13 @@
       <c r="G72" s="14">
         <v>8021</v>
       </c>
-      <c r="Q72" s="81" t="s">
+      <c r="Q72" s="83" t="s">
         <v>154</v>
       </c>
-      <c r="R72" s="82"/>
-      <c r="S72" s="83"/>
-    </row>
-    <row r="73" spans="5:19" x14ac:dyDescent="0.2">
+      <c r="R72" s="84"/>
+      <c r="S72" s="85"/>
+    </row>
+    <row r="73" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E73" s="10" t="s">
         <v>370</v>
       </c>
@@ -6890,7 +6906,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="74" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="74" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E74" s="10" t="s">
         <v>371</v>
       </c>
@@ -6910,7 +6926,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="75" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="75" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E75" s="10" t="s">
         <v>372</v>
       </c>
@@ -6930,7 +6946,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="76" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="76" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E76" s="10" t="s">
         <v>373</v>
       </c>
@@ -6950,7 +6966,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="77" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E77" s="10" t="s">
         <v>374</v>
       </c>
@@ -6970,7 +6986,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="78" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="78" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E78" s="10" t="s">
         <v>375</v>
       </c>
@@ -6990,7 +7006,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="79" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="79" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E79" s="10" t="s">
         <v>376</v>
       </c>
@@ -7010,7 +7026,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="80" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E80" s="10" t="s">
         <v>377</v>
       </c>
@@ -7030,7 +7046,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="81" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E81" s="10" t="s">
         <v>378</v>
       </c>
@@ -7040,13 +7056,13 @@
       <c r="G81" s="14">
         <v>8021</v>
       </c>
-      <c r="Q81" s="81" t="s">
+      <c r="Q81" s="83" t="s">
         <v>193</v>
       </c>
-      <c r="R81" s="82"/>
-      <c r="S81" s="83"/>
-    </row>
-    <row r="82" spans="5:19" x14ac:dyDescent="0.2">
+      <c r="R81" s="84"/>
+      <c r="S81" s="85"/>
+    </row>
+    <row r="82" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E82" s="10" t="s">
         <v>379</v>
       </c>
@@ -7066,7 +7082,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="83" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="83" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E83" s="10" t="s">
         <v>380</v>
       </c>
@@ -7086,12 +7102,12 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="84" spans="5:19" x14ac:dyDescent="0.2">
-      <c r="E84" s="81" t="s">
+    <row r="84" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E84" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="F84" s="82"/>
-      <c r="G84" s="83"/>
+      <c r="F84" s="84"/>
+      <c r="G84" s="85"/>
       <c r="Q84" s="2" t="s">
         <v>165</v>
       </c>
@@ -7102,7 +7118,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="85" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E85" s="10" t="s">
         <v>393</v>
       </c>
@@ -7122,7 +7138,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="86" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="86" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E86" s="10" t="s">
         <v>394</v>
       </c>
@@ -7142,7 +7158,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="87" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="87" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E87" s="10" t="s">
         <v>395</v>
       </c>
@@ -7152,13 +7168,13 @@
       <c r="G87" s="14">
         <v>8023</v>
       </c>
-      <c r="Q87" s="84" t="s">
+      <c r="Q87" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="R87" s="84"/>
-      <c r="S87" s="84"/>
-    </row>
-    <row r="88" spans="5:19" x14ac:dyDescent="0.2">
+      <c r="R87" s="86"/>
+      <c r="S87" s="86"/>
+    </row>
+    <row r="88" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E88" s="10" t="s">
         <v>396</v>
       </c>
@@ -7178,7 +7194,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="89" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="89" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E89" s="10" t="s">
         <v>397</v>
       </c>
@@ -7198,7 +7214,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="90" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E90" s="10" t="s">
         <v>398</v>
       </c>
@@ -7218,7 +7234,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="91" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="91" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E91" s="10" t="s">
         <v>399</v>
       </c>
@@ -7238,12 +7254,12 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="92" spans="5:19" x14ac:dyDescent="0.2">
-      <c r="E92" s="81" t="s">
+    <row r="92" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E92" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="F92" s="82"/>
-      <c r="G92" s="83"/>
+      <c r="F92" s="84"/>
+      <c r="G92" s="85"/>
       <c r="Q92" s="2" t="s">
         <v>171</v>
       </c>
@@ -7254,7 +7270,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="93" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="93" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E93" s="10" t="s">
         <v>19</v>
       </c>
@@ -7274,12 +7290,12 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="94" spans="5:19" x14ac:dyDescent="0.2">
-      <c r="E94" s="81" t="s">
+    <row r="94" spans="5:19" x14ac:dyDescent="0.25">
+      <c r="E94" s="83" t="s">
         <v>115</v>
       </c>
-      <c r="F94" s="82"/>
-      <c r="G94" s="83"/>
+      <c r="F94" s="84"/>
+      <c r="G94" s="85"/>
       <c r="Q94" s="2" t="s">
         <v>173</v>
       </c>
@@ -7290,7 +7306,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="95" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E95" s="10" t="s">
         <v>407</v>
       </c>
@@ -7310,7 +7326,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="96" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="96" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E96" s="10" t="s">
         <v>408</v>
       </c>
@@ -7330,7 +7346,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="97" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="97" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E97" s="10" t="s">
         <v>409</v>
       </c>
@@ -7350,7 +7366,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="98" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="98" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E98" s="10" t="s">
         <v>331</v>
       </c>
@@ -7370,7 +7386,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="99" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="99" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E99" s="10" t="s">
         <v>332</v>
       </c>
@@ -7390,7 +7406,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="100" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="100" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E100" s="10" t="s">
         <v>333</v>
       </c>
@@ -7410,7 +7426,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="101" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E101" s="10" t="s">
         <v>334</v>
       </c>
@@ -7420,13 +7436,13 @@
       <c r="G101" s="14">
         <v>8021</v>
       </c>
-      <c r="Q101" s="84" t="s">
+      <c r="Q101" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="R101" s="84"/>
-      <c r="S101" s="84"/>
-    </row>
-    <row r="102" spans="5:19" x14ac:dyDescent="0.2">
+      <c r="R101" s="86"/>
+      <c r="S101" s="86"/>
+    </row>
+    <row r="102" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E102" s="10" t="s">
         <v>410</v>
       </c>
@@ -7446,7 +7462,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="103" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="103" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E103" s="10" t="s">
         <v>411</v>
       </c>
@@ -7466,7 +7482,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="104" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="104" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E104" s="10" t="s">
         <v>370</v>
       </c>
@@ -7477,7 +7493,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="105" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="105" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E105" s="10" t="s">
         <v>412</v>
       </c>
@@ -7488,7 +7504,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="106" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="106" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E106" s="10" t="s">
         <v>413</v>
       </c>
@@ -7499,7 +7515,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="107" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="107" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E107" s="10" t="s">
         <v>414</v>
       </c>
@@ -7510,7 +7526,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="108" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="108" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E108" s="10" t="s">
         <v>415</v>
       </c>
@@ -7521,7 +7537,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="109" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="109" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E109" s="10" t="s">
         <v>416</v>
       </c>
@@ -7532,7 +7548,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="110" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="110" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E110" s="10" t="s">
         <v>417</v>
       </c>
@@ -7543,7 +7559,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="111" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="111" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E111" s="10" t="s">
         <v>418</v>
       </c>
@@ -7554,7 +7570,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="112" spans="5:19" x14ac:dyDescent="0.2">
+    <row r="112" spans="5:19" x14ac:dyDescent="0.25">
       <c r="E112" s="10" t="s">
         <v>419</v>
       </c>
@@ -7565,7 +7581,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="113" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E113" s="10" t="s">
         <v>420</v>
       </c>
@@ -7576,7 +7592,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="114" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E114" s="10" t="s">
         <v>421</v>
       </c>
@@ -7587,7 +7603,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="115" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E115" s="10" t="s">
         <v>335</v>
       </c>
@@ -7598,7 +7614,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="116" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E116" s="10" t="s">
         <v>281</v>
       </c>
@@ -7609,7 +7625,7 @@
         <v>14630</v>
       </c>
     </row>
-    <row r="117" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E117" s="10" t="s">
         <v>422</v>
       </c>
@@ -7620,7 +7636,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="118" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E118" s="10" t="s">
         <v>336</v>
       </c>
@@ -7631,7 +7647,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="119" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E119" s="10" t="s">
         <v>337</v>
       </c>
@@ -7642,7 +7658,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="120" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E120" s="10" t="s">
         <v>338</v>
       </c>
@@ -7653,7 +7669,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="121" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E121" s="10" t="s">
         <v>339</v>
       </c>
@@ -7664,7 +7680,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="122" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E122" s="10" t="s">
         <v>423</v>
       </c>
@@ -7675,7 +7691,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="123" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E123" s="10" t="s">
         <v>424</v>
       </c>
@@ -7686,7 +7702,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="124" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E124" s="10" t="s">
         <v>425</v>
       </c>
@@ -7697,7 +7713,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="125" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E125" s="10" t="s">
         <v>426</v>
       </c>
@@ -7708,7 +7724,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="126" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E126" s="10" t="s">
         <v>376</v>
       </c>
@@ -7719,7 +7735,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="127" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E127" s="10" t="s">
         <v>427</v>
       </c>
@@ -7730,7 +7746,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="128" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E128" s="10" t="s">
         <v>340</v>
       </c>
@@ -7741,7 +7757,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="129" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E129" s="10" t="s">
         <v>341</v>
       </c>
@@ -7752,7 +7768,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="130" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="130" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E130" s="10" t="s">
         <v>342</v>
       </c>
@@ -7763,7 +7779,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="131" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="131" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E131" s="10" t="s">
         <v>343</v>
       </c>
@@ -7774,7 +7790,7 @@
         <v>11401</v>
       </c>
     </row>
-    <row r="132" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="132" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E132" s="10" t="s">
         <v>428</v>
       </c>
@@ -7785,7 +7801,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="133" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="133" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E133" s="10" t="s">
         <v>344</v>
       </c>
@@ -7796,7 +7812,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="134" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="134" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E134" s="10" t="s">
         <v>429</v>
       </c>
@@ -7807,7 +7823,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="135" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="135" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E135" s="10" t="s">
         <v>55</v>
       </c>
@@ -7818,7 +7834,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="136" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="136" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E136" s="10" t="s">
         <v>379</v>
       </c>
@@ -7829,7 +7845,7 @@
         <v>8021</v>
       </c>
     </row>
-    <row r="137" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="137" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E137" s="10" t="s">
         <v>430</v>
       </c>
@@ -7840,7 +7856,7 @@
         <v>11401</v>
       </c>
     </row>
-    <row r="138" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="138" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E138" s="10" t="s">
         <v>431</v>
       </c>
@@ -7851,14 +7867,14 @@
         <v>11401</v>
       </c>
     </row>
-    <row r="139" spans="5:7" x14ac:dyDescent="0.2">
-      <c r="E139" s="81" t="s">
+    <row r="139" spans="5:7" x14ac:dyDescent="0.25">
+      <c r="E139" s="83" t="s">
         <v>551</v>
       </c>
-      <c r="F139" s="82"/>
-      <c r="G139" s="83"/>
-    </row>
-    <row r="140" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="F139" s="84"/>
+      <c r="G139" s="85"/>
+    </row>
+    <row r="140" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E140" s="37" t="s">
         <v>552</v>
       </c>
@@ -7869,7 +7885,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="141" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="141" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E141" s="37" t="s">
         <v>553</v>
       </c>
@@ -7880,7 +7896,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="142" spans="5:7" x14ac:dyDescent="0.2">
+    <row r="142" spans="5:7" x14ac:dyDescent="0.25">
       <c r="E142" s="37" t="s">
         <v>554</v>
       </c>
@@ -7987,74 +8003,74 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C257E56-1218-9941-A2E9-1275C7DD74EE}">
   <dimension ref="B3:AF143"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="60.33203125" style="27" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="60.375" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.125" style="27" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="60.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="60.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="46.5" style="59" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="52.375" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.5" style="70" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="55.83203125" style="59" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.1640625" style="27" customWidth="1"/>
+    <col min="26" max="26" width="55.875" style="59" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.125" style="27" customWidth="1"/>
     <col min="28" max="28" width="20.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="63.83203125" style="59" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.1640625" style="27" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="63.875" style="59" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.125" style="27" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="19.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="D3" s="81" t="s">
+    <row r="3" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="D3" s="83" t="s">
         <v>546</v>
       </c>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="83"/>
-    </row>
-    <row r="4" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="85"/>
+    </row>
+    <row r="4" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B4" s="25"/>
       <c r="C4" s="35"/>
       <c r="D4" s="26"/>
     </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B5" s="113"/>
-      <c r="C5" s="115" t="s">
+    <row r="5" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B5" s="115"/>
+      <c r="C5" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="116"/>
+      <c r="D5" s="118"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="87" t="s">
+      <c r="G5" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="88"/>
-      <c r="K5" s="85" t="s">
+      <c r="H5" s="90"/>
+      <c r="K5" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="L5" s="85"/>
+      <c r="L5" s="87"/>
       <c r="N5" s="19"/>
-      <c r="O5" s="85" t="s">
+      <c r="O5" s="87" t="s">
         <v>126</v>
       </c>
-      <c r="P5" s="85"/>
-    </row>
-    <row r="6" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B6" s="114"/>
+      <c r="P5" s="87"/>
+    </row>
+    <row r="6" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B6" s="116"/>
       <c r="C6" s="28" t="s">
         <v>547</v>
       </c>
@@ -8082,47 +8098,47 @@
         <v>558</v>
       </c>
       <c r="R6" s="27"/>
-      <c r="S6" s="85" t="s">
+      <c r="S6" s="87" t="s">
         <v>209</v>
       </c>
-      <c r="T6" s="85"/>
+      <c r="T6" s="87"/>
       <c r="V6" s="1"/>
-      <c r="W6" s="85" t="s">
+      <c r="W6" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="X6" s="85"/>
+      <c r="X6" s="87"/>
       <c r="Z6" s="27"/>
-      <c r="AA6" s="85" t="s">
+      <c r="AA6" s="87" t="s">
         <v>475</v>
       </c>
-      <c r="AB6" s="85"/>
+      <c r="AB6" s="87"/>
       <c r="AD6" s="27"/>
-      <c r="AE6" s="85" t="s">
+      <c r="AE6" s="87" t="s">
         <v>505</v>
       </c>
-      <c r="AF6" s="85"/>
-    </row>
-    <row r="7" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B7" s="115" t="s">
+      <c r="AF6" s="87"/>
+    </row>
+    <row r="7" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B7" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="117"/>
-      <c r="D7" s="116"/>
-      <c r="F7" s="84" t="s">
+      <c r="C7" s="119"/>
+      <c r="D7" s="118"/>
+      <c r="F7" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="84"/>
-      <c r="H7" s="84"/>
-      <c r="J7" s="104" t="s">
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="J7" s="106" t="s">
         <v>121</v>
       </c>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
-      <c r="N7" s="84" t="s">
+      <c r="K7" s="107"/>
+      <c r="L7" s="108"/>
+      <c r="N7" s="86" t="s">
         <v>186</v>
       </c>
-      <c r="O7" s="84"/>
-      <c r="P7" s="84"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="86"/>
       <c r="R7" s="27"/>
       <c r="S7" s="16" t="s">
         <v>547</v>
@@ -8152,7 +8168,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="8" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B8" s="30" t="s">
         <v>9</v>
       </c>
@@ -8171,7 +8187,7 @@
       <c r="H8" s="4">
         <v>10400</v>
       </c>
-      <c r="J8" s="92" t="s">
+      <c r="J8" s="94" t="s">
         <v>6</v>
       </c>
       <c r="K8" s="43" t="s">
@@ -8189,28 +8205,28 @@
       <c r="P8" s="18">
         <v>10400</v>
       </c>
-      <c r="R8" s="95" t="s">
+      <c r="R8" s="97" t="s">
         <v>210</v>
       </c>
-      <c r="S8" s="95"/>
-      <c r="T8" s="95"/>
-      <c r="V8" s="81" t="s">
+      <c r="S8" s="97"/>
+      <c r="T8" s="97"/>
+      <c r="V8" s="83" t="s">
         <v>235</v>
       </c>
-      <c r="W8" s="82"/>
-      <c r="X8" s="83"/>
-      <c r="Z8" s="95" t="s">
+      <c r="W8" s="84"/>
+      <c r="X8" s="85"/>
+      <c r="Z8" s="97" t="s">
         <v>476</v>
       </c>
-      <c r="AA8" s="95"/>
-      <c r="AB8" s="95"/>
-      <c r="AD8" s="95" t="s">
+      <c r="AA8" s="97"/>
+      <c r="AB8" s="97"/>
+      <c r="AD8" s="97" t="s">
         <v>506</v>
       </c>
-      <c r="AE8" s="95"/>
-      <c r="AF8" s="95"/>
-    </row>
-    <row r="9" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AE8" s="97"/>
+      <c r="AF8" s="97"/>
+    </row>
+    <row r="9" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B9" s="30" t="s">
         <v>10</v>
       </c>
@@ -8229,7 +8245,7 @@
       <c r="H9" s="4">
         <v>10400</v>
       </c>
-      <c r="J9" s="92"/>
+      <c r="J9" s="94"/>
       <c r="K9" s="7" t="s">
         <v>560</v>
       </c>
@@ -8272,7 +8288,7 @@
       <c r="AB9" s="18">
         <v>11440</v>
       </c>
-      <c r="AD9" s="91" t="s">
+      <c r="AD9" s="93" t="s">
         <v>95</v>
       </c>
       <c r="AE9" s="7" t="s">
@@ -8282,7 +8298,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="10" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="30" t="s">
         <v>11</v>
       </c>
@@ -8301,7 +8317,7 @@
       <c r="H10" s="4">
         <v>10400</v>
       </c>
-      <c r="J10" s="93"/>
+      <c r="J10" s="95"/>
       <c r="K10" s="46" t="s">
         <v>561</v>
       </c>
@@ -8317,7 +8333,7 @@
       <c r="P10" s="18">
         <v>10400</v>
       </c>
-      <c r="R10" s="91" t="s">
+      <c r="R10" s="93" t="s">
         <v>6</v>
       </c>
       <c r="S10" s="4" t="s">
@@ -8326,11 +8342,11 @@
       <c r="T10" s="18">
         <v>9620</v>
       </c>
-      <c r="V10" s="84" t="s">
+      <c r="V10" s="86" t="s">
         <v>236</v>
       </c>
-      <c r="W10" s="84"/>
-      <c r="X10" s="84"/>
+      <c r="W10" s="86"/>
+      <c r="X10" s="86"/>
       <c r="Z10" s="39" t="s">
         <v>478</v>
       </c>
@@ -8340,7 +8356,7 @@
       <c r="AB10" s="18">
         <v>11440</v>
       </c>
-      <c r="AD10" s="93"/>
+      <c r="AD10" s="95"/>
       <c r="AE10" s="46" t="s">
         <v>582</v>
       </c>
@@ -8348,7 +8364,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="11" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B11" s="30" t="s">
         <v>12</v>
       </c>
@@ -8367,7 +8383,7 @@
       <c r="H11" s="4">
         <v>9490</v>
       </c>
-      <c r="J11" s="96" t="s">
+      <c r="J11" s="98" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="45" t="s">
@@ -8385,7 +8401,7 @@
       <c r="P11" s="18">
         <v>10400</v>
       </c>
-      <c r="R11" s="92"/>
+      <c r="R11" s="94"/>
       <c r="S11" s="4" t="s">
         <v>567</v>
       </c>
@@ -8420,7 +8436,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="12" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B12" s="30" t="s">
         <v>14</v>
       </c>
@@ -8430,12 +8446,12 @@
       <c r="D12" s="32">
         <v>11400</v>
       </c>
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="82"/>
-      <c r="H12" s="83"/>
-      <c r="J12" s="92"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="85"/>
+      <c r="J12" s="94"/>
       <c r="K12" s="7" t="s">
         <v>560</v>
       </c>
@@ -8451,7 +8467,7 @@
       <c r="P12" s="18">
         <v>10400</v>
       </c>
-      <c r="R12" s="92"/>
+      <c r="R12" s="94"/>
       <c r="S12" s="63" t="s">
         <v>569</v>
       </c>
@@ -8486,7 +8502,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="13" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="30" t="s">
         <v>15</v>
       </c>
@@ -8505,7 +8521,7 @@
       <c r="H13" s="4">
         <v>9490</v>
       </c>
-      <c r="J13" s="93"/>
+      <c r="J13" s="95"/>
       <c r="K13" s="46" t="s">
         <v>561</v>
       </c>
@@ -8521,18 +8537,18 @@
       <c r="P13" s="18">
         <v>10400</v>
       </c>
-      <c r="R13" s="92"/>
+      <c r="R13" s="94"/>
       <c r="S13" s="63" t="s">
         <v>568</v>
       </c>
       <c r="T13" s="56">
         <v>8580</v>
       </c>
-      <c r="V13" s="81" t="s">
+      <c r="V13" s="83" t="s">
         <v>240</v>
       </c>
-      <c r="W13" s="82"/>
-      <c r="X13" s="83"/>
+      <c r="W13" s="84"/>
+      <c r="X13" s="85"/>
       <c r="Z13" s="39" t="s">
         <v>477</v>
       </c>
@@ -8552,7 +8568,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="14" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B14" s="30" t="s">
         <v>16</v>
       </c>
@@ -8571,7 +8587,7 @@
       <c r="H14" s="4">
         <v>10400</v>
       </c>
-      <c r="J14" s="96" t="s">
+      <c r="J14" s="98" t="s">
         <v>66</v>
       </c>
       <c r="K14" s="45" t="s">
@@ -8589,7 +8605,7 @@
       <c r="P14" s="18">
         <v>10400</v>
       </c>
-      <c r="R14" s="92"/>
+      <c r="R14" s="94"/>
       <c r="S14" s="63" t="s">
         <v>571</v>
       </c>
@@ -8614,7 +8630,7 @@
       <c r="AB14" s="18">
         <v>11440</v>
       </c>
-      <c r="AD14" s="91" t="s">
+      <c r="AD14" s="93" t="s">
         <v>508</v>
       </c>
       <c r="AE14" s="7" t="s">
@@ -8624,7 +8640,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="15" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="30" t="s">
         <v>17</v>
       </c>
@@ -8644,7 +8660,7 @@
         <f>H13</f>
         <v>9490</v>
       </c>
-      <c r="J15" s="92"/>
+      <c r="J15" s="94"/>
       <c r="K15" s="43" t="s">
         <v>560</v>
       </c>
@@ -8661,18 +8677,18 @@
       <c r="P15" s="18">
         <v>10400</v>
       </c>
-      <c r="R15" s="93"/>
+      <c r="R15" s="95"/>
       <c r="S15" s="62" t="s">
         <v>570</v>
       </c>
       <c r="T15" s="47">
         <v>0</v>
       </c>
-      <c r="V15" s="81" t="s">
+      <c r="V15" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="W15" s="82"/>
-      <c r="X15" s="83"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="85"/>
       <c r="Z15" s="39" t="s">
         <v>18</v>
       </c>
@@ -8682,7 +8698,7 @@
       <c r="AB15" s="18">
         <v>11440</v>
       </c>
-      <c r="AD15" s="93"/>
+      <c r="AD15" s="95"/>
       <c r="AE15" s="46" t="s">
         <v>582</v>
       </c>
@@ -8690,12 +8706,12 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="16" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="118" t="s">
+    <row r="16" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="120" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="119"/>
-      <c r="D16" s="120"/>
+      <c r="C16" s="121"/>
+      <c r="D16" s="122"/>
       <c r="F16" s="10" t="s">
         <v>31</v>
       </c>
@@ -8705,7 +8721,7 @@
       <c r="H16" s="4">
         <v>9490</v>
       </c>
-      <c r="J16" s="93"/>
+      <c r="J16" s="95"/>
       <c r="K16" s="50" t="s">
         <v>561</v>
       </c>
@@ -8748,13 +8764,13 @@
       <c r="AB16" s="18">
         <v>11440</v>
       </c>
-      <c r="AD16" s="100" t="s">
+      <c r="AD16" s="102" t="s">
         <v>509</v>
       </c>
-      <c r="AE16" s="101"/>
-      <c r="AF16" s="102"/>
-    </row>
-    <row r="17" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AE16" s="103"/>
+      <c r="AF16" s="104"/>
+    </row>
+    <row r="17" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B17" s="30" t="s">
         <v>270</v>
       </c>
@@ -8764,12 +8780,12 @@
       <c r="D17" s="33">
         <v>11400</v>
       </c>
-      <c r="F17" s="84" t="s">
+      <c r="F17" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="84"/>
-      <c r="H17" s="84"/>
-      <c r="J17" s="92" t="s">
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="J17" s="94" t="s">
         <v>72</v>
       </c>
       <c r="K17" s="43" t="s">
@@ -8814,7 +8830,7 @@
       <c r="AB17" s="18">
         <v>11440</v>
       </c>
-      <c r="AD17" s="91" t="s">
+      <c r="AD17" s="93" t="s">
         <v>6</v>
       </c>
       <c r="AE17" s="7" t="s">
@@ -8824,7 +8840,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="18" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="30" t="s">
         <v>271</v>
       </c>
@@ -8843,18 +8859,18 @@
       <c r="H18" s="4">
         <v>10400</v>
       </c>
-      <c r="J18" s="93"/>
+      <c r="J18" s="95"/>
       <c r="K18" s="46" t="s">
         <v>561</v>
       </c>
       <c r="L18" s="47">
         <v>0</v>
       </c>
-      <c r="N18" s="81" t="s">
+      <c r="N18" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="O18" s="82"/>
-      <c r="P18" s="83"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="85"/>
       <c r="R18" s="39" t="s">
         <v>214</v>
       </c>
@@ -8873,7 +8889,7 @@
       <c r="X18" s="18">
         <v>15210</v>
       </c>
-      <c r="Z18" s="91" t="s">
+      <c r="Z18" s="93" t="s">
         <v>481</v>
       </c>
       <c r="AA18" s="7" t="s">
@@ -8882,7 +8898,7 @@
       <c r="AB18" s="18">
         <v>11440</v>
       </c>
-      <c r="AD18" s="92"/>
+      <c r="AD18" s="94"/>
       <c r="AE18" s="7" t="s">
         <v>573</v>
       </c>
@@ -8890,7 +8906,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="19" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="30" t="s">
         <v>272</v>
       </c>
@@ -8909,7 +8925,7 @@
       <c r="H19" s="4">
         <v>9490</v>
       </c>
-      <c r="J19" s="96" t="s">
+      <c r="J19" s="98" t="s">
         <v>73</v>
       </c>
       <c r="K19" s="45" t="s">
@@ -8945,14 +8961,14 @@
       <c r="X19" s="18">
         <v>15210</v>
       </c>
-      <c r="Z19" s="93"/>
+      <c r="Z19" s="95"/>
       <c r="AA19" s="46" t="s">
         <v>570</v>
       </c>
       <c r="AB19" s="47">
         <v>0</v>
       </c>
-      <c r="AD19" s="92"/>
+      <c r="AD19" s="94"/>
       <c r="AE19" s="7" t="s">
         <v>582</v>
       </c>
@@ -8960,7 +8976,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="20" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="34" t="s">
         <v>273</v>
       </c>
@@ -8979,7 +8995,7 @@
       <c r="H20" s="4">
         <v>10400</v>
       </c>
-      <c r="J20" s="92"/>
+      <c r="J20" s="94"/>
       <c r="K20" s="7" t="s">
         <v>560</v>
       </c>
@@ -9013,12 +9029,12 @@
       <c r="X20" s="18">
         <v>15210</v>
       </c>
-      <c r="Z20" s="103" t="s">
+      <c r="Z20" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="AA20" s="103"/>
-      <c r="AB20" s="103"/>
-      <c r="AD20" s="93"/>
+      <c r="AA20" s="105"/>
+      <c r="AB20" s="105"/>
+      <c r="AD20" s="95"/>
       <c r="AE20" s="46" t="s">
         <v>570</v>
       </c>
@@ -9026,7 +9042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="30" t="s">
         <v>274</v>
       </c>
@@ -9045,7 +9061,7 @@
       <c r="H21" s="4">
         <v>10400</v>
       </c>
-      <c r="J21" s="93"/>
+      <c r="J21" s="95"/>
       <c r="K21" s="46" t="s">
         <v>561</v>
       </c>
@@ -9061,17 +9077,17 @@
       <c r="P21" s="18">
         <v>10400</v>
       </c>
-      <c r="R21" s="95" t="s">
+      <c r="R21" s="97" t="s">
         <v>217</v>
       </c>
-      <c r="S21" s="95"/>
-      <c r="T21" s="95"/>
-      <c r="V21" s="84" t="s">
+      <c r="S21" s="97"/>
+      <c r="T21" s="97"/>
+      <c r="V21" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="W21" s="84"/>
-      <c r="X21" s="84"/>
-      <c r="Z21" s="91" t="s">
+      <c r="W21" s="86"/>
+      <c r="X21" s="86"/>
+      <c r="Z21" s="93" t="s">
         <v>68</v>
       </c>
       <c r="AA21" s="74" t="s">
@@ -9080,7 +9096,7 @@
       <c r="AB21" s="18">
         <v>10400</v>
       </c>
-      <c r="AD21" s="96" t="s">
+      <c r="AD21" s="98" t="s">
         <v>510</v>
       </c>
       <c r="AE21" s="45" t="s">
@@ -9090,7 +9106,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="22" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="30" t="s">
         <v>275</v>
       </c>
@@ -9109,7 +9125,7 @@
       <c r="H22" s="4">
         <v>9360</v>
       </c>
-      <c r="J22" s="96" t="s">
+      <c r="J22" s="98" t="s">
         <v>74</v>
       </c>
       <c r="K22" s="45" t="s">
@@ -9127,7 +9143,7 @@
       <c r="P22" s="18">
         <v>9620</v>
       </c>
-      <c r="R22" s="91" t="s">
+      <c r="R22" s="93" t="s">
         <v>218</v>
       </c>
       <c r="S22" s="4" t="s">
@@ -9145,14 +9161,14 @@
       <c r="X22" s="18">
         <v>15210</v>
       </c>
-      <c r="Z22" s="93"/>
+      <c r="Z22" s="95"/>
       <c r="AA22" s="46" t="s">
         <v>578</v>
       </c>
       <c r="AB22" s="47">
         <v>11440</v>
       </c>
-      <c r="AD22" s="92"/>
+      <c r="AD22" s="94"/>
       <c r="AE22" s="7" t="s">
         <v>573</v>
       </c>
@@ -9160,7 +9176,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="23" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="30" t="s">
         <v>276</v>
       </c>
@@ -9179,7 +9195,7 @@
       <c r="H23" s="4">
         <v>9490</v>
       </c>
-      <c r="J23" s="92"/>
+      <c r="J23" s="94"/>
       <c r="K23" s="7" t="s">
         <v>560</v>
       </c>
@@ -9195,7 +9211,7 @@
       <c r="P23" s="18">
         <v>10400</v>
       </c>
-      <c r="R23" s="92"/>
+      <c r="R23" s="94"/>
       <c r="S23" s="4" t="s">
         <v>568</v>
       </c>
@@ -9211,12 +9227,12 @@
       <c r="X23" s="18">
         <v>15210</v>
       </c>
-      <c r="Z23" s="100" t="s">
+      <c r="Z23" s="102" t="s">
         <v>482</v>
       </c>
-      <c r="AA23" s="101"/>
-      <c r="AB23" s="102"/>
-      <c r="AD23" s="93"/>
+      <c r="AA23" s="103"/>
+      <c r="AB23" s="104"/>
+      <c r="AD23" s="95"/>
       <c r="AE23" s="46" t="s">
         <v>582</v>
       </c>
@@ -9224,7 +9240,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="24" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="30" t="s">
         <v>277</v>
       </c>
@@ -9243,7 +9259,7 @@
       <c r="H24" s="4">
         <v>9490</v>
       </c>
-      <c r="J24" s="93"/>
+      <c r="J24" s="95"/>
       <c r="K24" s="46" t="s">
         <v>561</v>
       </c>
@@ -9259,7 +9275,7 @@
       <c r="P24" s="18">
         <v>10400</v>
       </c>
-      <c r="R24" s="92"/>
+      <c r="R24" s="94"/>
       <c r="S24" s="4" t="s">
         <v>572</v>
       </c>
@@ -9284,7 +9300,7 @@
       <c r="AB24" s="18">
         <v>11440</v>
       </c>
-      <c r="AD24" s="96" t="s">
+      <c r="AD24" s="98" t="s">
         <v>511</v>
       </c>
       <c r="AE24" s="45" t="s">
@@ -9294,7 +9310,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="25" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="30" t="s">
         <v>28</v>
       </c>
@@ -9313,7 +9329,7 @@
       <c r="H25" s="4">
         <v>9490</v>
       </c>
-      <c r="J25" s="96" t="s">
+      <c r="J25" s="98" t="s">
         <v>75</v>
       </c>
       <c r="K25" s="45" t="s">
@@ -9331,7 +9347,7 @@
       <c r="P25" s="18">
         <v>10400</v>
       </c>
-      <c r="R25" s="93"/>
+      <c r="R25" s="95"/>
       <c r="S25" s="62" t="s">
         <v>570</v>
       </c>
@@ -9356,7 +9372,7 @@
       <c r="AB25" s="18">
         <v>11440</v>
       </c>
-      <c r="AD25" s="92"/>
+      <c r="AD25" s="94"/>
       <c r="AE25" s="7" t="s">
         <v>573</v>
       </c>
@@ -9364,7 +9380,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="26" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B26" s="30" t="s">
         <v>39</v>
       </c>
@@ -9383,7 +9399,7 @@
       <c r="H26" s="4">
         <v>10400</v>
       </c>
-      <c r="J26" s="92"/>
+      <c r="J26" s="94"/>
       <c r="K26" s="7" t="s">
         <v>560</v>
       </c>
@@ -9399,7 +9415,7 @@
       <c r="P26" s="18">
         <v>10400</v>
       </c>
-      <c r="R26" s="96" t="s">
+      <c r="R26" s="98" t="s">
         <v>68</v>
       </c>
       <c r="S26" s="64" t="s">
@@ -9408,17 +9424,17 @@
       <c r="T26" s="48">
         <v>9620</v>
       </c>
-      <c r="V26" s="84" t="s">
+      <c r="V26" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="W26" s="84"/>
-      <c r="X26" s="84"/>
-      <c r="Z26" s="95" t="s">
+      <c r="W26" s="86"/>
+      <c r="X26" s="86"/>
+      <c r="Z26" s="97" t="s">
         <v>43</v>
       </c>
-      <c r="AA26" s="95"/>
-      <c r="AB26" s="95"/>
-      <c r="AD26" s="92"/>
+      <c r="AA26" s="97"/>
+      <c r="AB26" s="97"/>
+      <c r="AD26" s="94"/>
       <c r="AE26" s="7" t="s">
         <v>582</v>
       </c>
@@ -9426,7 +9442,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="27" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="30" t="s">
         <v>278</v>
       </c>
@@ -9445,7 +9461,7 @@
       <c r="H27" s="4">
         <v>10400</v>
       </c>
-      <c r="J27" s="93"/>
+      <c r="J27" s="95"/>
       <c r="K27" s="46" t="s">
         <v>561</v>
       </c>
@@ -9461,7 +9477,7 @@
       <c r="P27" s="18">
         <v>10400</v>
       </c>
-      <c r="R27" s="92"/>
+      <c r="R27" s="94"/>
       <c r="S27" s="4" t="s">
         <v>568</v>
       </c>
@@ -9486,7 +9502,7 @@
       <c r="AB27" s="18">
         <v>11440</v>
       </c>
-      <c r="AD27" s="93"/>
+      <c r="AD27" s="95"/>
       <c r="AE27" s="46" t="s">
         <v>570</v>
       </c>
@@ -9494,7 +9510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B28" s="30" t="s">
         <v>279</v>
       </c>
@@ -9504,11 +9520,11 @@
       <c r="D28" s="33">
         <v>11400</v>
       </c>
-      <c r="F28" s="84" t="s">
+      <c r="F28" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="G28" s="84"/>
-      <c r="H28" s="84"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
       <c r="J28" s="41" t="s">
         <v>78</v>
       </c>
@@ -9527,7 +9543,7 @@
       <c r="P28" s="18">
         <v>10400</v>
       </c>
-      <c r="R28" s="92"/>
+      <c r="R28" s="94"/>
       <c r="S28" s="4" t="s">
         <v>572</v>
       </c>
@@ -9552,7 +9568,7 @@
       <c r="AB28" s="18">
         <v>11440</v>
       </c>
-      <c r="AD28" s="96" t="s">
+      <c r="AD28" s="98" t="s">
         <v>512</v>
       </c>
       <c r="AE28" s="45" t="s">
@@ -9562,7 +9578,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="29" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="30" t="s">
         <v>280</v>
       </c>
@@ -9590,23 +9606,23 @@
       <c r="L29" s="44">
         <v>10660</v>
       </c>
-      <c r="N29" s="84" t="s">
+      <c r="N29" s="86" t="s">
         <v>161</v>
       </c>
-      <c r="O29" s="84"/>
-      <c r="P29" s="84"/>
-      <c r="R29" s="93"/>
+      <c r="O29" s="86"/>
+      <c r="P29" s="86"/>
+      <c r="R29" s="95"/>
       <c r="S29" s="62" t="s">
         <v>570</v>
       </c>
       <c r="T29" s="47">
         <v>0</v>
       </c>
-      <c r="V29" s="84" t="s">
+      <c r="V29" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="W29" s="84"/>
-      <c r="X29" s="84"/>
+      <c r="W29" s="86"/>
+      <c r="X29" s="86"/>
       <c r="Z29" s="39" t="s">
         <v>484</v>
       </c>
@@ -9616,7 +9632,7 @@
       <c r="AB29" s="18">
         <v>11440</v>
       </c>
-      <c r="AD29" s="92"/>
+      <c r="AD29" s="94"/>
       <c r="AE29" s="7" t="s">
         <v>573</v>
       </c>
@@ -9624,7 +9640,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="30" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B30" s="30" t="s">
         <v>281</v>
       </c>
@@ -9634,11 +9650,11 @@
       <c r="D30" s="33">
         <v>11400</v>
       </c>
-      <c r="F30" s="84" t="s">
+      <c r="F30" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="84"/>
-      <c r="H30" s="84"/>
+      <c r="G30" s="86"/>
+      <c r="H30" s="86"/>
       <c r="J30" s="41" t="s">
         <v>80</v>
       </c>
@@ -9675,7 +9691,7 @@
       <c r="X30" s="18">
         <v>15210</v>
       </c>
-      <c r="Z30" s="91" t="s">
+      <c r="Z30" s="93" t="s">
         <v>485</v>
       </c>
       <c r="AA30" s="7" t="s">
@@ -9684,7 +9700,7 @@
       <c r="AB30" s="18">
         <v>11440</v>
       </c>
-      <c r="AD30" s="92"/>
+      <c r="AD30" s="94"/>
       <c r="AE30" s="7" t="s">
         <v>582</v>
       </c>
@@ -9692,7 +9708,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="31" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B31" s="30" t="s">
         <v>282</v>
       </c>
@@ -9747,14 +9763,14 @@
       <c r="X31" s="18">
         <v>15210</v>
       </c>
-      <c r="Z31" s="93"/>
+      <c r="Z31" s="95"/>
       <c r="AA31" s="46" t="s">
         <v>580</v>
       </c>
       <c r="AB31" s="47">
         <v>8060</v>
       </c>
-      <c r="AD31" s="93"/>
+      <c r="AD31" s="95"/>
       <c r="AE31" s="46" t="s">
         <v>570</v>
       </c>
@@ -9762,7 +9778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B32" s="30" t="s">
         <v>283</v>
       </c>
@@ -9772,12 +9788,12 @@
       <c r="D32" s="33">
         <v>11400</v>
       </c>
-      <c r="F32" s="84" t="s">
+      <c r="F32" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="84"/>
-      <c r="H32" s="84"/>
-      <c r="J32" s="96" t="s">
+      <c r="G32" s="86"/>
+      <c r="H32" s="86"/>
+      <c r="J32" s="98" t="s">
         <v>82</v>
       </c>
       <c r="K32" s="45" t="s">
@@ -9795,11 +9811,11 @@
       <c r="P32" s="18">
         <v>10400</v>
       </c>
-      <c r="R32" s="95" t="s">
+      <c r="R32" s="97" t="s">
         <v>219</v>
       </c>
-      <c r="S32" s="95"/>
-      <c r="T32" s="95"/>
+      <c r="S32" s="97"/>
+      <c r="T32" s="97"/>
       <c r="V32" s="10" t="s">
         <v>250</v>
       </c>
@@ -9818,13 +9834,13 @@
       <c r="AB32" s="44">
         <v>11440</v>
       </c>
-      <c r="AD32" s="100" t="s">
+      <c r="AD32" s="102" t="s">
         <v>37</v>
       </c>
-      <c r="AE32" s="101"/>
-      <c r="AF32" s="102"/>
-    </row>
-    <row r="33" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+      <c r="AE32" s="103"/>
+      <c r="AF32" s="104"/>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B33" s="30" t="s">
         <v>284</v>
       </c>
@@ -9843,7 +9859,7 @@
       <c r="H33" s="18">
         <v>9490</v>
       </c>
-      <c r="J33" s="92"/>
+      <c r="J33" s="94"/>
       <c r="K33" s="7" t="s">
         <v>560</v>
       </c>
@@ -9859,7 +9875,7 @@
       <c r="P33" s="18">
         <v>10400</v>
       </c>
-      <c r="R33" s="91" t="s">
+      <c r="R33" s="93" t="s">
         <v>89</v>
       </c>
       <c r="S33" s="4" t="s">
@@ -9877,11 +9893,11 @@
       <c r="X33" s="18">
         <v>15210</v>
       </c>
-      <c r="Z33" s="95" t="s">
+      <c r="Z33" s="97" t="s">
         <v>487</v>
       </c>
-      <c r="AA33" s="95"/>
-      <c r="AB33" s="95"/>
+      <c r="AA33" s="97"/>
+      <c r="AB33" s="97"/>
       <c r="AD33" s="39" t="s">
         <v>513</v>
       </c>
@@ -9892,7 +9908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B34" s="30" t="s">
         <v>285</v>
       </c>
@@ -9911,7 +9927,7 @@
       <c r="H34" s="18">
         <v>9490</v>
       </c>
-      <c r="J34" s="92"/>
+      <c r="J34" s="94"/>
       <c r="K34" s="55" t="s">
         <v>561</v>
       </c>
@@ -9927,7 +9943,7 @@
       <c r="P34" s="18">
         <v>10400</v>
       </c>
-      <c r="R34" s="94"/>
+      <c r="R34" s="96"/>
       <c r="S34" s="4" t="s">
         <v>571</v>
       </c>
@@ -9952,7 +9968,7 @@
       <c r="AB34" s="76">
         <v>11440</v>
       </c>
-      <c r="AD34" s="91" t="s">
+      <c r="AD34" s="93" t="s">
         <v>68</v>
       </c>
       <c r="AE34" s="7" t="s">
@@ -9962,7 +9978,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="35" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B35" s="30" t="s">
         <v>286</v>
       </c>
@@ -9972,11 +9988,11 @@
       <c r="D35" s="33">
         <v>11400</v>
       </c>
-      <c r="F35" s="84" t="s">
+      <c r="F35" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="84"/>
-      <c r="H35" s="84"/>
+      <c r="G35" s="86"/>
+      <c r="H35" s="86"/>
       <c r="J35" s="39" t="s">
         <v>84</v>
       </c>
@@ -9995,7 +10011,7 @@
       <c r="P35" s="18">
         <v>14040</v>
       </c>
-      <c r="R35" s="91" t="s">
+      <c r="R35" s="93" t="s">
         <v>90</v>
       </c>
       <c r="S35" s="4" t="s">
@@ -10022,7 +10038,7 @@
       <c r="AB35" s="76">
         <v>11440</v>
       </c>
-      <c r="AD35" s="92"/>
+      <c r="AD35" s="94"/>
       <c r="AE35" s="7" t="s">
         <v>573</v>
       </c>
@@ -10030,7 +10046,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="36" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B36" s="30" t="s">
         <v>287</v>
       </c>
@@ -10067,7 +10083,7 @@
       <c r="P36" s="18">
         <v>14040</v>
       </c>
-      <c r="R36" s="92"/>
+      <c r="R36" s="94"/>
       <c r="S36" s="63" t="s">
         <v>569</v>
       </c>
@@ -10092,7 +10108,7 @@
       <c r="AB36" s="76">
         <v>11440</v>
       </c>
-      <c r="AD36" s="92"/>
+      <c r="AD36" s="94"/>
       <c r="AE36" s="7" t="s">
         <v>582</v>
       </c>
@@ -10100,7 +10116,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="30" t="s">
         <v>288</v>
       </c>
@@ -10110,12 +10126,12 @@
       <c r="D37" s="33">
         <v>11400</v>
       </c>
-      <c r="F37" s="84" t="s">
+      <c r="F37" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="G37" s="84"/>
-      <c r="H37" s="84"/>
-      <c r="J37" s="91" t="s">
+      <c r="G37" s="86"/>
+      <c r="H37" s="86"/>
+      <c r="J37" s="93" t="s">
         <v>87</v>
       </c>
       <c r="K37" s="7" t="s">
@@ -10133,7 +10149,7 @@
       <c r="P37" s="18">
         <v>14040</v>
       </c>
-      <c r="R37" s="93"/>
+      <c r="R37" s="95"/>
       <c r="S37" s="62" t="s">
         <v>568</v>
       </c>
@@ -10158,7 +10174,7 @@
       <c r="AB37" s="76">
         <v>11440</v>
       </c>
-      <c r="AD37" s="93"/>
+      <c r="AD37" s="95"/>
       <c r="AE37" s="46" t="s">
         <v>570</v>
       </c>
@@ -10166,7 +10182,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="38" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="30" t="s">
         <v>289</v>
       </c>
@@ -10185,7 +10201,7 @@
       <c r="H38" s="18">
         <v>9490</v>
       </c>
-      <c r="J38" s="93"/>
+      <c r="J38" s="95"/>
       <c r="K38" s="46" t="s">
         <v>562</v>
       </c>
@@ -10201,7 +10217,7 @@
       <c r="P38" s="18">
         <v>10400</v>
       </c>
-      <c r="R38" s="96" t="s">
+      <c r="R38" s="98" t="s">
         <v>220</v>
       </c>
       <c r="S38" s="64" t="s">
@@ -10228,7 +10244,7 @@
       <c r="AB38" s="76">
         <v>11440</v>
       </c>
-      <c r="AD38" s="96" t="s">
+      <c r="AD38" s="98" t="s">
         <v>514</v>
       </c>
       <c r="AE38" s="45" t="s">
@@ -10238,7 +10254,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B39" s="30" t="s">
         <v>290</v>
       </c>
@@ -10275,18 +10291,18 @@
       <c r="P39" s="18">
         <v>14040</v>
       </c>
-      <c r="R39" s="92"/>
+      <c r="R39" s="94"/>
       <c r="S39" s="63" t="s">
         <v>569</v>
       </c>
       <c r="T39" s="56">
         <v>7540</v>
       </c>
-      <c r="V39" s="84" t="s">
+      <c r="V39" s="86" t="s">
         <v>261</v>
       </c>
-      <c r="W39" s="84"/>
-      <c r="X39" s="84"/>
+      <c r="W39" s="86"/>
+      <c r="X39" s="86"/>
       <c r="Z39" s="39" t="s">
         <v>174</v>
       </c>
@@ -10296,7 +10312,7 @@
       <c r="AB39" s="76">
         <v>11440</v>
       </c>
-      <c r="AD39" s="92"/>
+      <c r="AD39" s="94"/>
       <c r="AE39" s="7" t="s">
         <v>573</v>
       </c>
@@ -10304,7 +10320,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="40" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="30" t="s">
         <v>291</v>
       </c>
@@ -10323,7 +10339,7 @@
       <c r="H40" s="18">
         <v>9490</v>
       </c>
-      <c r="J40" s="92" t="s">
+      <c r="J40" s="94" t="s">
         <v>104</v>
       </c>
       <c r="K40" s="53" t="s">
@@ -10332,12 +10348,12 @@
       <c r="L40" s="54">
         <v>10660</v>
       </c>
-      <c r="N40" s="84" t="s">
+      <c r="N40" s="86" t="s">
         <v>137</v>
       </c>
-      <c r="O40" s="84"/>
-      <c r="P40" s="84"/>
-      <c r="R40" s="93"/>
+      <c r="O40" s="86"/>
+      <c r="P40" s="86"/>
+      <c r="R40" s="95"/>
       <c r="S40" s="62" t="s">
         <v>568</v>
       </c>
@@ -10362,7 +10378,7 @@
       <c r="AB40" s="76">
         <v>11440</v>
       </c>
-      <c r="AD40" s="92"/>
+      <c r="AD40" s="94"/>
       <c r="AE40" s="7" t="s">
         <v>582</v>
       </c>
@@ -10370,7 +10386,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="41" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B41" s="30" t="s">
         <v>292</v>
       </c>
@@ -10389,7 +10405,7 @@
       <c r="H41" s="18">
         <v>9490</v>
       </c>
-      <c r="J41" s="92"/>
+      <c r="J41" s="94"/>
       <c r="K41" s="53" t="s">
         <v>562</v>
       </c>
@@ -10423,12 +10439,12 @@
       <c r="X41" s="18">
         <v>15210</v>
       </c>
-      <c r="Z41" s="95" t="s">
+      <c r="Z41" s="97" t="s">
         <v>493</v>
       </c>
-      <c r="AA41" s="95"/>
-      <c r="AB41" s="95"/>
-      <c r="AD41" s="93"/>
+      <c r="AA41" s="97"/>
+      <c r="AB41" s="97"/>
+      <c r="AD41" s="95"/>
       <c r="AE41" s="46" t="s">
         <v>570</v>
       </c>
@@ -10436,7 +10452,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="42" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B42" s="30" t="s">
         <v>293</v>
       </c>
@@ -10455,7 +10471,7 @@
       <c r="H42" s="18">
         <v>9360</v>
       </c>
-      <c r="J42" s="92"/>
+      <c r="J42" s="94"/>
       <c r="K42" s="53" t="s">
         <v>561</v>
       </c>
@@ -10471,11 +10487,11 @@
       <c r="P42" s="18">
         <v>9620</v>
       </c>
-      <c r="R42" s="95" t="s">
+      <c r="R42" s="97" t="s">
         <v>120</v>
       </c>
-      <c r="S42" s="95"/>
-      <c r="T42" s="95"/>
+      <c r="S42" s="97"/>
+      <c r="T42" s="97"/>
       <c r="V42" s="10" t="s">
         <v>258</v>
       </c>
@@ -10485,7 +10501,7 @@
       <c r="X42" s="18">
         <v>15210</v>
       </c>
-      <c r="Z42" s="91" t="s">
+      <c r="Z42" s="93" t="s">
         <v>494</v>
       </c>
       <c r="AA42" s="7" t="s">
@@ -10494,7 +10510,7 @@
       <c r="AB42" s="18">
         <v>11440</v>
       </c>
-      <c r="AD42" s="97" t="s">
+      <c r="AD42" s="99" t="s">
         <v>515</v>
       </c>
       <c r="AE42" s="45" t="s">
@@ -10504,7 +10520,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="43" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="30" t="s">
         <v>294</v>
       </c>
@@ -10523,11 +10539,11 @@
       <c r="H43" s="18">
         <v>9360</v>
       </c>
-      <c r="J43" s="110" t="s">
+      <c r="J43" s="112" t="s">
         <v>122</v>
       </c>
-      <c r="K43" s="111"/>
-      <c r="L43" s="112"/>
+      <c r="K43" s="113"/>
+      <c r="L43" s="114"/>
       <c r="N43" s="10" t="s">
         <v>110</v>
       </c>
@@ -10555,14 +10571,14 @@
       <c r="X43" s="18">
         <v>15210</v>
       </c>
-      <c r="Z43" s="93"/>
+      <c r="Z43" s="95"/>
       <c r="AA43" s="46" t="s">
         <v>579</v>
       </c>
       <c r="AB43" s="47">
         <v>8580</v>
       </c>
-      <c r="AD43" s="98"/>
+      <c r="AD43" s="100"/>
       <c r="AE43" s="7" t="s">
         <v>573</v>
       </c>
@@ -10570,7 +10586,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="44" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B44" s="30" t="s">
         <v>55</v>
       </c>
@@ -10589,7 +10605,7 @@
       <c r="H44" s="18">
         <v>9360</v>
       </c>
-      <c r="J44" s="92" t="s">
+      <c r="J44" s="94" t="s">
         <v>88</v>
       </c>
       <c r="K44" s="43" t="s">
@@ -10607,7 +10623,7 @@
       <c r="P44" s="18">
         <v>9620</v>
       </c>
-      <c r="R44" s="91" t="s">
+      <c r="R44" s="93" t="s">
         <v>99</v>
       </c>
       <c r="S44" s="4" t="s">
@@ -10634,7 +10650,7 @@
       <c r="AB44" s="44">
         <v>8580</v>
       </c>
-      <c r="AD44" s="98"/>
+      <c r="AD44" s="100"/>
       <c r="AE44" s="7" t="s">
         <v>582</v>
       </c>
@@ -10642,7 +10658,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="45" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B45" s="30" t="s">
         <v>295</v>
       </c>
@@ -10661,7 +10677,7 @@
       <c r="H45" s="18">
         <v>9490</v>
       </c>
-      <c r="J45" s="93"/>
+      <c r="J45" s="95"/>
       <c r="K45" s="46" t="s">
         <v>561</v>
       </c>
@@ -10677,7 +10693,7 @@
       <c r="P45" s="18">
         <v>9620</v>
       </c>
-      <c r="R45" s="93"/>
+      <c r="R45" s="95"/>
       <c r="S45" s="62" t="s">
         <v>568</v>
       </c>
@@ -10693,7 +10709,7 @@
       <c r="X45" s="18">
         <v>15210</v>
       </c>
-      <c r="Z45" s="91" t="s">
+      <c r="Z45" s="93" t="s">
         <v>7</v>
       </c>
       <c r="AA45" s="7" t="s">
@@ -10702,7 +10718,7 @@
       <c r="AB45" s="18">
         <v>11440</v>
       </c>
-      <c r="AD45" s="99"/>
+      <c r="AD45" s="101"/>
       <c r="AE45" s="46" t="s">
         <v>570</v>
       </c>
@@ -10710,7 +10726,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="46" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="30" t="s">
         <v>296</v>
       </c>
@@ -10729,7 +10745,7 @@
       <c r="H46" s="18">
         <v>10400</v>
       </c>
-      <c r="J46" s="96" t="s">
+      <c r="J46" s="98" t="s">
         <v>89</v>
       </c>
       <c r="K46" s="7" t="s">
@@ -10738,12 +10754,12 @@
       <c r="L46" s="48">
         <v>10660</v>
       </c>
-      <c r="N46" s="81" t="s">
+      <c r="N46" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="O46" s="82"/>
-      <c r="P46" s="83"/>
-      <c r="R46" s="96" t="s">
+      <c r="O46" s="84"/>
+      <c r="P46" s="85"/>
+      <c r="R46" s="98" t="s">
         <v>110</v>
       </c>
       <c r="S46" s="64" t="s">
@@ -10752,25 +10768,25 @@
       <c r="T46" s="48">
         <v>9620</v>
       </c>
-      <c r="V46" s="81" t="s">
+      <c r="V46" s="83" t="s">
         <v>263</v>
       </c>
-      <c r="W46" s="82"/>
-      <c r="X46" s="83"/>
-      <c r="Z46" s="93"/>
+      <c r="W46" s="84"/>
+      <c r="X46" s="85"/>
+      <c r="Z46" s="95"/>
       <c r="AA46" s="46" t="s">
         <v>579</v>
       </c>
       <c r="AB46" s="47">
         <v>8580</v>
       </c>
-      <c r="AD46" s="100" t="s">
+      <c r="AD46" s="102" t="s">
         <v>516</v>
       </c>
-      <c r="AE46" s="101"/>
-      <c r="AF46" s="102"/>
-    </row>
-    <row r="47" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AE46" s="103"/>
+      <c r="AF46" s="104"/>
+    </row>
+    <row r="47" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="30" t="s">
         <v>297</v>
       </c>
@@ -10789,7 +10805,7 @@
       <c r="H47" s="18">
         <v>9490</v>
       </c>
-      <c r="J47" s="93"/>
+      <c r="J47" s="95"/>
       <c r="K47" s="46" t="s">
         <v>561</v>
       </c>
@@ -10805,14 +10821,14 @@
       <c r="P47" s="18">
         <v>10400</v>
       </c>
-      <c r="R47" s="92"/>
+      <c r="R47" s="94"/>
       <c r="S47" s="61" t="s">
         <v>567</v>
       </c>
       <c r="T47" s="44">
         <v>8320</v>
       </c>
-      <c r="V47" s="91" t="s">
+      <c r="V47" s="93" t="s">
         <v>110</v>
       </c>
       <c r="W47" s="69" t="s">
@@ -10830,7 +10846,7 @@
       <c r="AB47" s="44">
         <v>10400</v>
       </c>
-      <c r="AD47" s="91" t="s">
+      <c r="AD47" s="93" t="s">
         <v>247</v>
       </c>
       <c r="AE47" s="7" t="s">
@@ -10840,7 +10856,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="48" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B48" s="30" t="s">
         <v>298</v>
       </c>
@@ -10859,7 +10875,7 @@
       <c r="H48" s="18">
         <v>9490</v>
       </c>
-      <c r="J48" s="96" t="s">
+      <c r="J48" s="98" t="s">
         <v>90</v>
       </c>
       <c r="K48" s="45" t="s">
@@ -10877,14 +10893,14 @@
       <c r="P48" s="18">
         <v>10400</v>
       </c>
-      <c r="R48" s="92"/>
+      <c r="R48" s="94"/>
       <c r="S48" s="61" t="s">
         <v>568</v>
       </c>
       <c r="T48" s="44">
         <v>8580</v>
       </c>
-      <c r="V48" s="93"/>
+      <c r="V48" s="95"/>
       <c r="W48" s="73" t="s">
         <v>577</v>
       </c>
@@ -10900,7 +10916,7 @@
       <c r="AB48" s="18">
         <v>8580</v>
       </c>
-      <c r="AD48" s="92"/>
+      <c r="AD48" s="94"/>
       <c r="AE48" s="7" t="s">
         <v>573</v>
       </c>
@@ -10908,18 +10924,18 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="49" spans="2:32" ht="17" x14ac:dyDescent="0.2">
-      <c r="B49" s="118" t="s">
+    <row r="49" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B49" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="119"/>
-      <c r="D49" s="120"/>
-      <c r="F49" s="84" t="s">
+      <c r="C49" s="121"/>
+      <c r="D49" s="122"/>
+      <c r="F49" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="G49" s="84"/>
-      <c r="H49" s="84"/>
-      <c r="J49" s="92"/>
+      <c r="G49" s="86"/>
+      <c r="H49" s="86"/>
+      <c r="J49" s="94"/>
       <c r="K49" s="43" t="s">
         <v>560</v>
       </c>
@@ -10935,7 +10951,7 @@
       <c r="P49" s="18">
         <v>10400</v>
       </c>
-      <c r="R49" s="92"/>
+      <c r="R49" s="94"/>
       <c r="S49" s="61" t="s">
         <v>573</v>
       </c>
@@ -10960,7 +10976,7 @@
       <c r="AB49" s="18">
         <v>11440</v>
       </c>
-      <c r="AD49" s="92"/>
+      <c r="AD49" s="94"/>
       <c r="AE49" s="7" t="s">
         <v>582</v>
       </c>
@@ -10968,7 +10984,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="50" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="30" t="s">
         <v>331</v>
       </c>
@@ -10987,7 +11003,7 @@
       <c r="H50" s="18">
         <v>11400</v>
       </c>
-      <c r="J50" s="93"/>
+      <c r="J50" s="95"/>
       <c r="K50" s="50" t="s">
         <v>563</v>
       </c>
@@ -11003,7 +11019,7 @@
       <c r="P50" s="18">
         <v>10400</v>
       </c>
-      <c r="R50" s="92"/>
+      <c r="R50" s="94"/>
       <c r="S50" s="61" t="s">
         <v>574</v>
       </c>
@@ -11028,7 +11044,7 @@
       <c r="AB50" s="18">
         <v>8580</v>
       </c>
-      <c r="AD50" s="93"/>
+      <c r="AD50" s="95"/>
       <c r="AE50" s="46" t="s">
         <v>570</v>
       </c>
@@ -11036,7 +11052,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="51" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B51" s="30" t="s">
         <v>332</v>
       </c>
@@ -11055,7 +11071,7 @@
       <c r="H51" s="18">
         <v>11400</v>
       </c>
-      <c r="J51" s="96" t="s">
+      <c r="J51" s="98" t="s">
         <v>101</v>
       </c>
       <c r="K51" s="45" t="s">
@@ -11073,18 +11089,18 @@
       <c r="P51" s="18">
         <v>10400</v>
       </c>
-      <c r="R51" s="92"/>
+      <c r="R51" s="94"/>
       <c r="S51" s="63" t="s">
         <v>569</v>
       </c>
       <c r="T51" s="56">
         <v>7540</v>
       </c>
-      <c r="V51" s="84" t="s">
+      <c r="V51" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="W51" s="84"/>
-      <c r="X51" s="84"/>
+      <c r="W51" s="86"/>
+      <c r="X51" s="86"/>
       <c r="Z51" s="39" t="s">
         <v>497</v>
       </c>
@@ -11094,7 +11110,7 @@
       <c r="AB51" s="18">
         <v>8580</v>
       </c>
-      <c r="AD51" s="96" t="s">
+      <c r="AD51" s="98" t="s">
         <v>163</v>
       </c>
       <c r="AE51" s="45" t="s">
@@ -11104,7 +11120,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="52" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="30" t="s">
         <v>333</v>
       </c>
@@ -11114,12 +11130,12 @@
       <c r="D52" s="33">
         <v>11400</v>
       </c>
-      <c r="F52" s="84" t="s">
+      <c r="F52" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="G52" s="84"/>
-      <c r="H52" s="84"/>
-      <c r="J52" s="92"/>
+      <c r="G52" s="86"/>
+      <c r="H52" s="86"/>
+      <c r="J52" s="94"/>
       <c r="K52" s="53" t="s">
         <v>560</v>
       </c>
@@ -11135,7 +11151,7 @@
       <c r="P52" s="18">
         <v>10400</v>
       </c>
-      <c r="R52" s="93"/>
+      <c r="R52" s="95"/>
       <c r="S52" s="62" t="s">
         <v>571</v>
       </c>
@@ -11161,7 +11177,7 @@
       <c r="AB52" s="4">
         <v>11440</v>
       </c>
-      <c r="AD52" s="92"/>
+      <c r="AD52" s="94"/>
       <c r="AE52" s="7" t="s">
         <v>573</v>
       </c>
@@ -11169,7 +11185,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="53" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B53" s="30" t="s">
         <v>334</v>
       </c>
@@ -11188,11 +11204,11 @@
       <c r="H53" s="18">
         <v>9490</v>
       </c>
-      <c r="J53" s="95" t="s">
+      <c r="J53" s="97" t="s">
         <v>123</v>
       </c>
-      <c r="K53" s="95"/>
-      <c r="L53" s="95"/>
+      <c r="K53" s="97"/>
+      <c r="L53" s="97"/>
       <c r="N53" s="9" t="s">
         <v>144</v>
       </c>
@@ -11202,7 +11218,7 @@
       <c r="P53" s="18">
         <v>10400</v>
       </c>
-      <c r="R53" s="96" t="s">
+      <c r="R53" s="98" t="s">
         <v>223</v>
       </c>
       <c r="S53" s="64" t="s">
@@ -11220,12 +11236,12 @@
       <c r="X53" s="18">
         <v>15210</v>
       </c>
-      <c r="Z53" s="95" t="s">
+      <c r="Z53" s="97" t="s">
         <v>498</v>
       </c>
-      <c r="AA53" s="95"/>
-      <c r="AB53" s="95"/>
-      <c r="AD53" s="92"/>
+      <c r="AA53" s="97"/>
+      <c r="AB53" s="97"/>
+      <c r="AD53" s="94"/>
       <c r="AE53" s="7" t="s">
         <v>582</v>
       </c>
@@ -11233,7 +11249,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="54" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="30" t="s">
         <v>335</v>
       </c>
@@ -11252,7 +11268,7 @@
       <c r="H54" s="18">
         <v>9490</v>
       </c>
-      <c r="J54" s="92" t="s">
+      <c r="J54" s="94" t="s">
         <v>68</v>
       </c>
       <c r="K54" s="43" t="s">
@@ -11270,18 +11286,18 @@
       <c r="P54" s="18">
         <v>10400</v>
       </c>
-      <c r="R54" s="93"/>
+      <c r="R54" s="95"/>
       <c r="S54" s="65" t="s">
         <v>568</v>
       </c>
       <c r="T54" s="51">
         <v>8580</v>
       </c>
-      <c r="V54" s="84" t="s">
+      <c r="V54" s="86" t="s">
         <v>266</v>
       </c>
-      <c r="W54" s="84"/>
-      <c r="X54" s="84"/>
+      <c r="W54" s="86"/>
+      <c r="X54" s="86"/>
       <c r="Z54" s="39" t="str">
         <f>Z14</f>
         <v>Bachelor of Criminal Justice and Psychological Studies</v>
@@ -11292,7 +11308,7 @@
       <c r="AB54" s="4">
         <v>11440</v>
       </c>
-      <c r="AD54" s="93"/>
+      <c r="AD54" s="95"/>
       <c r="AE54" s="46" t="s">
         <v>570</v>
       </c>
@@ -11300,7 +11316,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="55" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B55" s="30" t="s">
         <v>336</v>
       </c>
@@ -11319,7 +11335,7 @@
       <c r="H55" s="18">
         <v>9490</v>
       </c>
-      <c r="J55" s="92"/>
+      <c r="J55" s="94"/>
       <c r="K55" s="7" t="s">
         <v>562</v>
       </c>
@@ -11363,7 +11379,7 @@
       <c r="AB55" s="4">
         <v>11440</v>
       </c>
-      <c r="AD55" s="96" t="s">
+      <c r="AD55" s="98" t="s">
         <v>90</v>
       </c>
       <c r="AE55" s="45" t="s">
@@ -11373,7 +11389,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="56" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="30" t="s">
         <v>337</v>
       </c>
@@ -11383,7 +11399,7 @@
       <c r="D56" s="33">
         <v>11400</v>
       </c>
-      <c r="J56" s="93"/>
+      <c r="J56" s="95"/>
       <c r="K56" s="46" t="s">
         <v>561</v>
       </c>
@@ -11399,7 +11415,7 @@
       <c r="P56" s="18">
         <v>10400</v>
       </c>
-      <c r="R56" s="91" t="s">
+      <c r="R56" s="93" t="s">
         <v>224</v>
       </c>
       <c r="S56" s="4" t="s">
@@ -11408,11 +11424,11 @@
       <c r="T56" s="18">
         <v>9620</v>
       </c>
-      <c r="V56" s="84" t="s">
+      <c r="V56" s="86" t="s">
         <v>267</v>
       </c>
-      <c r="W56" s="84"/>
-      <c r="X56" s="84"/>
+      <c r="W56" s="86"/>
+      <c r="X56" s="86"/>
       <c r="Z56" s="39" t="str">
         <f>Z12</f>
         <v>Bachelor of Criminology</v>
@@ -11423,7 +11439,7 @@
       <c r="AB56" s="4">
         <v>10400</v>
       </c>
-      <c r="AD56" s="92"/>
+      <c r="AD56" s="94"/>
       <c r="AE56" s="7" t="s">
         <v>573</v>
       </c>
@@ -11431,7 +11447,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="57" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B57" s="30" t="s">
         <v>338</v>
       </c>
@@ -11441,7 +11457,7 @@
       <c r="D57" s="33">
         <v>11400</v>
       </c>
-      <c r="J57" s="96" t="s">
+      <c r="J57" s="98" t="s">
         <v>69</v>
       </c>
       <c r="K57" s="45" t="s">
@@ -11459,7 +11475,7 @@
       <c r="P57" s="18">
         <v>10400</v>
       </c>
-      <c r="R57" s="92"/>
+      <c r="R57" s="94"/>
       <c r="S57" s="4" t="s">
         <v>567</v>
       </c>
@@ -11484,7 +11500,7 @@
       <c r="AB57" s="4">
         <v>10400</v>
       </c>
-      <c r="AD57" s="93"/>
+      <c r="AD57" s="95"/>
       <c r="AE57" s="46" t="s">
         <v>582</v>
       </c>
@@ -11492,7 +11508,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="58" spans="2:32" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="30" t="s">
         <v>339</v>
       </c>
@@ -11502,7 +11518,7 @@
       <c r="D58" s="33">
         <v>11400</v>
       </c>
-      <c r="J58" s="93"/>
+      <c r="J58" s="95"/>
       <c r="K58" s="46" t="s">
         <v>561</v>
       </c>
@@ -11518,7 +11534,7 @@
       <c r="P58" s="18">
         <v>10400</v>
       </c>
-      <c r="R58" s="92"/>
+      <c r="R58" s="94"/>
       <c r="S58" s="63" t="s">
         <v>569</v>
       </c>
@@ -11534,12 +11550,12 @@
       <c r="X58" s="18">
         <v>15210</v>
       </c>
-      <c r="Z58" s="95" t="s">
+      <c r="Z58" s="97" t="s">
         <v>499</v>
       </c>
-      <c r="AA58" s="95"/>
-      <c r="AB58" s="95"/>
-      <c r="AD58" s="96" t="s">
+      <c r="AA58" s="97"/>
+      <c r="AB58" s="97"/>
+      <c r="AD58" s="98" t="s">
         <v>485</v>
       </c>
       <c r="AE58" s="45" t="s">
@@ -11549,7 +11565,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="59" spans="2:32" ht="17" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B59" s="30" t="s">
         <v>340</v>
       </c>
@@ -11559,7 +11575,7 @@
       <c r="D59" s="33">
         <v>11400</v>
       </c>
-      <c r="J59" s="96" t="s">
+      <c r="J59" s="98" t="s">
         <v>70</v>
       </c>
       <c r="K59" s="45" t="s">
@@ -11577,7 +11593,7 @@
       <c r="P59" s="18">
         <v>10400</v>
       </c>
-      <c r="R59" s="92"/>
+      <c r="R59" s="94"/>
       <c r="S59" s="63" t="s">
         <v>568</v>
       </c>
@@ -11593,7 +11609,7 @@
       <c r="X59" s="18">
         <v>15210</v>
       </c>
-      <c r="Z59" s="91" t="str">
+      <c r="Z59" s="93" t="str">
         <f>Z42</f>
         <v>Bachelor of Biomedical and Exercise Science</v>
       </c>
@@ -11603,7 +11619,7 @@
       <c r="AB59" s="4">
         <v>11440</v>
       </c>
-      <c r="AD59" s="92"/>
+      <c r="AD59" s="94"/>
       <c r="AE59" s="7" t="s">
         <v>573</v>
       </c>
@@ -11611,7 +11627,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="60" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B60" s="30" t="s">
         <v>341</v>
       </c>
@@ -11621,7 +11637,7 @@
       <c r="D60" s="33">
         <v>11400</v>
       </c>
-      <c r="J60" s="93"/>
+      <c r="J60" s="95"/>
       <c r="K60" s="46" t="s">
         <v>561</v>
       </c>
@@ -11637,21 +11653,21 @@
       <c r="P60" s="18">
         <v>10400</v>
       </c>
-      <c r="R60" s="93"/>
+      <c r="R60" s="95"/>
       <c r="S60" s="62" t="s">
         <v>571</v>
       </c>
       <c r="T60" s="47">
         <v>7280</v>
       </c>
-      <c r="Z60" s="93"/>
+      <c r="Z60" s="95"/>
       <c r="AA60" s="46" t="s">
         <v>579</v>
       </c>
       <c r="AB60" s="62">
         <v>8580</v>
       </c>
-      <c r="AD60" s="93"/>
+      <c r="AD60" s="95"/>
       <c r="AE60" s="46" t="s">
         <v>582</v>
       </c>
@@ -11659,7 +11675,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="61" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B61" s="30" t="s">
         <v>342</v>
       </c>
@@ -11669,7 +11685,7 @@
       <c r="D61" s="33">
         <v>11400</v>
       </c>
-      <c r="J61" s="96" t="s">
+      <c r="J61" s="98" t="s">
         <v>8</v>
       </c>
       <c r="K61" s="45" t="s">
@@ -11678,12 +11694,12 @@
       <c r="L61" s="48">
         <v>10660</v>
       </c>
-      <c r="N61" s="84" t="s">
+      <c r="N61" s="86" t="s">
         <v>157</v>
       </c>
-      <c r="O61" s="84"/>
-      <c r="P61" s="84"/>
-      <c r="R61" s="96" t="s">
+      <c r="O61" s="86"/>
+      <c r="P61" s="86"/>
+      <c r="R61" s="98" t="s">
         <v>225</v>
       </c>
       <c r="S61" s="66" t="s">
@@ -11701,7 +11717,7 @@
       <c r="AB61" s="44">
         <v>11440</v>
       </c>
-      <c r="AD61" s="96" t="s">
+      <c r="AD61" s="98" t="s">
         <v>517</v>
       </c>
       <c r="AE61" s="45" t="s">
@@ -11711,7 +11727,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="62" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B62" s="30" t="s">
         <v>343</v>
       </c>
@@ -11721,7 +11737,7 @@
       <c r="D62" s="33">
         <v>11400</v>
       </c>
-      <c r="J62" s="92"/>
+      <c r="J62" s="94"/>
       <c r="K62" s="7" t="s">
         <v>562</v>
       </c>
@@ -11737,7 +11753,7 @@
       <c r="P62" s="18">
         <v>10400</v>
       </c>
-      <c r="R62" s="92"/>
+      <c r="R62" s="94"/>
       <c r="S62" s="4" t="s">
         <v>567</v>
       </c>
@@ -11753,7 +11769,7 @@
       <c r="AB62" s="44">
         <v>11440</v>
       </c>
-      <c r="AD62" s="92"/>
+      <c r="AD62" s="94"/>
       <c r="AE62" s="7" t="s">
         <v>573</v>
       </c>
@@ -11761,7 +11777,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="63" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="30" t="s">
         <v>344</v>
       </c>
@@ -11771,7 +11787,7 @@
       <c r="D63" s="33">
         <v>11400</v>
       </c>
-      <c r="J63" s="92"/>
+      <c r="J63" s="94"/>
       <c r="K63" s="7" t="s">
         <v>563</v>
       </c>
@@ -11787,7 +11803,7 @@
       <c r="P63" s="18">
         <v>10400</v>
       </c>
-      <c r="R63" s="92"/>
+      <c r="R63" s="94"/>
       <c r="S63" s="61" t="s">
         <v>565</v>
       </c>
@@ -11803,7 +11819,7 @@
       <c r="AB63" s="44">
         <v>11440</v>
       </c>
-      <c r="AD63" s="93"/>
+      <c r="AD63" s="95"/>
       <c r="AE63" s="46" t="s">
         <v>582</v>
       </c>
@@ -11811,7 +11827,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="64" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B64" s="30" t="s">
         <v>55</v>
       </c>
@@ -11821,7 +11837,7 @@
       <c r="D64" s="33">
         <v>11400</v>
       </c>
-      <c r="J64" s="93"/>
+      <c r="J64" s="95"/>
       <c r="K64" s="46" t="s">
         <v>561</v>
       </c>
@@ -11837,7 +11853,7 @@
       <c r="P64" s="18">
         <v>10400</v>
       </c>
-      <c r="R64" s="93"/>
+      <c r="R64" s="95"/>
       <c r="S64" s="65" t="s">
         <v>570</v>
       </c>
@@ -11853,7 +11869,7 @@
       <c r="AB64" s="44">
         <v>11440</v>
       </c>
-      <c r="AD64" s="96" t="s">
+      <c r="AD64" s="98" t="s">
         <v>518</v>
       </c>
       <c r="AE64" s="45" t="s">
@@ -11863,13 +11879,13 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B65" s="118" t="s">
+    <row r="65" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B65" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="119"/>
-      <c r="D65" s="120"/>
-      <c r="J65" s="96" t="s">
+      <c r="C65" s="121"/>
+      <c r="D65" s="122"/>
+      <c r="J65" s="98" t="s">
         <v>105</v>
       </c>
       <c r="K65" s="45" t="s">
@@ -11887,11 +11903,11 @@
       <c r="P65" s="18">
         <v>10400</v>
       </c>
-      <c r="R65" s="100" t="s">
+      <c r="R65" s="102" t="s">
         <v>226</v>
       </c>
-      <c r="S65" s="101"/>
-      <c r="T65" s="102"/>
+      <c r="S65" s="103"/>
+      <c r="T65" s="104"/>
       <c r="Z65" s="39" t="s">
         <v>503</v>
       </c>
@@ -11901,7 +11917,7 @@
       <c r="AB65" s="44">
         <v>11440</v>
       </c>
-      <c r="AD65" s="92"/>
+      <c r="AD65" s="94"/>
       <c r="AE65" s="7" t="s">
         <v>573</v>
       </c>
@@ -11909,7 +11925,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="66" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="30" t="s">
         <v>21</v>
       </c>
@@ -11919,7 +11935,7 @@
       <c r="D66" s="33">
         <v>11400</v>
       </c>
-      <c r="J66" s="92"/>
+      <c r="J66" s="94"/>
       <c r="K66" s="43" t="s">
         <v>562</v>
       </c>
@@ -11935,7 +11951,7 @@
       <c r="P66" s="18">
         <v>10400</v>
       </c>
-      <c r="R66" s="91" t="s">
+      <c r="R66" s="93" t="s">
         <v>71</v>
       </c>
       <c r="S66" s="4" t="s">
@@ -11953,7 +11969,7 @@
       <c r="AB66" s="44">
         <v>11440</v>
       </c>
-      <c r="AD66" s="93"/>
+      <c r="AD66" s="95"/>
       <c r="AE66" s="46" t="s">
         <v>582</v>
       </c>
@@ -11961,7 +11977,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B67" s="30" t="s">
         <v>361</v>
       </c>
@@ -11971,7 +11987,7 @@
       <c r="D67" s="33">
         <v>11400</v>
       </c>
-      <c r="J67" s="93"/>
+      <c r="J67" s="95"/>
       <c r="K67" s="50" t="s">
         <v>561</v>
       </c>
@@ -11987,14 +12003,14 @@
       <c r="P67" s="18">
         <v>10400</v>
       </c>
-      <c r="R67" s="93"/>
+      <c r="R67" s="95"/>
       <c r="S67" s="62" t="s">
         <v>568</v>
       </c>
       <c r="T67" s="47">
         <v>8580</v>
       </c>
-      <c r="AD67" s="96" t="s">
+      <c r="AD67" s="98" t="s">
         <v>519</v>
       </c>
       <c r="AE67" s="45" t="s">
@@ -12004,7 +12020,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B68" s="30" t="s">
         <v>39</v>
       </c>
@@ -12014,7 +12030,7 @@
       <c r="D68" s="33">
         <v>11400</v>
       </c>
-      <c r="J68" s="108" t="s">
+      <c r="J68" s="110" t="s">
         <v>119</v>
       </c>
       <c r="K68" s="45" t="s">
@@ -12041,7 +12057,7 @@
       <c r="T68" s="44">
         <v>9620</v>
       </c>
-      <c r="AD68" s="92"/>
+      <c r="AD68" s="94"/>
       <c r="AE68" s="7" t="s">
         <v>573</v>
       </c>
@@ -12049,7 +12065,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="69" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B69" s="30" t="s">
         <v>40</v>
       </c>
@@ -12059,7 +12075,7 @@
       <c r="D69" s="33">
         <v>11400</v>
       </c>
-      <c r="J69" s="109"/>
+      <c r="J69" s="111"/>
       <c r="K69" s="50" t="s">
         <v>561</v>
       </c>
@@ -12084,7 +12100,7 @@
       <c r="T69" s="18">
         <v>9620</v>
       </c>
-      <c r="AD69" s="93"/>
+      <c r="AD69" s="95"/>
       <c r="AE69" s="46" t="s">
         <v>582</v>
       </c>
@@ -12092,7 +12108,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B70" s="30" t="s">
         <v>362</v>
       </c>
@@ -12102,7 +12118,7 @@
       <c r="D70" s="33">
         <v>11400</v>
       </c>
-      <c r="J70" s="96" t="s">
+      <c r="J70" s="98" t="s">
         <v>113</v>
       </c>
       <c r="K70" s="45" t="s">
@@ -12111,11 +12127,11 @@
       <c r="L70" s="48">
         <v>10660</v>
       </c>
-      <c r="N70" s="84" t="s">
+      <c r="N70" s="86" t="s">
         <v>153</v>
       </c>
-      <c r="O70" s="84"/>
-      <c r="P70" s="84"/>
+      <c r="O70" s="86"/>
+      <c r="P70" s="86"/>
       <c r="R70" s="39" t="s">
         <v>228</v>
       </c>
@@ -12125,13 +12141,13 @@
       <c r="T70" s="18">
         <v>9620</v>
       </c>
-      <c r="AD70" s="103" t="s">
+      <c r="AD70" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="AE70" s="103"/>
-      <c r="AF70" s="103"/>
-    </row>
-    <row r="71" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AE70" s="105"/>
+      <c r="AF70" s="105"/>
+    </row>
+    <row r="71" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="30" t="s">
         <v>42</v>
       </c>
@@ -12141,7 +12157,7 @@
       <c r="D71" s="33">
         <v>11400</v>
       </c>
-      <c r="J71" s="93"/>
+      <c r="J71" s="95"/>
       <c r="K71" s="50" t="s">
         <v>561</v>
       </c>
@@ -12157,7 +12173,7 @@
       <c r="P71" s="18">
         <v>10400</v>
       </c>
-      <c r="R71" s="122" t="s">
+      <c r="R71" s="124" t="s">
         <v>103</v>
       </c>
       <c r="S71" s="4" t="s">
@@ -12166,7 +12182,7 @@
       <c r="T71" s="18">
         <v>9620</v>
       </c>
-      <c r="AD71" s="91" t="s">
+      <c r="AD71" s="93" t="s">
         <v>520</v>
       </c>
       <c r="AE71" s="7" t="s">
@@ -12176,12 +12192,12 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="72" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="118" t="s">
+    <row r="72" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="120" t="s">
         <v>244</v>
       </c>
-      <c r="C72" s="119"/>
-      <c r="D72" s="121"/>
+      <c r="C72" s="121"/>
+      <c r="D72" s="123"/>
       <c r="J72" s="40" t="s">
         <v>117</v>
       </c>
@@ -12200,14 +12216,14 @@
       <c r="P72" s="23">
         <v>10400</v>
       </c>
-      <c r="R72" s="123"/>
+      <c r="R72" s="125"/>
       <c r="S72" s="4" t="s">
         <v>568</v>
       </c>
       <c r="T72" s="18">
         <v>8520</v>
       </c>
-      <c r="AD72" s="93"/>
+      <c r="AD72" s="95"/>
       <c r="AE72" s="46" t="s">
         <v>582</v>
       </c>
@@ -12215,7 +12231,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B73" s="30" t="s">
         <v>369</v>
       </c>
@@ -12225,24 +12241,24 @@
       <c r="D73" s="33">
         <v>11400</v>
       </c>
-      <c r="J73" s="95" t="s">
+      <c r="J73" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="K73" s="95"/>
-      <c r="L73" s="95"/>
-      <c r="N73" s="81" t="s">
+      <c r="K73" s="97"/>
+      <c r="L73" s="97"/>
+      <c r="N73" s="83" t="s">
         <v>154</v>
       </c>
-      <c r="O73" s="82"/>
-      <c r="P73" s="83"/>
-      <c r="R73" s="124"/>
+      <c r="O73" s="84"/>
+      <c r="P73" s="85"/>
+      <c r="R73" s="126"/>
       <c r="S73" s="62" t="s">
         <v>570</v>
       </c>
       <c r="T73" s="47">
         <v>0</v>
       </c>
-      <c r="AD73" s="96" t="s">
+      <c r="AD73" s="98" t="s">
         <v>521</v>
       </c>
       <c r="AE73" s="45" t="s">
@@ -12252,7 +12268,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="74" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="30" t="s">
         <v>370</v>
       </c>
@@ -12262,7 +12278,7 @@
       <c r="D74" s="33">
         <v>11400</v>
       </c>
-      <c r="J74" s="92" t="s">
+      <c r="J74" s="94" t="s">
         <v>95</v>
       </c>
       <c r="K74" s="43" t="s">
@@ -12280,12 +12296,12 @@
       <c r="P74" s="18">
         <v>10400</v>
       </c>
-      <c r="R74" s="100" t="s">
+      <c r="R74" s="102" t="s">
         <v>229</v>
       </c>
-      <c r="S74" s="101"/>
-      <c r="T74" s="102"/>
-      <c r="AD74" s="93"/>
+      <c r="S74" s="103"/>
+      <c r="T74" s="104"/>
+      <c r="AD74" s="95"/>
       <c r="AE74" s="46" t="s">
         <v>582</v>
       </c>
@@ -12293,7 +12309,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="75" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B75" s="30" t="s">
         <v>371</v>
       </c>
@@ -12303,7 +12319,7 @@
       <c r="D75" s="33">
         <v>11400</v>
       </c>
-      <c r="J75" s="93"/>
+      <c r="J75" s="95"/>
       <c r="K75" s="46" t="s">
         <v>560</v>
       </c>
@@ -12319,7 +12335,7 @@
       <c r="P75" s="18">
         <v>10400</v>
       </c>
-      <c r="R75" s="91" t="s">
+      <c r="R75" s="93" t="s">
         <v>82</v>
       </c>
       <c r="S75" s="4" t="s">
@@ -12338,7 +12354,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="76" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="30" t="s">
         <v>372</v>
       </c>
@@ -12366,7 +12382,7 @@
       <c r="P76" s="18">
         <v>10400</v>
       </c>
-      <c r="R76" s="93"/>
+      <c r="R76" s="95"/>
       <c r="S76" s="62" t="s">
         <v>568</v>
       </c>
@@ -12383,7 +12399,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B77" s="30" t="s">
         <v>373</v>
       </c>
@@ -12393,7 +12409,7 @@
       <c r="D77" s="33">
         <v>11400</v>
       </c>
-      <c r="J77" s="91" t="s">
+      <c r="J77" s="93" t="s">
         <v>99</v>
       </c>
       <c r="K77" s="7" t="s">
@@ -12411,7 +12427,7 @@
       <c r="P77" s="18">
         <v>10400</v>
       </c>
-      <c r="R77" s="96" t="s">
+      <c r="R77" s="98" t="s">
         <v>230</v>
       </c>
       <c r="S77" s="64" t="s">
@@ -12420,13 +12436,13 @@
       <c r="T77" s="48">
         <v>9620</v>
       </c>
-      <c r="AD77" s="104" t="s">
+      <c r="AD77" s="106" t="s">
         <v>524</v>
       </c>
-      <c r="AE77" s="105"/>
-      <c r="AF77" s="106"/>
-    </row>
-    <row r="78" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AE77" s="107"/>
+      <c r="AF77" s="108"/>
+    </row>
+    <row r="78" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="30" t="s">
         <v>374</v>
       </c>
@@ -12436,7 +12452,7 @@
       <c r="D78" s="33">
         <v>11400</v>
       </c>
-      <c r="J78" s="92"/>
+      <c r="J78" s="94"/>
       <c r="K78" s="7" t="s">
         <v>560</v>
       </c>
@@ -12452,14 +12468,14 @@
       <c r="P78" s="18">
         <v>10400</v>
       </c>
-      <c r="R78" s="93"/>
+      <c r="R78" s="95"/>
       <c r="S78" s="62" t="s">
         <v>568</v>
       </c>
       <c r="T78" s="47">
         <v>8580</v>
       </c>
-      <c r="AD78" s="91" t="s">
+      <c r="AD78" s="93" t="s">
         <v>103</v>
       </c>
       <c r="AE78" s="7" t="s">
@@ -12469,7 +12485,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B79" s="30" t="s">
         <v>375</v>
       </c>
@@ -12479,7 +12495,7 @@
       <c r="D79" s="33">
         <v>11400</v>
       </c>
-      <c r="J79" s="92"/>
+      <c r="J79" s="94"/>
       <c r="K79" s="7" t="s">
         <v>563</v>
       </c>
@@ -12495,12 +12511,12 @@
       <c r="P79" s="18">
         <v>10400</v>
       </c>
-      <c r="R79" s="103" t="s">
+      <c r="R79" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="S79" s="103"/>
-      <c r="T79" s="103"/>
-      <c r="AD79" s="92"/>
+      <c r="S79" s="105"/>
+      <c r="T79" s="105"/>
+      <c r="AD79" s="94"/>
       <c r="AE79" s="7" t="s">
         <v>573</v>
       </c>
@@ -12508,7 +12524,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="80" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="30" t="s">
         <v>376</v>
       </c>
@@ -12518,7 +12534,7 @@
       <c r="D80" s="33">
         <v>11400</v>
       </c>
-      <c r="J80" s="93"/>
+      <c r="J80" s="95"/>
       <c r="K80" s="46" t="s">
         <v>561</v>
       </c>
@@ -12534,7 +12550,7 @@
       <c r="P80" s="18">
         <v>10400</v>
       </c>
-      <c r="R80" s="91" t="s">
+      <c r="R80" s="93" t="s">
         <v>5</v>
       </c>
       <c r="S80" s="4" t="s">
@@ -12543,7 +12559,7 @@
       <c r="T80" s="18">
         <v>9620</v>
       </c>
-      <c r="AD80" s="92"/>
+      <c r="AD80" s="94"/>
       <c r="AE80" s="7" t="s">
         <v>582</v>
       </c>
@@ -12551,7 +12567,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="81" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B81" s="30" t="s">
         <v>377</v>
       </c>
@@ -12579,14 +12595,14 @@
       <c r="P81" s="18">
         <v>10400</v>
       </c>
-      <c r="R81" s="93"/>
+      <c r="R81" s="95"/>
       <c r="S81" s="62" t="s">
         <v>567</v>
       </c>
       <c r="T81" s="47">
         <v>8320</v>
       </c>
-      <c r="AD81" s="93"/>
+      <c r="AD81" s="95"/>
       <c r="AE81" s="46" t="s">
         <v>570</v>
       </c>
@@ -12594,7 +12610,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="82" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B82" s="30" t="s">
         <v>378</v>
       </c>
@@ -12604,7 +12620,7 @@
       <c r="D82" s="33">
         <v>11400</v>
       </c>
-      <c r="J82" s="91" t="s">
+      <c r="J82" s="93" t="s">
         <v>110</v>
       </c>
       <c r="K82" s="7" t="s">
@@ -12613,12 +12629,12 @@
       <c r="L82" s="18">
         <v>10660</v>
       </c>
-      <c r="N82" s="81" t="s">
+      <c r="N82" s="83" t="s">
         <v>193</v>
       </c>
-      <c r="O82" s="82"/>
-      <c r="P82" s="83"/>
-      <c r="R82" s="96" t="s">
+      <c r="O82" s="84"/>
+      <c r="P82" s="85"/>
+      <c r="R82" s="98" t="s">
         <v>231</v>
       </c>
       <c r="S82" s="64" t="s">
@@ -12627,7 +12643,7 @@
       <c r="T82" s="48">
         <v>9620</v>
       </c>
-      <c r="AD82" s="96" t="s">
+      <c r="AD82" s="98" t="s">
         <v>525</v>
       </c>
       <c r="AE82" s="45" t="s">
@@ -12637,7 +12653,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="83" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="30" t="s">
         <v>379</v>
       </c>
@@ -12647,7 +12663,7 @@
       <c r="D83" s="33">
         <v>11400</v>
       </c>
-      <c r="J83" s="92"/>
+      <c r="J83" s="94"/>
       <c r="K83" s="7" t="s">
         <v>562</v>
       </c>
@@ -12663,14 +12679,14 @@
       <c r="P83" s="20">
         <v>9620</v>
       </c>
-      <c r="R83" s="93"/>
+      <c r="R83" s="95"/>
       <c r="S83" s="62" t="s">
         <v>567</v>
       </c>
       <c r="T83" s="47">
         <v>8320</v>
       </c>
-      <c r="AD83" s="93"/>
+      <c r="AD83" s="95"/>
       <c r="AE83" s="46" t="s">
         <v>573</v>
       </c>
@@ -12678,7 +12694,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="84" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B84" s="30" t="s">
         <v>380</v>
       </c>
@@ -12688,7 +12704,7 @@
       <c r="D84" s="33">
         <v>11400</v>
       </c>
-      <c r="J84" s="92"/>
+      <c r="J84" s="94"/>
       <c r="K84" s="55" t="s">
         <v>563</v>
       </c>
@@ -12704,7 +12720,7 @@
       <c r="P84" s="20">
         <v>9620</v>
       </c>
-      <c r="R84" s="96" t="s">
+      <c r="R84" s="98" t="s">
         <v>232</v>
       </c>
       <c r="S84" s="64" t="s">
@@ -12713,7 +12729,7 @@
       <c r="T84" s="48">
         <v>9620</v>
       </c>
-      <c r="AD84" s="96" t="s">
+      <c r="AD84" s="98" t="s">
         <v>526</v>
       </c>
       <c r="AE84" s="45" t="s">
@@ -12723,12 +12739,12 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="85" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="118" t="s">
+    <row r="85" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="C85" s="119"/>
-      <c r="D85" s="121"/>
+      <c r="C85" s="121"/>
+      <c r="D85" s="123"/>
       <c r="J85" s="39" t="s">
         <v>111</v>
       </c>
@@ -12747,14 +12763,14 @@
       <c r="P85" s="20">
         <v>9620</v>
       </c>
-      <c r="R85" s="93"/>
+      <c r="R85" s="95"/>
       <c r="S85" s="62" t="s">
         <v>567</v>
       </c>
       <c r="T85" s="47">
         <v>8320</v>
       </c>
-      <c r="AD85" s="92"/>
+      <c r="AD85" s="94"/>
       <c r="AE85" s="7" t="s">
         <v>573</v>
       </c>
@@ -12762,7 +12778,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="86" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B86" s="30" t="s">
         <v>393</v>
       </c>
@@ -12788,7 +12804,7 @@
       <c r="P86" s="20">
         <v>9620</v>
       </c>
-      <c r="R86" s="96" t="s">
+      <c r="R86" s="98" t="s">
         <v>7</v>
       </c>
       <c r="S86" s="64" t="s">
@@ -12797,7 +12813,7 @@
       <c r="T86" s="48">
         <v>9620</v>
       </c>
-      <c r="AD86" s="93"/>
+      <c r="AD86" s="95"/>
       <c r="AE86" s="46" t="s">
         <v>570</v>
       </c>
@@ -12805,7 +12821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="87" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B87" s="30" t="s">
         <v>394</v>
       </c>
@@ -12815,7 +12831,7 @@
       <c r="D87" s="33">
         <v>11400</v>
       </c>
-      <c r="J87" s="92" t="s">
+      <c r="J87" s="94" t="s">
         <v>114</v>
       </c>
       <c r="K87" s="53" t="s">
@@ -12833,14 +12849,14 @@
       <c r="P87" s="20">
         <v>9620</v>
       </c>
-      <c r="R87" s="92"/>
+      <c r="R87" s="94"/>
       <c r="S87" s="61" t="s">
         <v>567</v>
       </c>
       <c r="T87" s="44">
         <v>8320</v>
       </c>
-      <c r="AD87" s="96" t="s">
+      <c r="AD87" s="98" t="s">
         <v>527</v>
       </c>
       <c r="AE87" s="45" t="s">
@@ -12850,7 +12866,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="88" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B88" s="30" t="s">
         <v>395</v>
       </c>
@@ -12860,26 +12876,26 @@
       <c r="D88" s="33">
         <v>11400</v>
       </c>
-      <c r="J88" s="92"/>
+      <c r="J88" s="94"/>
       <c r="K88" s="53" t="s">
         <v>560</v>
       </c>
       <c r="L88" s="54">
         <v>8320</v>
       </c>
-      <c r="N88" s="84" t="s">
+      <c r="N88" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="O88" s="84"/>
-      <c r="P88" s="84"/>
-      <c r="R88" s="93"/>
+      <c r="O88" s="86"/>
+      <c r="P88" s="86"/>
+      <c r="R88" s="95"/>
       <c r="S88" s="65" t="s">
         <v>568</v>
       </c>
       <c r="T88" s="51">
         <v>8580</v>
       </c>
-      <c r="AD88" s="93"/>
+      <c r="AD88" s="95"/>
       <c r="AE88" s="46" t="s">
         <v>570</v>
       </c>
@@ -12887,7 +12903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="89" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B89" s="30" t="s">
         <v>396</v>
       </c>
@@ -12897,7 +12913,7 @@
       <c r="D89" s="33">
         <v>11400</v>
       </c>
-      <c r="J89" s="92"/>
+      <c r="J89" s="94"/>
       <c r="K89" s="53" t="s">
         <v>563</v>
       </c>
@@ -12913,7 +12929,7 @@
       <c r="P89" s="18">
         <v>9620</v>
       </c>
-      <c r="R89" s="96" t="s">
+      <c r="R89" s="98" t="s">
         <v>115</v>
       </c>
       <c r="S89" s="64" t="s">
@@ -12922,7 +12938,7 @@
       <c r="T89" s="48">
         <v>9620</v>
       </c>
-      <c r="AD89" s="96" t="s">
+      <c r="AD89" s="98" t="s">
         <v>528</v>
       </c>
       <c r="AE89" s="45" t="s">
@@ -12932,7 +12948,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="90" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B90" s="30" t="s">
         <v>397</v>
       </c>
@@ -12942,7 +12958,7 @@
       <c r="D90" s="33">
         <v>11400</v>
       </c>
-      <c r="J90" s="93"/>
+      <c r="J90" s="95"/>
       <c r="K90" s="50" t="s">
         <v>561</v>
       </c>
@@ -12958,14 +12974,14 @@
       <c r="P90" s="18">
         <v>9620</v>
       </c>
-      <c r="R90" s="93"/>
+      <c r="R90" s="95"/>
       <c r="S90" s="65" t="s">
         <v>568</v>
       </c>
       <c r="T90" s="51">
         <v>8580</v>
       </c>
-      <c r="AD90" s="93"/>
+      <c r="AD90" s="95"/>
       <c r="AE90" s="46" t="s">
         <v>570</v>
       </c>
@@ -12973,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="91" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B91" s="30" t="s">
         <v>398</v>
       </c>
@@ -12983,7 +12999,7 @@
       <c r="D91" s="33">
         <v>11400</v>
       </c>
-      <c r="J91" s="96" t="s">
+      <c r="J91" s="98" t="s">
         <v>116</v>
       </c>
       <c r="K91" s="45" t="s">
@@ -13010,7 +13026,7 @@
       <c r="T91" s="44">
         <v>9620</v>
       </c>
-      <c r="AD91" s="96" t="s">
+      <c r="AD91" s="98" t="s">
         <v>529</v>
       </c>
       <c r="AE91" s="45" t="s">
@@ -13020,7 +13036,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="92" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B92" s="30" t="s">
         <v>399</v>
       </c>
@@ -13030,7 +13046,7 @@
       <c r="D92" s="33">
         <v>11400</v>
       </c>
-      <c r="J92" s="92"/>
+      <c r="J92" s="94"/>
       <c r="K92" s="53" t="s">
         <v>561</v>
       </c>
@@ -13046,7 +13062,7 @@
       <c r="P92" s="18">
         <v>9620</v>
       </c>
-      <c r="AD92" s="93"/>
+      <c r="AD92" s="95"/>
       <c r="AE92" s="46" t="s">
         <v>570</v>
       </c>
@@ -13054,17 +13070,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="118" t="s">
+    <row r="93" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B93" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="C93" s="119"/>
-      <c r="D93" s="121"/>
-      <c r="J93" s="95" t="s">
+      <c r="C93" s="121"/>
+      <c r="D93" s="123"/>
+      <c r="J93" s="97" t="s">
         <v>125</v>
       </c>
-      <c r="K93" s="95"/>
-      <c r="L93" s="95"/>
+      <c r="K93" s="97"/>
+      <c r="L93" s="97"/>
       <c r="N93" s="10" t="s">
         <v>171</v>
       </c>
@@ -13074,13 +13090,13 @@
       <c r="P93" s="18">
         <v>10400</v>
       </c>
-      <c r="AD93" s="103" t="s">
+      <c r="AD93" s="105" t="s">
         <v>530</v>
       </c>
-      <c r="AE93" s="103"/>
-      <c r="AF93" s="103"/>
-    </row>
-    <row r="94" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AE93" s="105"/>
+      <c r="AF93" s="105"/>
+    </row>
+    <row r="94" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B94" s="30" t="s">
         <v>19</v>
       </c>
@@ -13090,7 +13106,7 @@
       <c r="D94" s="33">
         <v>11400</v>
       </c>
-      <c r="J94" s="92" t="s">
+      <c r="J94" s="94" t="s">
         <v>67</v>
       </c>
       <c r="K94" s="43" t="s">
@@ -13108,7 +13124,7 @@
       <c r="P94" s="18">
         <v>10400</v>
       </c>
-      <c r="AD94" s="91" t="s">
+      <c r="AD94" s="93" t="s">
         <v>110</v>
       </c>
       <c r="AE94" s="7" t="s">
@@ -13118,13 +13134,13 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="95" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="118" t="s">
+    <row r="95" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B95" s="120" t="s">
         <v>115</v>
       </c>
-      <c r="C95" s="119"/>
-      <c r="D95" s="121"/>
-      <c r="J95" s="93"/>
+      <c r="C95" s="121"/>
+      <c r="D95" s="123"/>
+      <c r="J95" s="95"/>
       <c r="K95" s="46" t="s">
         <v>560</v>
       </c>
@@ -13140,7 +13156,7 @@
       <c r="P95" s="18">
         <v>10400</v>
       </c>
-      <c r="AD95" s="92"/>
+      <c r="AD95" s="94"/>
       <c r="AE95" s="7" t="s">
         <v>573</v>
       </c>
@@ -13148,7 +13164,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="96" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="30" t="s">
         <v>407</v>
       </c>
@@ -13158,7 +13174,7 @@
       <c r="D96" s="33">
         <v>11400</v>
       </c>
-      <c r="J96" s="96" t="s">
+      <c r="J96" s="98" t="s">
         <v>71</v>
       </c>
       <c r="K96" s="45" t="s">
@@ -13176,7 +13192,7 @@
       <c r="P96" s="18">
         <v>10400</v>
       </c>
-      <c r="AD96" s="93"/>
+      <c r="AD96" s="95"/>
       <c r="AE96" s="46" t="s">
         <v>582</v>
       </c>
@@ -13184,7 +13200,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="97" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B97" s="30" t="s">
         <v>408</v>
       </c>
@@ -13194,7 +13210,7 @@
       <c r="D97" s="33">
         <v>11400</v>
       </c>
-      <c r="J97" s="92"/>
+      <c r="J97" s="94"/>
       <c r="K97" s="7" t="s">
         <v>560</v>
       </c>
@@ -13220,7 +13236,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="98" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B98" s="30" t="s">
         <v>409</v>
       </c>
@@ -13230,7 +13246,7 @@
       <c r="D98" s="33">
         <v>11400</v>
       </c>
-      <c r="J98" s="93"/>
+      <c r="J98" s="95"/>
       <c r="K98" s="46" t="s">
         <v>561</v>
       </c>
@@ -13246,13 +13262,13 @@
       <c r="P98" s="18">
         <v>10400</v>
       </c>
-      <c r="AD98" s="104" t="s">
+      <c r="AD98" s="106" t="s">
         <v>532</v>
       </c>
-      <c r="AE98" s="105"/>
-      <c r="AF98" s="106"/>
-    </row>
-    <row r="99" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AE98" s="107"/>
+      <c r="AF98" s="108"/>
+    </row>
+    <row r="99" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B99" s="30" t="s">
         <v>331</v>
       </c>
@@ -13262,7 +13278,7 @@
       <c r="D99" s="33">
         <v>11400</v>
       </c>
-      <c r="J99" s="96" t="s">
+      <c r="J99" s="98" t="s">
         <v>76</v>
       </c>
       <c r="K99" s="45" t="s">
@@ -13280,7 +13296,7 @@
       <c r="P99" s="18">
         <v>9620</v>
       </c>
-      <c r="AD99" s="91" t="s">
+      <c r="AD99" s="93" t="s">
         <v>533</v>
       </c>
       <c r="AE99" s="7" t="s">
@@ -13290,7 +13306,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="100" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B100" s="30" t="s">
         <v>332</v>
       </c>
@@ -13300,7 +13316,7 @@
       <c r="D100" s="33">
         <v>11400</v>
       </c>
-      <c r="J100" s="93"/>
+      <c r="J100" s="95"/>
       <c r="K100" s="46" t="s">
         <v>561</v>
       </c>
@@ -13316,7 +13332,7 @@
       <c r="P100" s="18">
         <v>9620</v>
       </c>
-      <c r="AD100" s="93"/>
+      <c r="AD100" s="95"/>
       <c r="AE100" s="46" t="s">
         <v>582</v>
       </c>
@@ -13324,7 +13340,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="101" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B101" s="30" t="s">
         <v>333</v>
       </c>
@@ -13362,7 +13378,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="102" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B102" s="30" t="s">
         <v>334</v>
       </c>
@@ -13372,7 +13388,7 @@
       <c r="D102" s="33">
         <v>11400</v>
       </c>
-      <c r="J102" s="91" t="s">
+      <c r="J102" s="93" t="s">
         <v>83</v>
       </c>
       <c r="K102" s="7" t="s">
@@ -13381,18 +13397,18 @@
       <c r="L102" s="18">
         <v>10660</v>
       </c>
-      <c r="N102" s="84" t="s">
+      <c r="N102" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="O102" s="84"/>
-      <c r="P102" s="84"/>
-      <c r="AD102" s="104" t="s">
+      <c r="O102" s="86"/>
+      <c r="P102" s="86"/>
+      <c r="AD102" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="AE102" s="105"/>
-      <c r="AF102" s="106"/>
-    </row>
-    <row r="103" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AE102" s="107"/>
+      <c r="AF102" s="108"/>
+    </row>
+    <row r="103" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B103" s="30" t="s">
         <v>410</v>
       </c>
@@ -13402,7 +13418,7 @@
       <c r="D103" s="33">
         <v>11400</v>
       </c>
-      <c r="J103" s="92"/>
+      <c r="J103" s="94"/>
       <c r="K103" s="7" t="s">
         <v>560</v>
       </c>
@@ -13418,7 +13434,7 @@
       <c r="P103" s="18">
         <v>10400</v>
       </c>
-      <c r="AD103" s="91" t="s">
+      <c r="AD103" s="93" t="s">
         <v>114</v>
       </c>
       <c r="AE103" s="7" t="s">
@@ -13428,7 +13444,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="104" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B104" s="30" t="s">
         <v>411</v>
       </c>
@@ -13438,7 +13454,7 @@
       <c r="D104" s="33">
         <v>11400</v>
       </c>
-      <c r="J104" s="93"/>
+      <c r="J104" s="95"/>
       <c r="K104" s="46" t="s">
         <v>561</v>
       </c>
@@ -13454,7 +13470,7 @@
       <c r="P104" s="18">
         <v>10400</v>
       </c>
-      <c r="AD104" s="92"/>
+      <c r="AD104" s="94"/>
       <c r="AE104" s="7" t="s">
         <v>573</v>
       </c>
@@ -13462,7 +13478,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="105" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B105" s="30" t="s">
         <v>370</v>
       </c>
@@ -13481,7 +13497,7 @@
       <c r="L105" s="44">
         <v>10920</v>
       </c>
-      <c r="AD105" s="93"/>
+      <c r="AD105" s="95"/>
       <c r="AE105" s="46" t="s">
         <v>582</v>
       </c>
@@ -13489,7 +13505,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="106" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="106" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B106" s="30" t="s">
         <v>412</v>
       </c>
@@ -13499,7 +13515,7 @@
       <c r="D106" s="33">
         <v>11400</v>
       </c>
-      <c r="J106" s="92" t="s">
+      <c r="J106" s="94" t="s">
         <v>91</v>
       </c>
       <c r="K106" s="43" t="s">
@@ -13508,13 +13524,13 @@
       <c r="L106" s="44">
         <v>10660</v>
       </c>
-      <c r="AD106" s="100" t="s">
+      <c r="AD106" s="102" t="s">
         <v>535</v>
       </c>
-      <c r="AE106" s="101"/>
-      <c r="AF106" s="102"/>
-    </row>
-    <row r="107" spans="2:32" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AE106" s="103"/>
+      <c r="AF106" s="104"/>
+    </row>
+    <row r="107" spans="2:32" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="30" t="s">
         <v>413</v>
       </c>
@@ -13524,14 +13540,14 @@
       <c r="D107" s="33">
         <v>11400</v>
       </c>
-      <c r="J107" s="92"/>
+      <c r="J107" s="94"/>
       <c r="K107" s="43" t="s">
         <v>560</v>
       </c>
       <c r="L107" s="44">
         <v>8320</v>
       </c>
-      <c r="AD107" s="107" t="s">
+      <c r="AD107" s="109" t="s">
         <v>67</v>
       </c>
       <c r="AE107" s="7" t="s">
@@ -13541,7 +13557,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="108" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B108" s="30" t="s">
         <v>414</v>
       </c>
@@ -13551,14 +13567,14 @@
       <c r="D108" s="33">
         <v>11400</v>
       </c>
-      <c r="J108" s="93"/>
+      <c r="J108" s="95"/>
       <c r="K108" s="50" t="s">
         <v>561</v>
       </c>
       <c r="L108" s="51">
         <v>0</v>
       </c>
-      <c r="AD108" s="98"/>
+      <c r="AD108" s="100"/>
       <c r="AE108" s="7" t="s">
         <v>573</v>
       </c>
@@ -13566,7 +13582,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="109" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="109" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B109" s="30" t="s">
         <v>415</v>
       </c>
@@ -13576,7 +13592,7 @@
       <c r="D109" s="33">
         <v>11400</v>
       </c>
-      <c r="J109" s="96" t="s">
+      <c r="J109" s="98" t="s">
         <v>92</v>
       </c>
       <c r="K109" s="45" t="s">
@@ -13585,7 +13601,7 @@
       <c r="L109" s="48">
         <v>8320</v>
       </c>
-      <c r="AD109" s="98"/>
+      <c r="AD109" s="100"/>
       <c r="AE109" s="7" t="s">
         <v>582</v>
       </c>
@@ -13593,7 +13609,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="110" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B110" s="30" t="s">
         <v>416</v>
       </c>
@@ -13603,14 +13619,14 @@
       <c r="D110" s="33">
         <v>11400</v>
       </c>
-      <c r="J110" s="93"/>
+      <c r="J110" s="95"/>
       <c r="K110" s="50" t="s">
         <v>561</v>
       </c>
       <c r="L110" s="51">
         <v>0</v>
       </c>
-      <c r="AD110" s="99"/>
+      <c r="AD110" s="101"/>
       <c r="AE110" s="46" t="s">
         <v>570</v>
       </c>
@@ -13618,7 +13634,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="111" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="111" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B111" s="30" t="s">
         <v>417</v>
       </c>
@@ -13637,7 +13653,7 @@
       <c r="L111" s="44">
         <v>9100</v>
       </c>
-      <c r="AD111" s="96" t="s">
+      <c r="AD111" s="98" t="s">
         <v>536</v>
       </c>
       <c r="AE111" s="45" t="s">
@@ -13647,7 +13663,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="112" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="112" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B112" s="30" t="s">
         <v>418</v>
       </c>
@@ -13666,7 +13682,7 @@
       <c r="L112" s="18">
         <v>10660</v>
       </c>
-      <c r="AD112" s="92"/>
+      <c r="AD112" s="94"/>
       <c r="AE112" s="7" t="s">
         <v>573</v>
       </c>
@@ -13674,7 +13690,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="113" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="113" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B113" s="30" t="s">
         <v>419</v>
       </c>
@@ -13693,7 +13709,7 @@
       <c r="L113" s="54">
         <v>8320</v>
       </c>
-      <c r="AD113" s="92"/>
+      <c r="AD113" s="94"/>
       <c r="AE113" s="7" t="s">
         <v>582</v>
       </c>
@@ -13701,7 +13717,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="114" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B114" s="30" t="s">
         <v>420</v>
       </c>
@@ -13720,7 +13736,7 @@
       <c r="L114" s="18">
         <v>8320</v>
       </c>
-      <c r="AD114" s="93"/>
+      <c r="AD114" s="95"/>
       <c r="AE114" s="46" t="s">
         <v>570</v>
       </c>
@@ -13728,7 +13744,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="115" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="115" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B115" s="30" t="s">
         <v>421</v>
       </c>
@@ -13738,7 +13754,7 @@
       <c r="D115" s="33">
         <v>11400</v>
       </c>
-      <c r="J115" s="92" t="s">
+      <c r="J115" s="94" t="s">
         <v>102</v>
       </c>
       <c r="K115" s="43" t="s">
@@ -13757,7 +13773,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="116" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="116" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B116" s="30" t="s">
         <v>335</v>
       </c>
@@ -13767,7 +13783,7 @@
       <c r="D116" s="33">
         <v>11400</v>
       </c>
-      <c r="J116" s="92"/>
+      <c r="J116" s="94"/>
       <c r="K116" s="43" t="s">
         <v>562</v>
       </c>
@@ -13784,7 +13800,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="117" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B117" s="30" t="s">
         <v>281</v>
       </c>
@@ -13794,14 +13810,14 @@
       <c r="D117" s="33">
         <v>11400</v>
       </c>
-      <c r="J117" s="93"/>
+      <c r="J117" s="95"/>
       <c r="K117" s="50" t="s">
         <v>561</v>
       </c>
       <c r="L117" s="51">
         <v>0</v>
       </c>
-      <c r="AD117" s="91" t="s">
+      <c r="AD117" s="93" t="s">
         <v>115</v>
       </c>
       <c r="AE117" s="7" t="s">
@@ -13811,7 +13827,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="118" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="118" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B118" s="30" t="s">
         <v>422</v>
       </c>
@@ -13821,7 +13837,7 @@
       <c r="D118" s="33">
         <v>11400</v>
       </c>
-      <c r="J118" s="96" t="s">
+      <c r="J118" s="98" t="s">
         <v>103</v>
       </c>
       <c r="K118" s="45" t="s">
@@ -13830,7 +13846,7 @@
       <c r="L118" s="48">
         <v>10660</v>
       </c>
-      <c r="AD118" s="92"/>
+      <c r="AD118" s="94"/>
       <c r="AE118" s="7" t="s">
         <v>573</v>
       </c>
@@ -13838,7 +13854,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="119" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="119" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B119" s="30" t="s">
         <v>336</v>
       </c>
@@ -13848,14 +13864,14 @@
       <c r="D119" s="33">
         <v>11400</v>
       </c>
-      <c r="J119" s="92"/>
+      <c r="J119" s="94"/>
       <c r="K119" s="43" t="s">
         <v>560</v>
       </c>
       <c r="L119" s="44">
         <v>8320</v>
       </c>
-      <c r="AD119" s="92"/>
+      <c r="AD119" s="94"/>
       <c r="AE119" s="7" t="s">
         <v>582</v>
       </c>
@@ -13863,7 +13879,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="120" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B120" s="30" t="s">
         <v>337</v>
       </c>
@@ -13873,14 +13889,14 @@
       <c r="D120" s="33">
         <v>11400</v>
       </c>
-      <c r="J120" s="93"/>
+      <c r="J120" s="95"/>
       <c r="K120" s="50" t="s">
         <v>561</v>
       </c>
       <c r="L120" s="51">
         <v>0</v>
       </c>
-      <c r="AD120" s="93"/>
+      <c r="AD120" s="95"/>
       <c r="AE120" s="46" t="s">
         <v>570</v>
       </c>
@@ -13888,7 +13904,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="121" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="121" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B121" s="30" t="s">
         <v>338</v>
       </c>
@@ -13907,7 +13923,7 @@
       <c r="L121" s="44">
         <v>8320</v>
       </c>
-      <c r="AD121" s="96" t="s">
+      <c r="AD121" s="98" t="s">
         <v>538</v>
       </c>
       <c r="AE121" s="45" t="s">
@@ -13917,7 +13933,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="122" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="122" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B122" s="30" t="s">
         <v>339</v>
       </c>
@@ -13927,7 +13943,7 @@
       <c r="D122" s="33">
         <v>11400</v>
       </c>
-      <c r="J122" s="92" t="s">
+      <c r="J122" s="94" t="s">
         <v>107</v>
       </c>
       <c r="K122" s="43" t="s">
@@ -13936,7 +13952,7 @@
       <c r="L122" s="44">
         <v>10660</v>
       </c>
-      <c r="AD122" s="92"/>
+      <c r="AD122" s="94"/>
       <c r="AE122" s="7" t="s">
         <v>582</v>
       </c>
@@ -13944,7 +13960,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="123" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B123" s="30" t="s">
         <v>423</v>
       </c>
@@ -13954,14 +13970,14 @@
       <c r="D123" s="33">
         <v>11400</v>
       </c>
-      <c r="J123" s="92"/>
+      <c r="J123" s="94"/>
       <c r="K123" s="7" t="s">
         <v>560</v>
       </c>
       <c r="L123" s="18">
         <v>8320</v>
       </c>
-      <c r="AD123" s="93"/>
+      <c r="AD123" s="95"/>
       <c r="AE123" s="46" t="s">
         <v>570</v>
       </c>
@@ -13969,7 +13985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="30" t="s">
         <v>424</v>
       </c>
@@ -13979,14 +13995,14 @@
       <c r="D124" s="33">
         <v>11400</v>
       </c>
-      <c r="J124" s="93"/>
+      <c r="J124" s="95"/>
       <c r="K124" s="46" t="s">
         <v>561</v>
       </c>
       <c r="L124" s="47">
         <v>0</v>
       </c>
-      <c r="AD124" s="96" t="s">
+      <c r="AD124" s="98" t="s">
         <v>539</v>
       </c>
       <c r="AE124" s="45" t="s">
@@ -13996,7 +14012,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="125" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="125" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B125" s="30" t="s">
         <v>425</v>
       </c>
@@ -14006,7 +14022,7 @@
       <c r="D125" s="33">
         <v>11400</v>
       </c>
-      <c r="J125" s="96" t="s">
+      <c r="J125" s="98" t="s">
         <v>108</v>
       </c>
       <c r="K125" s="45" t="s">
@@ -14015,7 +14031,7 @@
       <c r="L125" s="48">
         <v>10660</v>
       </c>
-      <c r="AD125" s="92"/>
+      <c r="AD125" s="94"/>
       <c r="AE125" s="7" t="s">
         <v>573</v>
       </c>
@@ -14023,7 +14039,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="126" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="126" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B126" s="30" t="s">
         <v>426</v>
       </c>
@@ -14033,14 +14049,14 @@
       <c r="D126" s="33">
         <v>11400</v>
       </c>
-      <c r="J126" s="92"/>
+      <c r="J126" s="94"/>
       <c r="K126" s="7" t="s">
         <v>560</v>
       </c>
       <c r="L126" s="44">
         <v>8320</v>
       </c>
-      <c r="AD126" s="92"/>
+      <c r="AD126" s="94"/>
       <c r="AE126" s="7" t="s">
         <v>582</v>
       </c>
@@ -14048,7 +14064,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="127" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B127" s="30" t="s">
         <v>376</v>
       </c>
@@ -14058,14 +14074,14 @@
       <c r="D127" s="33">
         <v>11400</v>
       </c>
-      <c r="J127" s="93"/>
+      <c r="J127" s="95"/>
       <c r="K127" s="46" t="s">
         <v>561</v>
       </c>
       <c r="L127" s="51">
         <v>0</v>
       </c>
-      <c r="AD127" s="93"/>
+      <c r="AD127" s="95"/>
       <c r="AE127" s="46" t="s">
         <v>570</v>
       </c>
@@ -14073,7 +14089,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="128" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="128" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B128" s="30" t="s">
         <v>427</v>
       </c>
@@ -14092,13 +14108,13 @@
       <c r="L128" s="44">
         <v>8320</v>
       </c>
-      <c r="AD128" s="103" t="s">
+      <c r="AD128" s="105" t="s">
         <v>540</v>
       </c>
-      <c r="AE128" s="103"/>
-      <c r="AF128" s="103"/>
-    </row>
-    <row r="129" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AE128" s="105"/>
+      <c r="AF128" s="105"/>
+    </row>
+    <row r="129" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B129" s="30" t="s">
         <v>340</v>
       </c>
@@ -14108,7 +14124,7 @@
       <c r="D129" s="33">
         <v>11400</v>
       </c>
-      <c r="J129" s="92" t="s">
+      <c r="J129" s="94" t="s">
         <v>115</v>
       </c>
       <c r="K129" s="43" t="s">
@@ -14127,7 +14143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B130" s="30" t="s">
         <v>341</v>
       </c>
@@ -14137,14 +14153,14 @@
       <c r="D130" s="33">
         <v>11400</v>
       </c>
-      <c r="J130" s="93"/>
+      <c r="J130" s="95"/>
       <c r="K130" s="50" t="s">
         <v>560</v>
       </c>
       <c r="L130" s="51">
         <v>8320</v>
       </c>
-      <c r="AD130" s="91" t="s">
+      <c r="AD130" s="93" t="s">
         <v>519</v>
       </c>
       <c r="AE130" s="7" t="s">
@@ -14154,7 +14170,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="131" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B131" s="30" t="s">
         <v>342</v>
       </c>
@@ -14173,7 +14189,7 @@
       <c r="L131" s="44">
         <v>8320</v>
       </c>
-      <c r="AD131" s="92"/>
+      <c r="AD131" s="94"/>
       <c r="AE131" s="7" t="s">
         <v>573</v>
       </c>
@@ -14181,7 +14197,7 @@
         <v>9360</v>
       </c>
     </row>
-    <row r="132" spans="2:32" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B132" s="30" t="s">
         <v>343</v>
       </c>
@@ -14191,7 +14207,7 @@
       <c r="D132" s="33">
         <v>11400</v>
       </c>
-      <c r="AD132" s="93"/>
+      <c r="AD132" s="95"/>
       <c r="AE132" s="46" t="s">
         <v>582</v>
       </c>
@@ -14199,7 +14215,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="133" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B133" s="30" t="s">
         <v>428</v>
       </c>
@@ -14219,7 +14235,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="134" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B134" s="30" t="s">
         <v>344</v>
       </c>
@@ -14229,13 +14245,13 @@
       <c r="D134" s="33">
         <v>11400</v>
       </c>
-      <c r="AD134" s="95" t="s">
+      <c r="AD134" s="97" t="s">
         <v>543</v>
       </c>
-      <c r="AE134" s="95"/>
-      <c r="AF134" s="95"/>
-    </row>
-    <row r="135" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AE134" s="97"/>
+      <c r="AF134" s="97"/>
+    </row>
+    <row r="135" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B135" s="30" t="s">
         <v>429</v>
       </c>
@@ -14245,7 +14261,7 @@
       <c r="D135" s="33">
         <v>11400</v>
       </c>
-      <c r="AD135" s="91" t="s">
+      <c r="AD135" s="93" t="s">
         <v>544</v>
       </c>
       <c r="AE135" s="7" t="s">
@@ -14255,7 +14271,7 @@
         <v>8138</v>
       </c>
     </row>
-    <row r="136" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B136" s="30" t="s">
         <v>55</v>
       </c>
@@ -14265,7 +14281,7 @@
       <c r="D136" s="33">
         <v>11400</v>
       </c>
-      <c r="AD136" s="94"/>
+      <c r="AD136" s="96"/>
       <c r="AE136" s="39" t="s">
         <v>582</v>
       </c>
@@ -14273,7 +14289,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="137" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B137" s="30" t="s">
         <v>379</v>
       </c>
@@ -14284,7 +14300,7 @@
         <v>11400</v>
       </c>
     </row>
-    <row r="138" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B138" s="30" t="s">
         <v>430</v>
       </c>
@@ -14295,7 +14311,7 @@
         <v>11400</v>
       </c>
     </row>
-    <row r="139" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B139" s="30" t="s">
         <v>431</v>
       </c>
@@ -14306,14 +14322,14 @@
         <v>11400</v>
       </c>
     </row>
-    <row r="140" spans="2:32" x14ac:dyDescent="0.2">
-      <c r="B140" s="81" t="s">
+    <row r="140" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B140" s="83" t="s">
         <v>551</v>
       </c>
-      <c r="C140" s="82"/>
-      <c r="D140" s="83"/>
-    </row>
-    <row r="141" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="C140" s="84"/>
+      <c r="D140" s="85"/>
+    </row>
+    <row r="141" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B141" s="37" t="s">
         <v>552</v>
       </c>
@@ -14324,7 +14340,7 @@
         <v>11400</v>
       </c>
     </row>
-    <row r="142" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B142" s="37" t="s">
         <v>553</v>
       </c>
@@ -14335,7 +14351,7 @@
         <v>11400</v>
       </c>
     </row>
-    <row r="143" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B143" s="37" t="s">
         <v>554</v>
       </c>
@@ -14348,16 +14364,6 @@
     </row>
   </sheetData>
   <mergeCells count="182">
-    <mergeCell ref="R82:R83"/>
-    <mergeCell ref="R84:R85"/>
-    <mergeCell ref="R86:R88"/>
-    <mergeCell ref="R61:R64"/>
-    <mergeCell ref="R89:R90"/>
-    <mergeCell ref="R66:R67"/>
-    <mergeCell ref="R71:R73"/>
-    <mergeCell ref="R75:R76"/>
-    <mergeCell ref="R77:R78"/>
-    <mergeCell ref="R80:R81"/>
     <mergeCell ref="R38:R40"/>
     <mergeCell ref="R44:R45"/>
     <mergeCell ref="R46:R52"/>
@@ -14382,7 +14388,6 @@
     <mergeCell ref="N61:P61"/>
     <mergeCell ref="N70:P70"/>
     <mergeCell ref="N73:P73"/>
-    <mergeCell ref="N82:P82"/>
     <mergeCell ref="O5:P5"/>
     <mergeCell ref="N7:P7"/>
     <mergeCell ref="N18:P18"/>
@@ -14417,7 +14422,6 @@
     <mergeCell ref="J8:J10"/>
     <mergeCell ref="J11:J13"/>
     <mergeCell ref="J32:J34"/>
-    <mergeCell ref="J102:J104"/>
     <mergeCell ref="J37:J38"/>
     <mergeCell ref="J44:J45"/>
     <mergeCell ref="J46:J47"/>
@@ -14435,9 +14439,7 @@
     <mergeCell ref="J65:J67"/>
     <mergeCell ref="J68:J69"/>
     <mergeCell ref="J77:J80"/>
-    <mergeCell ref="J99:J100"/>
     <mergeCell ref="J93:L93"/>
-    <mergeCell ref="J125:J127"/>
     <mergeCell ref="J82:J84"/>
     <mergeCell ref="J70:J71"/>
     <mergeCell ref="J87:J90"/>
@@ -14446,6 +14448,19 @@
     <mergeCell ref="J59:J60"/>
     <mergeCell ref="J57:J58"/>
     <mergeCell ref="Z42:Z43"/>
+    <mergeCell ref="J102:J104"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R82:R83"/>
+    <mergeCell ref="R84:R85"/>
+    <mergeCell ref="R86:R88"/>
+    <mergeCell ref="R61:R64"/>
+    <mergeCell ref="R89:R90"/>
+    <mergeCell ref="R66:R67"/>
+    <mergeCell ref="R71:R73"/>
+    <mergeCell ref="R75:R76"/>
+    <mergeCell ref="R77:R78"/>
+    <mergeCell ref="R80:R81"/>
     <mergeCell ref="J129:J130"/>
     <mergeCell ref="J91:J92"/>
     <mergeCell ref="J115:J117"/>
@@ -14469,6 +14484,7 @@
     <mergeCell ref="J109:J110"/>
     <mergeCell ref="J74:J75"/>
     <mergeCell ref="J51:J52"/>
+    <mergeCell ref="J125:J127"/>
     <mergeCell ref="AD93:AF93"/>
     <mergeCell ref="AD98:AF98"/>
     <mergeCell ref="AD102:AF102"/>

--- a/resources/Data/University Fees.xlsx
+++ b/resources/Data/University Fees.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Financial Calculator\resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2456CE-AADB-4A33-BA9F-7513D93D8D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521066F2-8F0C-4BD7-8FD0-16A2591786B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46335" yWindow="1995" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{9076E21E-61F9-4A5A-ABD0-5DFDD0B945A9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{9076E21E-61F9-4A5A-ABD0-5DFDD0B945A9}"/>
+    <workbookView xWindow="7545" yWindow="1695" windowWidth="21600" windowHeight="11385" xr2:uid="{ADD0AE33-0E96-45FA-8680-34EE88D7AD79}"/>
   </bookViews>
   <sheets>
     <sheet name="Tuition Fees" sheetId="1" r:id="rId1"/>
@@ -2358,7 +2359,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2367,23 +2368,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2397,32 +2386,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2451,6 +2416,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2459,6 +2448,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7909,74 +7910,6 @@
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="AG50:AI50"/>
-    <mergeCell ref="AG58:AI58"/>
-    <mergeCell ref="AG62:AI62"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AG35:AI35"/>
-    <mergeCell ref="AG42:AI42"/>
-    <mergeCell ref="AG45:AI45"/>
-    <mergeCell ref="AG48:AI48"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AG6:AI6"/>
-    <mergeCell ref="AG12:AI12"/>
-    <mergeCell ref="AG17:AI17"/>
-    <mergeCell ref="AG22:AI22"/>
-    <mergeCell ref="AC28:AE28"/>
-    <mergeCell ref="AC36:AE36"/>
-    <mergeCell ref="AC46:AE46"/>
-    <mergeCell ref="AC51:AE51"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="U32:W32"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="AC6:AE6"/>
-    <mergeCell ref="AC17:AE17"/>
-    <mergeCell ref="AC19:AE19"/>
-    <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="F2:N2"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="E15:G15"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="Q6:S6"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="Q87:S87"/>
-    <mergeCell ref="Q101:S101"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="Y24:AA24"/>
-    <mergeCell ref="Y27:AA27"/>
-    <mergeCell ref="Q81:S81"/>
-    <mergeCell ref="Q28:S28"/>
-    <mergeCell ref="Q39:S39"/>
-    <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="Q69:S69"/>
-    <mergeCell ref="Q72:S72"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="U6:W6"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="U19:W19"/>
-    <mergeCell ref="U24:W24"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="Y6:AA6"/>
-    <mergeCell ref="Y8:AA8"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="Y13:AA13"/>
     <mergeCell ref="E139:G139"/>
     <mergeCell ref="Y37:AA37"/>
     <mergeCell ref="Y44:AA44"/>
@@ -7993,6 +7926,74 @@
     <mergeCell ref="E71:G71"/>
     <mergeCell ref="E84:G84"/>
     <mergeCell ref="E92:G92"/>
+    <mergeCell ref="Z4:AA4"/>
+    <mergeCell ref="Y6:AA6"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="U24:W24"/>
+    <mergeCell ref="Q87:S87"/>
+    <mergeCell ref="Q101:S101"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="Y24:AA24"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="Q81:S81"/>
+    <mergeCell ref="Q28:S28"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="Q69:S69"/>
+    <mergeCell ref="Q72:S72"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="Q6:S6"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="F2:N2"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="AC6:AE6"/>
+    <mergeCell ref="AC17:AE17"/>
+    <mergeCell ref="AC19:AE19"/>
+    <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="AC28:AE28"/>
+    <mergeCell ref="AC36:AE36"/>
+    <mergeCell ref="AC46:AE46"/>
+    <mergeCell ref="AC51:AE51"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="U32:W32"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AG6:AI6"/>
+    <mergeCell ref="AG12:AI12"/>
+    <mergeCell ref="AG17:AI17"/>
+    <mergeCell ref="AG22:AI22"/>
+    <mergeCell ref="AG50:AI50"/>
+    <mergeCell ref="AG58:AI58"/>
+    <mergeCell ref="AG62:AI62"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AG35:AI35"/>
+    <mergeCell ref="AG42:AI42"/>
+    <mergeCell ref="AG45:AI45"/>
+    <mergeCell ref="AG48:AI48"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8049,11 +8050,11 @@
       <c r="D4" s="26"/>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B5" s="115"/>
-      <c r="C5" s="117" t="s">
+      <c r="B5" s="103"/>
+      <c r="C5" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="118"/>
+      <c r="D5" s="106"/>
       <c r="F5" s="1"/>
       <c r="G5" s="89" t="s">
         <v>20</v>
@@ -8070,7 +8071,7 @@
       <c r="P5" s="87"/>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B6" s="116"/>
+      <c r="B6" s="104"/>
       <c r="C6" s="28" t="s">
         <v>547</v>
       </c>
@@ -8119,21 +8120,21 @@
       <c r="AF6" s="87"/>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="119"/>
-      <c r="D7" s="118"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="106"/>
       <c r="F7" s="86" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="86"/>
       <c r="H7" s="86"/>
-      <c r="J7" s="106" t="s">
+      <c r="J7" s="112" t="s">
         <v>121</v>
       </c>
-      <c r="K7" s="107"/>
-      <c r="L7" s="108"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="114"/>
       <c r="N7" s="86" t="s">
         <v>186</v>
       </c>
@@ -8288,7 +8289,7 @@
       <c r="AB9" s="18">
         <v>11440</v>
       </c>
-      <c r="AD9" s="93" t="s">
+      <c r="AD9" s="96" t="s">
         <v>95</v>
       </c>
       <c r="AE9" s="7" t="s">
@@ -8333,7 +8334,7 @@
       <c r="P10" s="18">
         <v>10400</v>
       </c>
-      <c r="R10" s="93" t="s">
+      <c r="R10" s="96" t="s">
         <v>6</v>
       </c>
       <c r="S10" s="4" t="s">
@@ -8383,7 +8384,7 @@
       <c r="H11" s="4">
         <v>9490</v>
       </c>
-      <c r="J11" s="98" t="s">
+      <c r="J11" s="93" t="s">
         <v>65</v>
       </c>
       <c r="K11" s="45" t="s">
@@ -8587,7 +8588,7 @@
       <c r="H14" s="4">
         <v>10400</v>
       </c>
-      <c r="J14" s="98" t="s">
+      <c r="J14" s="93" t="s">
         <v>66</v>
       </c>
       <c r="K14" s="45" t="s">
@@ -8630,7 +8631,7 @@
       <c r="AB14" s="18">
         <v>11440</v>
       </c>
-      <c r="AD14" s="93" t="s">
+      <c r="AD14" s="96" t="s">
         <v>508</v>
       </c>
       <c r="AE14" s="7" t="s">
@@ -8707,11 +8708,11 @@
       </c>
     </row>
     <row r="16" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="120" t="s">
+      <c r="B16" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="121"/>
-      <c r="D16" s="122"/>
+      <c r="C16" s="109"/>
+      <c r="D16" s="110"/>
       <c r="F16" s="10" t="s">
         <v>31</v>
       </c>
@@ -8764,11 +8765,11 @@
       <c r="AB16" s="18">
         <v>11440</v>
       </c>
-      <c r="AD16" s="102" t="s">
+      <c r="AD16" s="98" t="s">
         <v>509</v>
       </c>
-      <c r="AE16" s="103"/>
-      <c r="AF16" s="104"/>
+      <c r="AE16" s="99"/>
+      <c r="AF16" s="100"/>
     </row>
     <row r="17" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B17" s="30" t="s">
@@ -8830,7 +8831,7 @@
       <c r="AB17" s="18">
         <v>11440</v>
       </c>
-      <c r="AD17" s="93" t="s">
+      <c r="AD17" s="96" t="s">
         <v>6</v>
       </c>
       <c r="AE17" s="7" t="s">
@@ -8889,7 +8890,7 @@
       <c r="X18" s="18">
         <v>15210</v>
       </c>
-      <c r="Z18" s="93" t="s">
+      <c r="Z18" s="96" t="s">
         <v>481</v>
       </c>
       <c r="AA18" s="7" t="s">
@@ -8925,7 +8926,7 @@
       <c r="H19" s="4">
         <v>9490</v>
       </c>
-      <c r="J19" s="98" t="s">
+      <c r="J19" s="93" t="s">
         <v>73</v>
       </c>
       <c r="K19" s="45" t="s">
@@ -9029,11 +9030,11 @@
       <c r="X20" s="18">
         <v>15210</v>
       </c>
-      <c r="Z20" s="105" t="s">
+      <c r="Z20" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="AA20" s="105"/>
-      <c r="AB20" s="105"/>
+      <c r="AA20" s="101"/>
+      <c r="AB20" s="101"/>
       <c r="AD20" s="95"/>
       <c r="AE20" s="46" t="s">
         <v>570</v>
@@ -9087,7 +9088,7 @@
       </c>
       <c r="W21" s="86"/>
       <c r="X21" s="86"/>
-      <c r="Z21" s="93" t="s">
+      <c r="Z21" s="96" t="s">
         <v>68</v>
       </c>
       <c r="AA21" s="74" t="s">
@@ -9096,7 +9097,7 @@
       <c r="AB21" s="18">
         <v>10400</v>
       </c>
-      <c r="AD21" s="98" t="s">
+      <c r="AD21" s="93" t="s">
         <v>510</v>
       </c>
       <c r="AE21" s="45" t="s">
@@ -9125,7 +9126,7 @@
       <c r="H22" s="4">
         <v>9360</v>
       </c>
-      <c r="J22" s="98" t="s">
+      <c r="J22" s="93" t="s">
         <v>74</v>
       </c>
       <c r="K22" s="45" t="s">
@@ -9143,7 +9144,7 @@
       <c r="P22" s="18">
         <v>9620</v>
       </c>
-      <c r="R22" s="93" t="s">
+      <c r="R22" s="96" t="s">
         <v>218</v>
       </c>
       <c r="S22" s="4" t="s">
@@ -9227,11 +9228,11 @@
       <c r="X23" s="18">
         <v>15210</v>
       </c>
-      <c r="Z23" s="102" t="s">
+      <c r="Z23" s="98" t="s">
         <v>482</v>
       </c>
-      <c r="AA23" s="103"/>
-      <c r="AB23" s="104"/>
+      <c r="AA23" s="99"/>
+      <c r="AB23" s="100"/>
       <c r="AD23" s="95"/>
       <c r="AE23" s="46" t="s">
         <v>582</v>
@@ -9300,7 +9301,7 @@
       <c r="AB24" s="18">
         <v>11440</v>
       </c>
-      <c r="AD24" s="98" t="s">
+      <c r="AD24" s="93" t="s">
         <v>511</v>
       </c>
       <c r="AE24" s="45" t="s">
@@ -9329,7 +9330,7 @@
       <c r="H25" s="4">
         <v>9490</v>
       </c>
-      <c r="J25" s="98" t="s">
+      <c r="J25" s="93" t="s">
         <v>75</v>
       </c>
       <c r="K25" s="45" t="s">
@@ -9415,7 +9416,7 @@
       <c r="P26" s="18">
         <v>10400</v>
       </c>
-      <c r="R26" s="98" t="s">
+      <c r="R26" s="93" t="s">
         <v>68</v>
       </c>
       <c r="S26" s="64" t="s">
@@ -9568,7 +9569,7 @@
       <c r="AB28" s="18">
         <v>11440</v>
       </c>
-      <c r="AD28" s="98" t="s">
+      <c r="AD28" s="93" t="s">
         <v>512</v>
       </c>
       <c r="AE28" s="45" t="s">
@@ -9691,7 +9692,7 @@
       <c r="X30" s="18">
         <v>15210</v>
       </c>
-      <c r="Z30" s="93" t="s">
+      <c r="Z30" s="96" t="s">
         <v>485</v>
       </c>
       <c r="AA30" s="7" t="s">
@@ -9793,7 +9794,7 @@
       </c>
       <c r="G32" s="86"/>
       <c r="H32" s="86"/>
-      <c r="J32" s="98" t="s">
+      <c r="J32" s="93" t="s">
         <v>82</v>
       </c>
       <c r="K32" s="45" t="s">
@@ -9834,11 +9835,11 @@
       <c r="AB32" s="44">
         <v>11440</v>
       </c>
-      <c r="AD32" s="102" t="s">
+      <c r="AD32" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="AE32" s="103"/>
-      <c r="AF32" s="104"/>
+      <c r="AE32" s="99"/>
+      <c r="AF32" s="100"/>
     </row>
     <row r="33" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B33" s="30" t="s">
@@ -9875,7 +9876,7 @@
       <c r="P33" s="18">
         <v>10400</v>
       </c>
-      <c r="R33" s="93" t="s">
+      <c r="R33" s="96" t="s">
         <v>89</v>
       </c>
       <c r="S33" s="4" t="s">
@@ -9943,7 +9944,7 @@
       <c r="P34" s="18">
         <v>10400</v>
       </c>
-      <c r="R34" s="96"/>
+      <c r="R34" s="102"/>
       <c r="S34" s="4" t="s">
         <v>571</v>
       </c>
@@ -9968,7 +9969,7 @@
       <c r="AB34" s="76">
         <v>11440</v>
       </c>
-      <c r="AD34" s="93" t="s">
+      <c r="AD34" s="96" t="s">
         <v>68</v>
       </c>
       <c r="AE34" s="7" t="s">
@@ -10011,7 +10012,7 @@
       <c r="P35" s="18">
         <v>14040</v>
       </c>
-      <c r="R35" s="93" t="s">
+      <c r="R35" s="96" t="s">
         <v>90</v>
       </c>
       <c r="S35" s="4" t="s">
@@ -10131,7 +10132,7 @@
       </c>
       <c r="G37" s="86"/>
       <c r="H37" s="86"/>
-      <c r="J37" s="93" t="s">
+      <c r="J37" s="96" t="s">
         <v>87</v>
       </c>
       <c r="K37" s="7" t="s">
@@ -10217,7 +10218,7 @@
       <c r="P38" s="18">
         <v>10400</v>
       </c>
-      <c r="R38" s="98" t="s">
+      <c r="R38" s="93" t="s">
         <v>220</v>
       </c>
       <c r="S38" s="64" t="s">
@@ -10244,7 +10245,7 @@
       <c r="AB38" s="76">
         <v>11440</v>
       </c>
-      <c r="AD38" s="98" t="s">
+      <c r="AD38" s="93" t="s">
         <v>514</v>
       </c>
       <c r="AE38" s="45" t="s">
@@ -10501,7 +10502,7 @@
       <c r="X42" s="18">
         <v>15210</v>
       </c>
-      <c r="Z42" s="93" t="s">
+      <c r="Z42" s="96" t="s">
         <v>494</v>
       </c>
       <c r="AA42" s="7" t="s">
@@ -10510,7 +10511,7 @@
       <c r="AB42" s="18">
         <v>11440</v>
       </c>
-      <c r="AD42" s="99" t="s">
+      <c r="AD42" s="126" t="s">
         <v>515</v>
       </c>
       <c r="AE42" s="45" t="s">
@@ -10539,11 +10540,11 @@
       <c r="H43" s="18">
         <v>9360</v>
       </c>
-      <c r="J43" s="112" t="s">
+      <c r="J43" s="115" t="s">
         <v>122</v>
       </c>
-      <c r="K43" s="113"/>
-      <c r="L43" s="114"/>
+      <c r="K43" s="116"/>
+      <c r="L43" s="117"/>
       <c r="N43" s="10" t="s">
         <v>110</v>
       </c>
@@ -10578,7 +10579,7 @@
       <c r="AB43" s="47">
         <v>8580</v>
       </c>
-      <c r="AD43" s="100"/>
+      <c r="AD43" s="124"/>
       <c r="AE43" s="7" t="s">
         <v>573</v>
       </c>
@@ -10623,7 +10624,7 @@
       <c r="P44" s="18">
         <v>9620</v>
       </c>
-      <c r="R44" s="93" t="s">
+      <c r="R44" s="96" t="s">
         <v>99</v>
       </c>
       <c r="S44" s="4" t="s">
@@ -10650,7 +10651,7 @@
       <c r="AB44" s="44">
         <v>8580</v>
       </c>
-      <c r="AD44" s="100"/>
+      <c r="AD44" s="124"/>
       <c r="AE44" s="7" t="s">
         <v>582</v>
       </c>
@@ -10709,7 +10710,7 @@
       <c r="X45" s="18">
         <v>15210</v>
       </c>
-      <c r="Z45" s="93" t="s">
+      <c r="Z45" s="96" t="s">
         <v>7</v>
       </c>
       <c r="AA45" s="7" t="s">
@@ -10718,7 +10719,7 @@
       <c r="AB45" s="18">
         <v>11440</v>
       </c>
-      <c r="AD45" s="101"/>
+      <c r="AD45" s="125"/>
       <c r="AE45" s="46" t="s">
         <v>570</v>
       </c>
@@ -10745,7 +10746,7 @@
       <c r="H46" s="18">
         <v>10400</v>
       </c>
-      <c r="J46" s="98" t="s">
+      <c r="J46" s="93" t="s">
         <v>89</v>
       </c>
       <c r="K46" s="7" t="s">
@@ -10759,7 +10760,7 @@
       </c>
       <c r="O46" s="84"/>
       <c r="P46" s="85"/>
-      <c r="R46" s="98" t="s">
+      <c r="R46" s="93" t="s">
         <v>110</v>
       </c>
       <c r="S46" s="64" t="s">
@@ -10780,11 +10781,11 @@
       <c r="AB46" s="47">
         <v>8580</v>
       </c>
-      <c r="AD46" s="102" t="s">
+      <c r="AD46" s="98" t="s">
         <v>516</v>
       </c>
-      <c r="AE46" s="103"/>
-      <c r="AF46" s="104"/>
+      <c r="AE46" s="99"/>
+      <c r="AF46" s="100"/>
     </row>
     <row r="47" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B47" s="30" t="s">
@@ -10828,7 +10829,7 @@
       <c r="T47" s="44">
         <v>8320</v>
       </c>
-      <c r="V47" s="93" t="s">
+      <c r="V47" s="96" t="s">
         <v>110</v>
       </c>
       <c r="W47" s="69" t="s">
@@ -10846,7 +10847,7 @@
       <c r="AB47" s="44">
         <v>10400</v>
       </c>
-      <c r="AD47" s="93" t="s">
+      <c r="AD47" s="96" t="s">
         <v>247</v>
       </c>
       <c r="AE47" s="7" t="s">
@@ -10875,7 +10876,7 @@
       <c r="H48" s="18">
         <v>9490</v>
       </c>
-      <c r="J48" s="98" t="s">
+      <c r="J48" s="93" t="s">
         <v>90</v>
       </c>
       <c r="K48" s="45" t="s">
@@ -10925,11 +10926,11 @@
       </c>
     </row>
     <row r="49" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B49" s="120" t="s">
+      <c r="B49" s="108" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="121"/>
-      <c r="D49" s="122"/>
+      <c r="C49" s="109"/>
+      <c r="D49" s="110"/>
       <c r="F49" s="86" t="s">
         <v>59</v>
       </c>
@@ -11071,7 +11072,7 @@
       <c r="H51" s="18">
         <v>11400</v>
       </c>
-      <c r="J51" s="98" t="s">
+      <c r="J51" s="93" t="s">
         <v>101</v>
       </c>
       <c r="K51" s="45" t="s">
@@ -11110,7 +11111,7 @@
       <c r="AB51" s="18">
         <v>8580</v>
       </c>
-      <c r="AD51" s="98" t="s">
+      <c r="AD51" s="93" t="s">
         <v>163</v>
       </c>
       <c r="AE51" s="45" t="s">
@@ -11218,7 +11219,7 @@
       <c r="P53" s="18">
         <v>10400</v>
       </c>
-      <c r="R53" s="98" t="s">
+      <c r="R53" s="93" t="s">
         <v>223</v>
       </c>
       <c r="S53" s="64" t="s">
@@ -11379,7 +11380,7 @@
       <c r="AB55" s="4">
         <v>11440</v>
       </c>
-      <c r="AD55" s="98" t="s">
+      <c r="AD55" s="93" t="s">
         <v>90</v>
       </c>
       <c r="AE55" s="45" t="s">
@@ -11415,7 +11416,7 @@
       <c r="P56" s="18">
         <v>10400</v>
       </c>
-      <c r="R56" s="93" t="s">
+      <c r="R56" s="96" t="s">
         <v>224</v>
       </c>
       <c r="S56" s="4" t="s">
@@ -11457,7 +11458,7 @@
       <c r="D57" s="33">
         <v>11400</v>
       </c>
-      <c r="J57" s="98" t="s">
+      <c r="J57" s="93" t="s">
         <v>69</v>
       </c>
       <c r="K57" s="45" t="s">
@@ -11555,7 +11556,7 @@
       </c>
       <c r="AA58" s="97"/>
       <c r="AB58" s="97"/>
-      <c r="AD58" s="98" t="s">
+      <c r="AD58" s="93" t="s">
         <v>485</v>
       </c>
       <c r="AE58" s="45" t="s">
@@ -11575,7 +11576,7 @@
       <c r="D59" s="33">
         <v>11400</v>
       </c>
-      <c r="J59" s="98" t="s">
+      <c r="J59" s="93" t="s">
         <v>70</v>
       </c>
       <c r="K59" s="45" t="s">
@@ -11609,7 +11610,7 @@
       <c r="X59" s="18">
         <v>15210</v>
       </c>
-      <c r="Z59" s="93" t="str">
+      <c r="Z59" s="96" t="str">
         <f>Z42</f>
         <v>Bachelor of Biomedical and Exercise Science</v>
       </c>
@@ -11685,7 +11686,7 @@
       <c r="D61" s="33">
         <v>11400</v>
       </c>
-      <c r="J61" s="98" t="s">
+      <c r="J61" s="93" t="s">
         <v>8</v>
       </c>
       <c r="K61" s="45" t="s">
@@ -11699,7 +11700,7 @@
       </c>
       <c r="O61" s="86"/>
       <c r="P61" s="86"/>
-      <c r="R61" s="98" t="s">
+      <c r="R61" s="93" t="s">
         <v>225</v>
       </c>
       <c r="S61" s="66" t="s">
@@ -11717,7 +11718,7 @@
       <c r="AB61" s="44">
         <v>11440</v>
       </c>
-      <c r="AD61" s="98" t="s">
+      <c r="AD61" s="93" t="s">
         <v>517</v>
       </c>
       <c r="AE61" s="45" t="s">
@@ -11869,7 +11870,7 @@
       <c r="AB64" s="44">
         <v>11440</v>
       </c>
-      <c r="AD64" s="98" t="s">
+      <c r="AD64" s="93" t="s">
         <v>518</v>
       </c>
       <c r="AE64" s="45" t="s">
@@ -11880,12 +11881,12 @@
       </c>
     </row>
     <row r="65" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B65" s="120" t="s">
+      <c r="B65" s="108" t="s">
         <v>8</v>
       </c>
-      <c r="C65" s="121"/>
-      <c r="D65" s="122"/>
-      <c r="J65" s="98" t="s">
+      <c r="C65" s="109"/>
+      <c r="D65" s="110"/>
+      <c r="J65" s="93" t="s">
         <v>105</v>
       </c>
       <c r="K65" s="45" t="s">
@@ -11903,11 +11904,11 @@
       <c r="P65" s="18">
         <v>10400</v>
       </c>
-      <c r="R65" s="102" t="s">
+      <c r="R65" s="98" t="s">
         <v>226</v>
       </c>
-      <c r="S65" s="103"/>
-      <c r="T65" s="104"/>
+      <c r="S65" s="99"/>
+      <c r="T65" s="100"/>
       <c r="Z65" s="39" t="s">
         <v>503</v>
       </c>
@@ -11951,7 +11952,7 @@
       <c r="P66" s="18">
         <v>10400</v>
       </c>
-      <c r="R66" s="93" t="s">
+      <c r="R66" s="96" t="s">
         <v>71</v>
       </c>
       <c r="S66" s="4" t="s">
@@ -12010,7 +12011,7 @@
       <c r="T67" s="47">
         <v>8580</v>
       </c>
-      <c r="AD67" s="98" t="s">
+      <c r="AD67" s="93" t="s">
         <v>519</v>
       </c>
       <c r="AE67" s="45" t="s">
@@ -12030,7 +12031,7 @@
       <c r="D68" s="33">
         <v>11400</v>
       </c>
-      <c r="J68" s="110" t="s">
+      <c r="J68" s="118" t="s">
         <v>119</v>
       </c>
       <c r="K68" s="45" t="s">
@@ -12075,7 +12076,7 @@
       <c r="D69" s="33">
         <v>11400</v>
       </c>
-      <c r="J69" s="111"/>
+      <c r="J69" s="119"/>
       <c r="K69" s="50" t="s">
         <v>561</v>
       </c>
@@ -12118,7 +12119,7 @@
       <c r="D70" s="33">
         <v>11400</v>
       </c>
-      <c r="J70" s="98" t="s">
+      <c r="J70" s="93" t="s">
         <v>113</v>
       </c>
       <c r="K70" s="45" t="s">
@@ -12141,11 +12142,11 @@
       <c r="T70" s="18">
         <v>9620</v>
       </c>
-      <c r="AD70" s="105" t="s">
+      <c r="AD70" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="AE70" s="105"/>
-      <c r="AF70" s="105"/>
+      <c r="AE70" s="101"/>
+      <c r="AF70" s="101"/>
     </row>
     <row r="71" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="30" t="s">
@@ -12173,7 +12174,7 @@
       <c r="P71" s="18">
         <v>10400</v>
       </c>
-      <c r="R71" s="124" t="s">
+      <c r="R71" s="120" t="s">
         <v>103</v>
       </c>
       <c r="S71" s="4" t="s">
@@ -12182,7 +12183,7 @@
       <c r="T71" s="18">
         <v>9620</v>
       </c>
-      <c r="AD71" s="93" t="s">
+      <c r="AD71" s="96" t="s">
         <v>520</v>
       </c>
       <c r="AE71" s="7" t="s">
@@ -12193,11 +12194,11 @@
       </c>
     </row>
     <row r="72" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="120" t="s">
+      <c r="B72" s="108" t="s">
         <v>244</v>
       </c>
-      <c r="C72" s="121"/>
-      <c r="D72" s="123"/>
+      <c r="C72" s="109"/>
+      <c r="D72" s="111"/>
       <c r="J72" s="40" t="s">
         <v>117</v>
       </c>
@@ -12216,7 +12217,7 @@
       <c r="P72" s="23">
         <v>10400</v>
       </c>
-      <c r="R72" s="125"/>
+      <c r="R72" s="121"/>
       <c r="S72" s="4" t="s">
         <v>568</v>
       </c>
@@ -12251,14 +12252,14 @@
       </c>
       <c r="O73" s="84"/>
       <c r="P73" s="85"/>
-      <c r="R73" s="126"/>
+      <c r="R73" s="122"/>
       <c r="S73" s="62" t="s">
         <v>570</v>
       </c>
       <c r="T73" s="47">
         <v>0</v>
       </c>
-      <c r="AD73" s="98" t="s">
+      <c r="AD73" s="93" t="s">
         <v>521</v>
       </c>
       <c r="AE73" s="45" t="s">
@@ -12296,11 +12297,11 @@
       <c r="P74" s="18">
         <v>10400</v>
       </c>
-      <c r="R74" s="102" t="s">
+      <c r="R74" s="98" t="s">
         <v>229</v>
       </c>
-      <c r="S74" s="103"/>
-      <c r="T74" s="104"/>
+      <c r="S74" s="99"/>
+      <c r="T74" s="100"/>
       <c r="AD74" s="95"/>
       <c r="AE74" s="46" t="s">
         <v>582</v>
@@ -12335,7 +12336,7 @@
       <c r="P75" s="18">
         <v>10400</v>
       </c>
-      <c r="R75" s="93" t="s">
+      <c r="R75" s="96" t="s">
         <v>82</v>
       </c>
       <c r="S75" s="4" t="s">
@@ -12409,7 +12410,7 @@
       <c r="D77" s="33">
         <v>11400</v>
       </c>
-      <c r="J77" s="93" t="s">
+      <c r="J77" s="96" t="s">
         <v>99</v>
       </c>
       <c r="K77" s="7" t="s">
@@ -12427,7 +12428,7 @@
       <c r="P77" s="18">
         <v>10400</v>
       </c>
-      <c r="R77" s="98" t="s">
+      <c r="R77" s="93" t="s">
         <v>230</v>
       </c>
       <c r="S77" s="64" t="s">
@@ -12436,11 +12437,11 @@
       <c r="T77" s="48">
         <v>9620</v>
       </c>
-      <c r="AD77" s="106" t="s">
+      <c r="AD77" s="112" t="s">
         <v>524</v>
       </c>
-      <c r="AE77" s="107"/>
-      <c r="AF77" s="108"/>
+      <c r="AE77" s="113"/>
+      <c r="AF77" s="114"/>
     </row>
     <row r="78" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B78" s="30" t="s">
@@ -12475,7 +12476,7 @@
       <c r="T78" s="47">
         <v>8580</v>
       </c>
-      <c r="AD78" s="93" t="s">
+      <c r="AD78" s="96" t="s">
         <v>103</v>
       </c>
       <c r="AE78" s="7" t="s">
@@ -12511,11 +12512,11 @@
       <c r="P79" s="18">
         <v>10400</v>
       </c>
-      <c r="R79" s="105" t="s">
+      <c r="R79" s="101" t="s">
         <v>61</v>
       </c>
-      <c r="S79" s="105"/>
-      <c r="T79" s="105"/>
+      <c r="S79" s="101"/>
+      <c r="T79" s="101"/>
       <c r="AD79" s="94"/>
       <c r="AE79" s="7" t="s">
         <v>573</v>
@@ -12550,7 +12551,7 @@
       <c r="P80" s="18">
         <v>10400</v>
       </c>
-      <c r="R80" s="93" t="s">
+      <c r="R80" s="96" t="s">
         <v>5</v>
       </c>
       <c r="S80" s="4" t="s">
@@ -12620,7 +12621,7 @@
       <c r="D82" s="33">
         <v>11400</v>
       </c>
-      <c r="J82" s="93" t="s">
+      <c r="J82" s="96" t="s">
         <v>110</v>
       </c>
       <c r="K82" s="7" t="s">
@@ -12634,7 +12635,7 @@
       </c>
       <c r="O82" s="84"/>
       <c r="P82" s="85"/>
-      <c r="R82" s="98" t="s">
+      <c r="R82" s="93" t="s">
         <v>231</v>
       </c>
       <c r="S82" s="64" t="s">
@@ -12643,7 +12644,7 @@
       <c r="T82" s="48">
         <v>9620</v>
       </c>
-      <c r="AD82" s="98" t="s">
+      <c r="AD82" s="93" t="s">
         <v>525</v>
       </c>
       <c r="AE82" s="45" t="s">
@@ -12720,7 +12721,7 @@
       <c r="P84" s="20">
         <v>9620</v>
       </c>
-      <c r="R84" s="98" t="s">
+      <c r="R84" s="93" t="s">
         <v>232</v>
       </c>
       <c r="S84" s="64" t="s">
@@ -12729,7 +12730,7 @@
       <c r="T84" s="48">
         <v>9620</v>
       </c>
-      <c r="AD84" s="98" t="s">
+      <c r="AD84" s="93" t="s">
         <v>526</v>
       </c>
       <c r="AE84" s="45" t="s">
@@ -12740,11 +12741,11 @@
       </c>
     </row>
     <row r="85" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="120" t="s">
+      <c r="B85" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="C85" s="121"/>
-      <c r="D85" s="123"/>
+      <c r="C85" s="109"/>
+      <c r="D85" s="111"/>
       <c r="J85" s="39" t="s">
         <v>111</v>
       </c>
@@ -12804,7 +12805,7 @@
       <c r="P86" s="20">
         <v>9620</v>
       </c>
-      <c r="R86" s="98" t="s">
+      <c r="R86" s="93" t="s">
         <v>7</v>
       </c>
       <c r="S86" s="64" t="s">
@@ -12856,7 +12857,7 @@
       <c r="T87" s="44">
         <v>8320</v>
       </c>
-      <c r="AD87" s="98" t="s">
+      <c r="AD87" s="93" t="s">
         <v>527</v>
       </c>
       <c r="AE87" s="45" t="s">
@@ -12929,7 +12930,7 @@
       <c r="P89" s="18">
         <v>9620</v>
       </c>
-      <c r="R89" s="98" t="s">
+      <c r="R89" s="93" t="s">
         <v>115</v>
       </c>
       <c r="S89" s="64" t="s">
@@ -12938,7 +12939,7 @@
       <c r="T89" s="48">
         <v>9620</v>
       </c>
-      <c r="AD89" s="98" t="s">
+      <c r="AD89" s="93" t="s">
         <v>528</v>
       </c>
       <c r="AE89" s="45" t="s">
@@ -12999,7 +13000,7 @@
       <c r="D91" s="33">
         <v>11400</v>
       </c>
-      <c r="J91" s="98" t="s">
+      <c r="J91" s="93" t="s">
         <v>116</v>
       </c>
       <c r="K91" s="45" t="s">
@@ -13026,7 +13027,7 @@
       <c r="T91" s="44">
         <v>9620</v>
       </c>
-      <c r="AD91" s="98" t="s">
+      <c r="AD91" s="93" t="s">
         <v>529</v>
       </c>
       <c r="AE91" s="45" t="s">
@@ -13071,11 +13072,11 @@
       </c>
     </row>
     <row r="93" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B93" s="120" t="s">
+      <c r="B93" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="C93" s="121"/>
-      <c r="D93" s="123"/>
+      <c r="C93" s="109"/>
+      <c r="D93" s="111"/>
       <c r="J93" s="97" t="s">
         <v>125</v>
       </c>
@@ -13090,11 +13091,11 @@
       <c r="P93" s="18">
         <v>10400</v>
       </c>
-      <c r="AD93" s="105" t="s">
+      <c r="AD93" s="101" t="s">
         <v>530</v>
       </c>
-      <c r="AE93" s="105"/>
-      <c r="AF93" s="105"/>
+      <c r="AE93" s="101"/>
+      <c r="AF93" s="101"/>
     </row>
     <row r="94" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B94" s="30" t="s">
@@ -13124,7 +13125,7 @@
       <c r="P94" s="18">
         <v>10400</v>
       </c>
-      <c r="AD94" s="93" t="s">
+      <c r="AD94" s="96" t="s">
         <v>110</v>
       </c>
       <c r="AE94" s="7" t="s">
@@ -13135,11 +13136,11 @@
       </c>
     </row>
     <row r="95" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="120" t="s">
+      <c r="B95" s="108" t="s">
         <v>115</v>
       </c>
-      <c r="C95" s="121"/>
-      <c r="D95" s="123"/>
+      <c r="C95" s="109"/>
+      <c r="D95" s="111"/>
       <c r="J95" s="95"/>
       <c r="K95" s="46" t="s">
         <v>560</v>
@@ -13174,7 +13175,7 @@
       <c r="D96" s="33">
         <v>11400</v>
       </c>
-      <c r="J96" s="98" t="s">
+      <c r="J96" s="93" t="s">
         <v>71</v>
       </c>
       <c r="K96" s="45" t="s">
@@ -13262,11 +13263,11 @@
       <c r="P98" s="18">
         <v>10400</v>
       </c>
-      <c r="AD98" s="106" t="s">
+      <c r="AD98" s="112" t="s">
         <v>532</v>
       </c>
-      <c r="AE98" s="107"/>
-      <c r="AF98" s="108"/>
+      <c r="AE98" s="113"/>
+      <c r="AF98" s="114"/>
     </row>
     <row r="99" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B99" s="30" t="s">
@@ -13278,7 +13279,7 @@
       <c r="D99" s="33">
         <v>11400</v>
       </c>
-      <c r="J99" s="98" t="s">
+      <c r="J99" s="93" t="s">
         <v>76</v>
       </c>
       <c r="K99" s="45" t="s">
@@ -13296,7 +13297,7 @@
       <c r="P99" s="18">
         <v>9620</v>
       </c>
-      <c r="AD99" s="93" t="s">
+      <c r="AD99" s="96" t="s">
         <v>533</v>
       </c>
       <c r="AE99" s="7" t="s">
@@ -13388,7 +13389,7 @@
       <c r="D102" s="33">
         <v>11400</v>
       </c>
-      <c r="J102" s="93" t="s">
+      <c r="J102" s="96" t="s">
         <v>83</v>
       </c>
       <c r="K102" s="7" t="s">
@@ -13402,11 +13403,11 @@
       </c>
       <c r="O102" s="86"/>
       <c r="P102" s="86"/>
-      <c r="AD102" s="106" t="s">
+      <c r="AD102" s="112" t="s">
         <v>55</v>
       </c>
-      <c r="AE102" s="107"/>
-      <c r="AF102" s="108"/>
+      <c r="AE102" s="113"/>
+      <c r="AF102" s="114"/>
     </row>
     <row r="103" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B103" s="30" t="s">
@@ -13434,7 +13435,7 @@
       <c r="P103" s="18">
         <v>10400</v>
       </c>
-      <c r="AD103" s="93" t="s">
+      <c r="AD103" s="96" t="s">
         <v>114</v>
       </c>
       <c r="AE103" s="7" t="s">
@@ -13524,11 +13525,11 @@
       <c r="L106" s="44">
         <v>10660</v>
       </c>
-      <c r="AD106" s="102" t="s">
+      <c r="AD106" s="98" t="s">
         <v>535</v>
       </c>
-      <c r="AE106" s="103"/>
-      <c r="AF106" s="104"/>
+      <c r="AE106" s="99"/>
+      <c r="AF106" s="100"/>
     </row>
     <row r="107" spans="2:32" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B107" s="30" t="s">
@@ -13547,7 +13548,7 @@
       <c r="L107" s="44">
         <v>8320</v>
       </c>
-      <c r="AD107" s="109" t="s">
+      <c r="AD107" s="123" t="s">
         <v>67</v>
       </c>
       <c r="AE107" s="7" t="s">
@@ -13574,7 +13575,7 @@
       <c r="L108" s="51">
         <v>0</v>
       </c>
-      <c r="AD108" s="100"/>
+      <c r="AD108" s="124"/>
       <c r="AE108" s="7" t="s">
         <v>573</v>
       </c>
@@ -13592,7 +13593,7 @@
       <c r="D109" s="33">
         <v>11400</v>
       </c>
-      <c r="J109" s="98" t="s">
+      <c r="J109" s="93" t="s">
         <v>92</v>
       </c>
       <c r="K109" s="45" t="s">
@@ -13601,7 +13602,7 @@
       <c r="L109" s="48">
         <v>8320</v>
       </c>
-      <c r="AD109" s="100"/>
+      <c r="AD109" s="124"/>
       <c r="AE109" s="7" t="s">
         <v>582</v>
       </c>
@@ -13626,7 +13627,7 @@
       <c r="L110" s="51">
         <v>0</v>
       </c>
-      <c r="AD110" s="101"/>
+      <c r="AD110" s="125"/>
       <c r="AE110" s="46" t="s">
         <v>570</v>
       </c>
@@ -13653,7 +13654,7 @@
       <c r="L111" s="44">
         <v>9100</v>
       </c>
-      <c r="AD111" s="98" t="s">
+      <c r="AD111" s="93" t="s">
         <v>536</v>
       </c>
       <c r="AE111" s="45" t="s">
@@ -13817,7 +13818,7 @@
       <c r="L117" s="51">
         <v>0</v>
       </c>
-      <c r="AD117" s="93" t="s">
+      <c r="AD117" s="96" t="s">
         <v>115</v>
       </c>
       <c r="AE117" s="7" t="s">
@@ -13837,7 +13838,7 @@
       <c r="D118" s="33">
         <v>11400</v>
       </c>
-      <c r="J118" s="98" t="s">
+      <c r="J118" s="93" t="s">
         <v>103</v>
       </c>
       <c r="K118" s="45" t="s">
@@ -13923,7 +13924,7 @@
       <c r="L121" s="44">
         <v>8320</v>
       </c>
-      <c r="AD121" s="98" t="s">
+      <c r="AD121" s="93" t="s">
         <v>538</v>
       </c>
       <c r="AE121" s="45" t="s">
@@ -14002,7 +14003,7 @@
       <c r="L124" s="47">
         <v>0</v>
       </c>
-      <c r="AD124" s="98" t="s">
+      <c r="AD124" s="93" t="s">
         <v>539</v>
       </c>
       <c r="AE124" s="45" t="s">
@@ -14022,7 +14023,7 @@
       <c r="D125" s="33">
         <v>11400</v>
       </c>
-      <c r="J125" s="98" t="s">
+      <c r="J125" s="93" t="s">
         <v>108</v>
       </c>
       <c r="K125" s="45" t="s">
@@ -14108,11 +14109,11 @@
       <c r="L128" s="44">
         <v>8320</v>
       </c>
-      <c r="AD128" s="105" t="s">
+      <c r="AD128" s="101" t="s">
         <v>540</v>
       </c>
-      <c r="AE128" s="105"/>
-      <c r="AF128" s="105"/>
+      <c r="AE128" s="101"/>
+      <c r="AF128" s="101"/>
     </row>
     <row r="129" spans="2:32" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B129" s="30" t="s">
@@ -14160,7 +14161,7 @@
       <c r="L130" s="51">
         <v>8320</v>
       </c>
-      <c r="AD130" s="93" t="s">
+      <c r="AD130" s="96" t="s">
         <v>519</v>
       </c>
       <c r="AE130" s="7" t="s">
@@ -14261,7 +14262,7 @@
       <c r="D135" s="33">
         <v>11400</v>
       </c>
-      <c r="AD135" s="93" t="s">
+      <c r="AD135" s="96" t="s">
         <v>544</v>
       </c>
       <c r="AE135" s="7" t="s">
@@ -14281,7 +14282,7 @@
       <c r="D136" s="33">
         <v>11400</v>
       </c>
-      <c r="AD136" s="96"/>
+      <c r="AD136" s="102"/>
       <c r="AE136" s="39" t="s">
         <v>582</v>
       </c>
@@ -14364,6 +14365,164 @@
     </row>
   </sheetData>
   <mergeCells count="182">
+    <mergeCell ref="AD130:AD132"/>
+    <mergeCell ref="AD135:AD136"/>
+    <mergeCell ref="AD14:AD15"/>
+    <mergeCell ref="AD134:AF134"/>
+    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="AD17:AD20"/>
+    <mergeCell ref="AD21:AD23"/>
+    <mergeCell ref="AD24:AD27"/>
+    <mergeCell ref="AD28:AD31"/>
+    <mergeCell ref="AD34:AD37"/>
+    <mergeCell ref="AD38:AD41"/>
+    <mergeCell ref="AD42:AD45"/>
+    <mergeCell ref="AD47:AD50"/>
+    <mergeCell ref="AD51:AD54"/>
+    <mergeCell ref="AD55:AD57"/>
+    <mergeCell ref="AD58:AD60"/>
+    <mergeCell ref="AD61:AD63"/>
+    <mergeCell ref="AD64:AD66"/>
+    <mergeCell ref="AD67:AD69"/>
+    <mergeCell ref="AD71:AD72"/>
+    <mergeCell ref="AD73:AD74"/>
+    <mergeCell ref="AD78:AD81"/>
+    <mergeCell ref="AD82:AD83"/>
+    <mergeCell ref="AD84:AD86"/>
+    <mergeCell ref="AD87:AD88"/>
+    <mergeCell ref="AD89:AD90"/>
+    <mergeCell ref="AD91:AD92"/>
+    <mergeCell ref="Z59:Z60"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AD8:AF8"/>
+    <mergeCell ref="AD16:AF16"/>
+    <mergeCell ref="AD32:AF32"/>
+    <mergeCell ref="AD46:AF46"/>
+    <mergeCell ref="AD70:AF70"/>
+    <mergeCell ref="AD77:AF77"/>
+    <mergeCell ref="AA6:AB6"/>
+    <mergeCell ref="Z8:AB8"/>
+    <mergeCell ref="Z20:AB20"/>
+    <mergeCell ref="Z23:AB23"/>
+    <mergeCell ref="Z26:AB26"/>
+    <mergeCell ref="Z33:AB33"/>
+    <mergeCell ref="Z41:AB41"/>
+    <mergeCell ref="Z53:AB53"/>
+    <mergeCell ref="Z58:AB58"/>
+    <mergeCell ref="Z21:Z22"/>
+    <mergeCell ref="Z30:Z31"/>
+    <mergeCell ref="Z18:Z19"/>
+    <mergeCell ref="Z45:Z46"/>
+    <mergeCell ref="AD93:AF93"/>
+    <mergeCell ref="AD98:AF98"/>
+    <mergeCell ref="AD102:AF102"/>
+    <mergeCell ref="AD106:AF106"/>
+    <mergeCell ref="AD128:AF128"/>
+    <mergeCell ref="AD94:AD96"/>
+    <mergeCell ref="AD99:AD100"/>
+    <mergeCell ref="AD103:AD105"/>
+    <mergeCell ref="AD107:AD110"/>
+    <mergeCell ref="AD111:AD114"/>
+    <mergeCell ref="AD117:AD120"/>
+    <mergeCell ref="AD121:AD123"/>
+    <mergeCell ref="AD124:AD127"/>
+    <mergeCell ref="J129:J130"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="J115:J117"/>
+    <mergeCell ref="J118:J120"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="V8:X8"/>
+    <mergeCell ref="V10:X10"/>
+    <mergeCell ref="V13:X13"/>
+    <mergeCell ref="V15:X15"/>
+    <mergeCell ref="V21:X21"/>
+    <mergeCell ref="V26:X26"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="V39:X39"/>
+    <mergeCell ref="V46:X46"/>
+    <mergeCell ref="V51:X51"/>
+    <mergeCell ref="V54:X54"/>
+    <mergeCell ref="V56:X56"/>
+    <mergeCell ref="V47:V48"/>
+    <mergeCell ref="J122:J124"/>
+    <mergeCell ref="J106:J108"/>
+    <mergeCell ref="J109:J110"/>
+    <mergeCell ref="J74:J75"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="J125:J127"/>
+    <mergeCell ref="Z42:Z43"/>
+    <mergeCell ref="J102:J104"/>
+    <mergeCell ref="J99:J100"/>
+    <mergeCell ref="N82:P82"/>
+    <mergeCell ref="R82:R83"/>
+    <mergeCell ref="R84:R85"/>
+    <mergeCell ref="R86:R88"/>
+    <mergeCell ref="R61:R64"/>
+    <mergeCell ref="R89:R90"/>
+    <mergeCell ref="R66:R67"/>
+    <mergeCell ref="R71:R73"/>
+    <mergeCell ref="R75:R76"/>
+    <mergeCell ref="R77:R78"/>
+    <mergeCell ref="R80:R81"/>
+    <mergeCell ref="J96:J98"/>
+    <mergeCell ref="J61:J64"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="J25:J27"/>
+    <mergeCell ref="J53:L53"/>
+    <mergeCell ref="J73:L73"/>
+    <mergeCell ref="J40:J42"/>
+    <mergeCell ref="J65:J67"/>
+    <mergeCell ref="J68:J69"/>
+    <mergeCell ref="J77:J80"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="J82:J84"/>
+    <mergeCell ref="J70:J71"/>
+    <mergeCell ref="J87:J90"/>
+    <mergeCell ref="J94:J95"/>
+    <mergeCell ref="J54:J56"/>
+    <mergeCell ref="J59:J60"/>
+    <mergeCell ref="J57:J58"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="J8:J10"/>
+    <mergeCell ref="J11:J13"/>
+    <mergeCell ref="J32:J34"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="J48:J50"/>
+    <mergeCell ref="J14:J16"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="B140:D140"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B95:D95"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="J7:L7"/>
     <mergeCell ref="R38:R40"/>
     <mergeCell ref="R44:R45"/>
     <mergeCell ref="R46:R52"/>
@@ -14388,164 +14547,6 @@
     <mergeCell ref="N61:P61"/>
     <mergeCell ref="N70:P70"/>
     <mergeCell ref="N73:P73"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="N40:P40"/>
-    <mergeCell ref="B140:D140"/>
-    <mergeCell ref="D3:K3"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="B95:D95"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="J8:J10"/>
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="J32:J34"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="J44:J45"/>
-    <mergeCell ref="J46:J47"/>
-    <mergeCell ref="J48:J50"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="J96:J98"/>
-    <mergeCell ref="J61:J64"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="J25:J27"/>
-    <mergeCell ref="J53:L53"/>
-    <mergeCell ref="J73:L73"/>
-    <mergeCell ref="J40:J42"/>
-    <mergeCell ref="J65:J67"/>
-    <mergeCell ref="J68:J69"/>
-    <mergeCell ref="J77:J80"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="J82:J84"/>
-    <mergeCell ref="J70:J71"/>
-    <mergeCell ref="J87:J90"/>
-    <mergeCell ref="J94:J95"/>
-    <mergeCell ref="J54:J56"/>
-    <mergeCell ref="J59:J60"/>
-    <mergeCell ref="J57:J58"/>
-    <mergeCell ref="Z42:Z43"/>
-    <mergeCell ref="J102:J104"/>
-    <mergeCell ref="J99:J100"/>
-    <mergeCell ref="N82:P82"/>
-    <mergeCell ref="R82:R83"/>
-    <mergeCell ref="R84:R85"/>
-    <mergeCell ref="R86:R88"/>
-    <mergeCell ref="R61:R64"/>
-    <mergeCell ref="R89:R90"/>
-    <mergeCell ref="R66:R67"/>
-    <mergeCell ref="R71:R73"/>
-    <mergeCell ref="R75:R76"/>
-    <mergeCell ref="R77:R78"/>
-    <mergeCell ref="R80:R81"/>
-    <mergeCell ref="J129:J130"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="J115:J117"/>
-    <mergeCell ref="J118:J120"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="V8:X8"/>
-    <mergeCell ref="V10:X10"/>
-    <mergeCell ref="V13:X13"/>
-    <mergeCell ref="V15:X15"/>
-    <mergeCell ref="V21:X21"/>
-    <mergeCell ref="V26:X26"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="V39:X39"/>
-    <mergeCell ref="V46:X46"/>
-    <mergeCell ref="V51:X51"/>
-    <mergeCell ref="V54:X54"/>
-    <mergeCell ref="V56:X56"/>
-    <mergeCell ref="V47:V48"/>
-    <mergeCell ref="J122:J124"/>
-    <mergeCell ref="J106:J108"/>
-    <mergeCell ref="J109:J110"/>
-    <mergeCell ref="J74:J75"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="J125:J127"/>
-    <mergeCell ref="AD93:AF93"/>
-    <mergeCell ref="AD98:AF98"/>
-    <mergeCell ref="AD102:AF102"/>
-    <mergeCell ref="AD106:AF106"/>
-    <mergeCell ref="AD128:AF128"/>
-    <mergeCell ref="AD94:AD96"/>
-    <mergeCell ref="AD99:AD100"/>
-    <mergeCell ref="AD103:AD105"/>
-    <mergeCell ref="AD107:AD110"/>
-    <mergeCell ref="AD111:AD114"/>
-    <mergeCell ref="AD117:AD120"/>
-    <mergeCell ref="AD121:AD123"/>
-    <mergeCell ref="AD124:AD127"/>
-    <mergeCell ref="AD87:AD88"/>
-    <mergeCell ref="AD89:AD90"/>
-    <mergeCell ref="AD91:AD92"/>
-    <mergeCell ref="Z59:Z60"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AD8:AF8"/>
-    <mergeCell ref="AD16:AF16"/>
-    <mergeCell ref="AD32:AF32"/>
-    <mergeCell ref="AD46:AF46"/>
-    <mergeCell ref="AD70:AF70"/>
-    <mergeCell ref="AD77:AF77"/>
-    <mergeCell ref="AA6:AB6"/>
-    <mergeCell ref="Z8:AB8"/>
-    <mergeCell ref="Z20:AB20"/>
-    <mergeCell ref="Z23:AB23"/>
-    <mergeCell ref="Z26:AB26"/>
-    <mergeCell ref="Z33:AB33"/>
-    <mergeCell ref="Z41:AB41"/>
-    <mergeCell ref="Z53:AB53"/>
-    <mergeCell ref="Z58:AB58"/>
-    <mergeCell ref="Z21:Z22"/>
-    <mergeCell ref="Z30:Z31"/>
-    <mergeCell ref="Z18:Z19"/>
-    <mergeCell ref="Z45:Z46"/>
-    <mergeCell ref="AD130:AD132"/>
-    <mergeCell ref="AD135:AD136"/>
-    <mergeCell ref="AD14:AD15"/>
-    <mergeCell ref="AD134:AF134"/>
-    <mergeCell ref="AD9:AD10"/>
-    <mergeCell ref="AD17:AD20"/>
-    <mergeCell ref="AD21:AD23"/>
-    <mergeCell ref="AD24:AD27"/>
-    <mergeCell ref="AD28:AD31"/>
-    <mergeCell ref="AD34:AD37"/>
-    <mergeCell ref="AD38:AD41"/>
-    <mergeCell ref="AD42:AD45"/>
-    <mergeCell ref="AD47:AD50"/>
-    <mergeCell ref="AD51:AD54"/>
-    <mergeCell ref="AD55:AD57"/>
-    <mergeCell ref="AD58:AD60"/>
-    <mergeCell ref="AD61:AD63"/>
-    <mergeCell ref="AD64:AD66"/>
-    <mergeCell ref="AD67:AD69"/>
-    <mergeCell ref="AD71:AD72"/>
-    <mergeCell ref="AD73:AD74"/>
-    <mergeCell ref="AD78:AD81"/>
-    <mergeCell ref="AD82:AD83"/>
-    <mergeCell ref="AD84:AD86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/resources/Data/University Fees.xlsx
+++ b/resources/Data/University Fees.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Financial Calculator\resources\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521066F2-8F0C-4BD7-8FD0-16A2591786B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3BA86D-3234-4C5B-BD88-39B53E874394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{9076E21E-61F9-4A5A-ABD0-5DFDD0B945A9}"/>
     <workbookView xWindow="7545" yWindow="1695" windowWidth="21600" windowHeight="11385" xr2:uid="{ADD0AE33-0E96-45FA-8680-34EE88D7AD79}"/>
